--- a/システム開発演習/000-要件定義/003-WBS.xlsx
+++ b/システム開発演習/000-要件定義/003-WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\システム開発演習\000-要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C8EB0C-6C84-4B6A-AFE8-02CD459B0C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA15A06D-9CDE-4CEF-912F-D03F3F6B9A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1762,7 +1762,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2052,12 +2052,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2139,14 +2133,224 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2157,12 +2361,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2175,33 +2373,6 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2226,183 +2397,6 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2420,6 +2414,24 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3138,94 +3150,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="198" t="s">
+      <c r="A1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="201" t="s">
+      <c r="B1" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="204" t="s">
+      <c r="C1" s="135" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="205"/>
-      <c r="E1" s="210" t="s">
+      <c r="D1" s="136"/>
+      <c r="E1" s="141" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="213" t="s">
+      <c r="F1" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="195">
+      <c r="G1" s="126">
         <v>45536</v>
       </c>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="196"/>
-      <c r="M1" s="196"/>
-      <c r="N1" s="196"/>
-      <c r="O1" s="196"/>
-      <c r="P1" s="196"/>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="196"/>
-      <c r="T1" s="196"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="196"/>
-      <c r="W1" s="196"/>
-      <c r="X1" s="196"/>
-      <c r="Y1" s="196"/>
-      <c r="Z1" s="196"/>
-      <c r="AA1" s="196"/>
-      <c r="AB1" s="196"/>
-      <c r="AC1" s="196"/>
-      <c r="AD1" s="196"/>
-      <c r="AE1" s="196"/>
-      <c r="AF1" s="196"/>
-      <c r="AG1" s="196"/>
-      <c r="AH1" s="196"/>
-      <c r="AI1" s="196"/>
-      <c r="AJ1" s="197"/>
-      <c r="AK1" s="195">
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="128"/>
+      <c r="AK1" s="126">
         <v>45566</v>
       </c>
-      <c r="AL1" s="196"/>
-      <c r="AM1" s="196"/>
-      <c r="AN1" s="196"/>
-      <c r="AO1" s="196"/>
-      <c r="AP1" s="196"/>
-      <c r="AQ1" s="196"/>
-      <c r="AR1" s="196"/>
-      <c r="AS1" s="196"/>
-      <c r="AT1" s="196"/>
-      <c r="AU1" s="196"/>
-      <c r="AV1" s="196"/>
-      <c r="AW1" s="196"/>
-      <c r="AX1" s="196"/>
-      <c r="AY1" s="196"/>
-      <c r="AZ1" s="196"/>
-      <c r="BA1" s="196"/>
-      <c r="BB1" s="196"/>
-      <c r="BC1" s="196"/>
-      <c r="BD1" s="196"/>
-      <c r="BE1" s="196"/>
-      <c r="BF1" s="196"/>
-      <c r="BG1" s="196"/>
-      <c r="BH1" s="196"/>
-      <c r="BI1" s="196"/>
-      <c r="BJ1" s="196"/>
-      <c r="BK1" s="196"/>
-      <c r="BL1" s="196"/>
-      <c r="BM1" s="196"/>
-      <c r="BN1" s="197"/>
+      <c r="AL1" s="127"/>
+      <c r="AM1" s="127"/>
+      <c r="AN1" s="127"/>
+      <c r="AO1" s="127"/>
+      <c r="AP1" s="127"/>
+      <c r="AQ1" s="127"/>
+      <c r="AR1" s="127"/>
+      <c r="AS1" s="127"/>
+      <c r="AT1" s="127"/>
+      <c r="AU1" s="127"/>
+      <c r="AV1" s="127"/>
+      <c r="AW1" s="127"/>
+      <c r="AX1" s="127"/>
+      <c r="AY1" s="127"/>
+      <c r="AZ1" s="127"/>
+      <c r="BA1" s="127"/>
+      <c r="BB1" s="127"/>
+      <c r="BC1" s="127"/>
+      <c r="BD1" s="127"/>
+      <c r="BE1" s="127"/>
+      <c r="BF1" s="127"/>
+      <c r="BG1" s="127"/>
+      <c r="BH1" s="127"/>
+      <c r="BI1" s="127"/>
+      <c r="BJ1" s="127"/>
+      <c r="BK1" s="127"/>
+      <c r="BL1" s="127"/>
+      <c r="BM1" s="127"/>
+      <c r="BN1" s="128"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="199"/>
-      <c r="B2" s="202"/>
-      <c r="C2" s="206"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="211"/>
-      <c r="F2" s="214"/>
+      <c r="A2" s="130"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="145"/>
       <c r="G2" s="46">
         <v>45537</v>
       </c>
@@ -3467,12 +3479,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="200"/>
-      <c r="B3" s="203"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="209"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="215"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="146"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -3655,28 +3667,28 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="188">
+      <c r="A4" s="157">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="191" t="s">
+      <c r="D4" s="159"/>
+      <c r="E4" s="162" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="193"/>
+      <c r="F4" s="164"/>
       <c r="G4" s="95"/>
       <c r="H4" s="29"/>
-      <c r="I4" s="127"/>
+      <c r="I4" s="125"/>
       <c r="J4" s="61"/>
       <c r="K4" s="61"/>
       <c r="L4" s="12"/>
       <c r="M4" s="18"/>
-      <c r="N4" s="126"/>
+      <c r="N4" s="124"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
@@ -3733,10 +3745,10 @@
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
       <c r="A5" s="148"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="192"/>
-      <c r="F5" s="194"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="163"/>
+      <c r="F5" s="165"/>
       <c r="G5" s="96"/>
       <c r="H5" s="31"/>
       <c r="I5" s="97"/>
@@ -3799,18 +3811,18 @@
       <c r="BN5" s="72"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="130">
+      <c r="A6" s="147">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="165" t="s">
+      <c r="C6" s="149" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="141"/>
-      <c r="E6" s="184" t="s">
+      <c r="D6" s="150"/>
+      <c r="E6" s="153" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="186"/>
+      <c r="F6" s="155"/>
       <c r="G6" s="51"/>
       <c r="H6" s="63"/>
       <c r="I6" s="30"/>
@@ -3875,10 +3887,10 @@
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
       <c r="A7" s="148"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="166"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="185"/>
-      <c r="F7" s="187"/>
+      <c r="C7" s="151"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="156"/>
       <c r="G7" s="52"/>
       <c r="H7" s="64"/>
       <c r="I7" s="32"/>
@@ -3941,7 +3953,7 @@
       <c r="BN7" s="74"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="157">
+      <c r="A8" s="166">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
@@ -3954,7 +3966,7 @@
       <c r="E8" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="172"/>
+      <c r="F8" s="186"/>
       <c r="G8" s="38"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65"/>
@@ -4017,96 +4029,96 @@
       <c r="BN8" s="75"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="169"/>
+      <c r="A9" s="167"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="173"/>
-      <c r="D9" s="174"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="107"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="108"/>
-      <c r="M9" s="109"/>
+      <c r="C9" s="169"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="175"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="108"/>
+      <c r="L9" s="106"/>
+      <c r="M9" s="107"/>
       <c r="N9" s="32"/>
-      <c r="O9" s="123"/>
-      <c r="P9" s="110"/>
-      <c r="Q9" s="110"/>
-      <c r="R9" s="110"/>
-      <c r="S9" s="108"/>
-      <c r="T9" s="109"/>
-      <c r="U9" s="109"/>
-      <c r="V9" s="111"/>
-      <c r="W9" s="111"/>
-      <c r="X9" s="111"/>
-      <c r="Y9" s="111"/>
-      <c r="Z9" s="108"/>
-      <c r="AA9" s="109"/>
-      <c r="AB9" s="109"/>
-      <c r="AC9" s="111"/>
-      <c r="AD9" s="111"/>
-      <c r="AE9" s="111"/>
-      <c r="AF9" s="111"/>
-      <c r="AG9" s="108"/>
-      <c r="AH9" s="109"/>
-      <c r="AI9" s="111"/>
-      <c r="AJ9" s="112"/>
-      <c r="AK9" s="113"/>
-      <c r="AL9" s="111"/>
-      <c r="AM9" s="111"/>
-      <c r="AN9" s="108"/>
-      <c r="AO9" s="109"/>
-      <c r="AP9" s="111"/>
-      <c r="AQ9" s="111"/>
-      <c r="AR9" s="111"/>
-      <c r="AS9" s="111"/>
-      <c r="AT9" s="111"/>
-      <c r="AU9" s="108"/>
-      <c r="AV9" s="109"/>
-      <c r="AW9" s="109"/>
-      <c r="AX9" s="111"/>
-      <c r="AY9" s="111"/>
-      <c r="AZ9" s="111"/>
-      <c r="BA9" s="111"/>
-      <c r="BB9" s="108"/>
-      <c r="BC9" s="109"/>
-      <c r="BD9" s="111"/>
-      <c r="BE9" s="111"/>
-      <c r="BF9" s="111"/>
-      <c r="BG9" s="111"/>
-      <c r="BH9" s="111"/>
-      <c r="BI9" s="108"/>
-      <c r="BJ9" s="109"/>
-      <c r="BK9" s="111"/>
-      <c r="BL9" s="111"/>
-      <c r="BM9" s="111"/>
-      <c r="BN9" s="112"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="108"/>
+      <c r="Q9" s="108"/>
+      <c r="R9" s="108"/>
+      <c r="S9" s="106"/>
+      <c r="T9" s="107"/>
+      <c r="U9" s="107"/>
+      <c r="V9" s="109"/>
+      <c r="W9" s="109"/>
+      <c r="X9" s="109"/>
+      <c r="Y9" s="109"/>
+      <c r="Z9" s="106"/>
+      <c r="AA9" s="107"/>
+      <c r="AB9" s="107"/>
+      <c r="AC9" s="109"/>
+      <c r="AD9" s="109"/>
+      <c r="AE9" s="109"/>
+      <c r="AF9" s="109"/>
+      <c r="AG9" s="106"/>
+      <c r="AH9" s="107"/>
+      <c r="AI9" s="109"/>
+      <c r="AJ9" s="110"/>
+      <c r="AK9" s="111"/>
+      <c r="AL9" s="109"/>
+      <c r="AM9" s="109"/>
+      <c r="AN9" s="106"/>
+      <c r="AO9" s="107"/>
+      <c r="AP9" s="109"/>
+      <c r="AQ9" s="109"/>
+      <c r="AR9" s="109"/>
+      <c r="AS9" s="109"/>
+      <c r="AT9" s="109"/>
+      <c r="AU9" s="106"/>
+      <c r="AV9" s="107"/>
+      <c r="AW9" s="107"/>
+      <c r="AX9" s="109"/>
+      <c r="AY9" s="109"/>
+      <c r="AZ9" s="109"/>
+      <c r="BA9" s="109"/>
+      <c r="BB9" s="106"/>
+      <c r="BC9" s="107"/>
+      <c r="BD9" s="109"/>
+      <c r="BE9" s="109"/>
+      <c r="BF9" s="109"/>
+      <c r="BG9" s="109"/>
+      <c r="BH9" s="109"/>
+      <c r="BI9" s="106"/>
+      <c r="BJ9" s="107"/>
+      <c r="BK9" s="109"/>
+      <c r="BL9" s="109"/>
+      <c r="BM9" s="109"/>
+      <c r="BN9" s="110"/>
     </row>
     <row r="10" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A10" s="169"/>
+      <c r="A10" s="167"/>
       <c r="B10" s="36"/>
       <c r="C10" s="179" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="180"/>
-      <c r="E10" s="162" t="s">
+      <c r="E10" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="146"/>
-      <c r="G10" s="117"/>
+      <c r="F10" s="187"/>
+      <c r="G10" s="115"/>
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
       <c r="J10" s="64"/>
-      <c r="K10" s="104"/>
+      <c r="K10" s="102"/>
       <c r="L10" s="25"/>
       <c r="M10" s="26"/>
       <c r="N10" s="42"/>
       <c r="O10" s="42"/>
-      <c r="P10" s="104"/>
-      <c r="Q10" s="104"/>
-      <c r="R10" s="104"/>
+      <c r="P10" s="102"/>
+      <c r="Q10" s="102"/>
+      <c r="R10" s="102"/>
       <c r="S10" s="25"/>
       <c r="T10" s="26"/>
       <c r="U10" s="26"/>
@@ -4153,28 +4165,28 @@
       <c r="BJ10" s="26"/>
       <c r="BK10" s="24"/>
       <c r="BL10" s="24"/>
-      <c r="BM10" s="114"/>
+      <c r="BM10" s="112"/>
       <c r="BN10" s="73"/>
     </row>
     <row r="11" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A11" s="169"/>
+      <c r="A11" s="167"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="175"/>
-      <c r="D11" s="176"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="106"/>
+      <c r="C11" s="171"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="174"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="104"/>
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
       <c r="J11" s="63"/>
-      <c r="K11" s="103"/>
+      <c r="K11" s="101"/>
       <c r="L11" s="13"/>
       <c r="M11" s="19"/>
-      <c r="N11" s="124"/>
-      <c r="O11" s="124"/>
-      <c r="P11" s="103"/>
-      <c r="Q11" s="103"/>
-      <c r="R11" s="103"/>
+      <c r="N11" s="122"/>
+      <c r="O11" s="122"/>
+      <c r="P11" s="101"/>
+      <c r="Q11" s="101"/>
+      <c r="R11" s="101"/>
       <c r="S11" s="13"/>
       <c r="T11" s="19"/>
       <c r="U11" s="19"/>
@@ -4209,7 +4221,7 @@
       <c r="AX11" s="7"/>
       <c r="AY11" s="7"/>
       <c r="AZ11" s="7"/>
-      <c r="BA11" s="116"/>
+      <c r="BA11" s="114"/>
       <c r="BB11" s="13"/>
       <c r="BC11" s="19"/>
       <c r="BD11" s="7"/>
@@ -4221,21 +4233,21 @@
       <c r="BJ11" s="19"/>
       <c r="BK11" s="7"/>
       <c r="BL11" s="7"/>
-      <c r="BM11" s="116"/>
-      <c r="BN11" s="112"/>
+      <c r="BM11" s="114"/>
+      <c r="BN11" s="110"/>
     </row>
     <row r="12" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A12" s="169"/>
+      <c r="A12" s="167"/>
       <c r="B12" s="36"/>
-      <c r="C12" s="173" t="s">
+      <c r="C12" s="169" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="174"/>
-      <c r="E12" s="163" t="s">
+      <c r="D12" s="170"/>
+      <c r="E12" s="173" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="128"/>
-      <c r="G12" s="117"/>
+      <c r="F12" s="175"/>
+      <c r="G12" s="115"/>
       <c r="H12" s="62"/>
       <c r="I12" s="62"/>
       <c r="J12" s="62"/>
@@ -4295,16 +4307,16 @@
       <c r="BJ12" s="22"/>
       <c r="BK12" s="9"/>
       <c r="BL12" s="9"/>
-      <c r="BM12" s="115"/>
+      <c r="BM12" s="113"/>
       <c r="BN12" s="73"/>
     </row>
     <row r="13" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A13" s="158"/>
+      <c r="A13" s="168"/>
       <c r="B13" s="37"/>
       <c r="C13" s="181"/>
       <c r="D13" s="182"/>
-      <c r="E13" s="168"/>
-      <c r="F13" s="147"/>
+      <c r="E13" s="185"/>
+      <c r="F13" s="188"/>
       <c r="G13" s="53"/>
       <c r="H13" s="66"/>
       <c r="I13" s="66"/>
@@ -4312,9 +4324,9 @@
       <c r="K13" s="66"/>
       <c r="L13" s="44"/>
       <c r="M13" s="45"/>
-      <c r="N13" s="107"/>
-      <c r="O13" s="125"/>
-      <c r="P13" s="125"/>
+      <c r="N13" s="105"/>
+      <c r="O13" s="123"/>
+      <c r="P13" s="123"/>
       <c r="Q13" s="66"/>
       <c r="R13" s="66"/>
       <c r="S13" s="44"/>
@@ -4367,20 +4379,20 @@
       <c r="BN13" s="76"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="169">
+      <c r="A14" s="167">
         <v>4</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="173" t="s">
+      <c r="C14" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="174"/>
-      <c r="E14" s="163" t="s">
+      <c r="D14" s="170"/>
+      <c r="E14" s="173" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="128"/>
+      <c r="F14" s="175"/>
       <c r="G14" s="50"/>
       <c r="H14" s="62"/>
       <c r="I14" s="62"/>
@@ -4445,12 +4457,12 @@
       <c r="BN14" s="72"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="158"/>
+      <c r="A15" s="168"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="175"/>
-      <c r="D15" s="176"/>
-      <c r="E15" s="145"/>
-      <c r="F15" s="129"/>
+      <c r="C15" s="171"/>
+      <c r="D15" s="172"/>
+      <c r="E15" s="174"/>
+      <c r="F15" s="176"/>
       <c r="G15" s="50"/>
       <c r="H15" s="62"/>
       <c r="I15" s="62"/>
@@ -4513,18 +4525,18 @@
       <c r="BN15" s="72"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="157">
+      <c r="A16" s="166">
         <v>5</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="165" t="s">
+      <c r="C16" s="149" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="141"/>
-      <c r="E16" s="162" t="s">
+      <c r="D16" s="150"/>
+      <c r="E16" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="146"/>
+      <c r="F16" s="187"/>
       <c r="G16" s="51"/>
       <c r="H16" s="63"/>
       <c r="I16" s="63"/>
@@ -4541,20 +4553,20 @@
       <c r="T16" s="19"/>
       <c r="U16" s="19"/>
       <c r="V16" s="30"/>
-      <c r="W16" s="103"/>
-      <c r="X16" s="103"/>
-      <c r="Y16" s="103"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="30"/>
       <c r="Z16" s="13"/>
       <c r="AA16" s="19"/>
       <c r="AB16" s="19"/>
-      <c r="AC16" s="7"/>
-      <c r="AD16" s="7"/>
-      <c r="AE16" s="7"/>
-      <c r="AF16" s="7"/>
+      <c r="AC16" s="30"/>
+      <c r="AD16" s="30"/>
+      <c r="AE16" s="30"/>
+      <c r="AF16" s="30"/>
       <c r="AG16" s="13"/>
       <c r="AH16" s="19"/>
-      <c r="AI16" s="7"/>
-      <c r="AJ16" s="73"/>
+      <c r="AI16" s="30"/>
+      <c r="AJ16" s="223"/>
       <c r="AK16" s="84"/>
       <c r="AL16" s="7"/>
       <c r="AM16" s="7"/>
@@ -4587,12 +4599,12 @@
       <c r="BN16" s="73"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="169"/>
+      <c r="A17" s="167"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="170"/>
-      <c r="D17" s="171"/>
-      <c r="E17" s="163"/>
-      <c r="F17" s="128"/>
+      <c r="C17" s="189"/>
+      <c r="D17" s="190"/>
+      <c r="E17" s="173"/>
+      <c r="F17" s="175"/>
       <c r="G17" s="52"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
@@ -4609,34 +4621,34 @@
       <c r="T17" s="26"/>
       <c r="U17" s="26"/>
       <c r="V17" s="32"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="24"/>
+      <c r="W17" s="32"/>
+      <c r="X17" s="32"/>
+      <c r="Y17" s="32"/>
       <c r="Z17" s="25"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="26"/>
-      <c r="AC17" s="24"/>
-      <c r="AD17" s="24"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="24"/>
+      <c r="AC17" s="32"/>
+      <c r="AD17" s="32"/>
+      <c r="AE17" s="32"/>
+      <c r="AF17" s="32"/>
       <c r="AG17" s="25"/>
       <c r="AH17" s="26"/>
-      <c r="AI17" s="24"/>
-      <c r="AJ17" s="74"/>
-      <c r="AK17" s="85"/>
-      <c r="AL17" s="24"/>
-      <c r="AM17" s="24"/>
+      <c r="AI17" s="32"/>
+      <c r="AJ17" s="225"/>
+      <c r="AK17" s="224"/>
+      <c r="AL17" s="32"/>
+      <c r="AM17" s="32"/>
       <c r="AN17" s="25"/>
       <c r="AO17" s="26"/>
-      <c r="AP17" s="24"/>
-      <c r="AQ17" s="24"/>
-      <c r="AR17" s="24"/>
-      <c r="AS17" s="24"/>
-      <c r="AT17" s="24"/>
+      <c r="AP17" s="32"/>
+      <c r="AQ17" s="32"/>
+      <c r="AR17" s="102"/>
+      <c r="AS17" s="32"/>
+      <c r="AT17" s="32"/>
       <c r="AU17" s="25"/>
       <c r="AV17" s="26"/>
       <c r="AW17" s="26"/>
-      <c r="AX17" s="24"/>
+      <c r="AX17" s="32"/>
       <c r="AY17" s="24"/>
       <c r="AZ17" s="24"/>
       <c r="BA17" s="24"/>
@@ -4655,20 +4667,20 @@
       <c r="BN17" s="74"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="164">
+      <c r="A18" s="191">
         <v>6</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="134" t="s">
+      <c r="C18" s="192" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="135"/>
-      <c r="E18" s="159" t="s">
+      <c r="D18" s="193"/>
+      <c r="E18" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="172"/>
+      <c r="F18" s="186"/>
       <c r="G18" s="38"/>
       <c r="H18" s="65"/>
       <c r="I18" s="65"/>
@@ -4685,9 +4697,9 @@
       <c r="T18" s="21"/>
       <c r="U18" s="21"/>
       <c r="V18" s="6"/>
-      <c r="W18" s="40"/>
-      <c r="X18" s="40"/>
-      <c r="Y18" s="40"/>
+      <c r="W18" s="98"/>
+      <c r="X18" s="98"/>
+      <c r="Y18" s="98"/>
       <c r="Z18" s="15"/>
       <c r="AA18" s="21"/>
       <c r="AB18" s="21"/>
@@ -4699,13 +4711,13 @@
       <c r="AH18" s="21"/>
       <c r="AI18" s="6"/>
       <c r="AJ18" s="75"/>
-      <c r="AK18" s="86"/>
-      <c r="AL18" s="6"/>
-      <c r="AM18" s="6"/>
+      <c r="AK18" s="222"/>
+      <c r="AL18" s="40"/>
+      <c r="AM18" s="40"/>
       <c r="AN18" s="15"/>
       <c r="AO18" s="21"/>
-      <c r="AP18" s="6"/>
-      <c r="AQ18" s="6"/>
+      <c r="AP18" s="40"/>
+      <c r="AQ18" s="40"/>
       <c r="AR18" s="6"/>
       <c r="AS18" s="6"/>
       <c r="AT18" s="6"/>
@@ -4731,12 +4743,12 @@
       <c r="BN18" s="75"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="164"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="36"/>
-      <c r="C19" s="142"/>
-      <c r="D19" s="143"/>
-      <c r="E19" s="145"/>
-      <c r="F19" s="129"/>
+      <c r="C19" s="160"/>
+      <c r="D19" s="161"/>
+      <c r="E19" s="174"/>
+      <c r="F19" s="176"/>
       <c r="G19" s="52"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
@@ -4760,21 +4772,21 @@
       <c r="AA19" s="26"/>
       <c r="AB19" s="26"/>
       <c r="AC19" s="24"/>
-      <c r="AD19" s="104"/>
-      <c r="AE19" s="104"/>
+      <c r="AD19" s="102"/>
+      <c r="AE19" s="102"/>
       <c r="AF19" s="24"/>
       <c r="AG19" s="25"/>
       <c r="AH19" s="26"/>
       <c r="AI19" s="24"/>
       <c r="AJ19" s="74"/>
-      <c r="AK19" s="85"/>
-      <c r="AL19" s="24"/>
-      <c r="AM19" s="24"/>
+      <c r="AK19" s="224"/>
+      <c r="AL19" s="32"/>
+      <c r="AM19" s="32"/>
       <c r="AN19" s="25"/>
       <c r="AO19" s="26"/>
-      <c r="AP19" s="24"/>
-      <c r="AQ19" s="24"/>
-      <c r="AR19" s="24"/>
+      <c r="AP19" s="102"/>
+      <c r="AQ19" s="102"/>
+      <c r="AR19" s="102"/>
       <c r="AS19" s="24"/>
       <c r="AT19" s="24"/>
       <c r="AU19" s="25"/>
@@ -4799,18 +4811,18 @@
       <c r="BN19" s="74"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="164">
+      <c r="A20" s="191">
         <v>7</v>
       </c>
       <c r="B20" s="36"/>
-      <c r="C20" s="165" t="s">
+      <c r="C20" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="141"/>
-      <c r="E20" s="144" t="s">
+      <c r="D20" s="150"/>
+      <c r="E20" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="146"/>
+      <c r="F20" s="187"/>
       <c r="G20" s="51"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -4833,10 +4845,10 @@
       <c r="Z20" s="13"/>
       <c r="AA20" s="19"/>
       <c r="AB20" s="19"/>
-      <c r="AC20" s="30"/>
-      <c r="AD20" s="30"/>
-      <c r="AE20" s="103"/>
-      <c r="AF20" s="7"/>
+      <c r="AC20" s="101"/>
+      <c r="AD20" s="101"/>
+      <c r="AE20" s="101"/>
+      <c r="AF20" s="101"/>
       <c r="AG20" s="13"/>
       <c r="AH20" s="19"/>
       <c r="AI20" s="7"/>
@@ -4846,9 +4858,9 @@
       <c r="AM20" s="7"/>
       <c r="AN20" s="13"/>
       <c r="AO20" s="19"/>
-      <c r="AP20" s="7"/>
-      <c r="AQ20" s="7"/>
-      <c r="AR20" s="7"/>
+      <c r="AP20" s="30"/>
+      <c r="AQ20" s="30"/>
+      <c r="AR20" s="101"/>
       <c r="AS20" s="7"/>
       <c r="AT20" s="7"/>
       <c r="AU20" s="13"/>
@@ -4873,12 +4885,12 @@
       <c r="BN20" s="73"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="164"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="36"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="145"/>
-      <c r="F21" s="129"/>
+      <c r="C21" s="160"/>
+      <c r="D21" s="161"/>
+      <c r="E21" s="174"/>
+      <c r="F21" s="176"/>
       <c r="G21" s="52"/>
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
@@ -4901,10 +4913,10 @@
       <c r="Z21" s="25"/>
       <c r="AA21" s="26"/>
       <c r="AB21" s="26"/>
-      <c r="AC21" s="24"/>
-      <c r="AD21" s="24"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
+      <c r="AC21" s="102"/>
+      <c r="AD21" s="102"/>
+      <c r="AE21" s="102"/>
+      <c r="AF21" s="102"/>
       <c r="AG21" s="25"/>
       <c r="AH21" s="26"/>
       <c r="AI21" s="24"/>
@@ -4914,10 +4926,10 @@
       <c r="AM21" s="24"/>
       <c r="AN21" s="25"/>
       <c r="AO21" s="26"/>
-      <c r="AP21" s="24"/>
-      <c r="AQ21" s="24"/>
-      <c r="AR21" s="24"/>
-      <c r="AS21" s="24"/>
+      <c r="AP21" s="102"/>
+      <c r="AQ21" s="102"/>
+      <c r="AR21" s="102"/>
+      <c r="AS21" s="102"/>
       <c r="AT21" s="24"/>
       <c r="AU21" s="25"/>
       <c r="AV21" s="26"/>
@@ -4941,18 +4953,18 @@
       <c r="BN21" s="74"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="164">
+      <c r="A22" s="191">
         <v>8</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="165" t="s">
+      <c r="C22" s="149" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="141"/>
-      <c r="E22" s="144" t="s">
+      <c r="D22" s="150"/>
+      <c r="E22" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="146"/>
+      <c r="F22" s="187"/>
       <c r="G22" s="52"/>
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
@@ -4975,10 +4987,10 @@
       <c r="Z22" s="25"/>
       <c r="AA22" s="26"/>
       <c r="AB22" s="26"/>
-      <c r="AC22" s="64"/>
-      <c r="AD22" s="64"/>
-      <c r="AE22" s="42"/>
-      <c r="AF22" s="42"/>
+      <c r="AC22" s="102"/>
+      <c r="AD22" s="102"/>
+      <c r="AE22" s="102"/>
+      <c r="AF22" s="102"/>
       <c r="AG22" s="25"/>
       <c r="AH22" s="26"/>
       <c r="AI22" s="64"/>
@@ -4991,12 +5003,12 @@
       <c r="AP22" s="64"/>
       <c r="AQ22" s="64"/>
       <c r="AR22" s="64"/>
-      <c r="AS22" s="64"/>
-      <c r="AT22" s="64"/>
+      <c r="AS22" s="42"/>
+      <c r="AT22" s="42"/>
       <c r="AU22" s="25"/>
       <c r="AV22" s="26"/>
       <c r="AW22" s="26"/>
-      <c r="AX22" s="64"/>
+      <c r="AX22" s="42"/>
       <c r="AY22" s="64"/>
       <c r="AZ22" s="64"/>
       <c r="BA22" s="64"/>
@@ -5015,12 +5027,12 @@
       <c r="BN22" s="77"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="164"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="37"/>
-      <c r="C23" s="166"/>
-      <c r="D23" s="167"/>
-      <c r="E23" s="168"/>
-      <c r="F23" s="147"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="185"/>
+      <c r="F23" s="188"/>
       <c r="G23" s="54"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -5083,20 +5095,20 @@
       <c r="BN23" s="78"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="157">
+      <c r="A24" s="166">
         <v>9</v>
       </c>
       <c r="B24" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="134" t="s">
+      <c r="C24" s="192" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="135"/>
-      <c r="E24" s="159" t="s">
+      <c r="D24" s="193"/>
+      <c r="E24" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="160"/>
+      <c r="F24" s="196"/>
       <c r="G24" s="38"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -5125,9 +5137,9 @@
       <c r="AF24" s="65"/>
       <c r="AG24" s="15"/>
       <c r="AH24" s="21"/>
-      <c r="AI24" s="40"/>
-      <c r="AJ24" s="99"/>
-      <c r="AK24" s="101"/>
+      <c r="AI24" s="98"/>
+      <c r="AJ24" s="221"/>
+      <c r="AK24" s="99"/>
       <c r="AL24" s="98"/>
       <c r="AM24" s="98"/>
       <c r="AN24" s="15"/>
@@ -5141,8 +5153,8 @@
       <c r="AV24" s="21"/>
       <c r="AW24" s="21"/>
       <c r="AX24" s="65"/>
-      <c r="AY24" s="65"/>
-      <c r="AZ24" s="65"/>
+      <c r="AY24" s="40"/>
+      <c r="AZ24" s="40"/>
       <c r="BA24" s="65"/>
       <c r="BB24" s="15"/>
       <c r="BC24" s="21"/>
@@ -5159,14 +5171,14 @@
       <c r="BN24" s="79"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="158"/>
+      <c r="A25" s="168"/>
       <c r="B25" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="142"/>
-      <c r="D25" s="143"/>
-      <c r="E25" s="145"/>
-      <c r="F25" s="161"/>
+      <c r="C25" s="160"/>
+      <c r="D25" s="161"/>
+      <c r="E25" s="174"/>
+      <c r="F25" s="197"/>
       <c r="G25" s="51"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -5197,9 +5209,9 @@
       <c r="AH25" s="19"/>
       <c r="AI25" s="63"/>
       <c r="AJ25" s="80"/>
-      <c r="AK25" s="102"/>
-      <c r="AL25" s="103"/>
-      <c r="AM25" s="103"/>
+      <c r="AK25" s="100"/>
+      <c r="AL25" s="101"/>
+      <c r="AM25" s="101"/>
       <c r="AN25" s="13"/>
       <c r="AO25" s="19"/>
       <c r="AP25" s="63"/>
@@ -5229,18 +5241,18 @@
       <c r="BN25" s="80"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="118">
+      <c r="A26" s="116">
         <v>10</v>
       </c>
       <c r="B26" s="36"/>
-      <c r="C26" s="140" t="s">
+      <c r="C26" s="198" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="141"/>
-      <c r="E26" s="162" t="s">
+      <c r="D26" s="150"/>
+      <c r="E26" s="184" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="146"/>
+      <c r="F26" s="187"/>
       <c r="G26" s="51"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -5272,8 +5284,8 @@
       <c r="AI26" s="63"/>
       <c r="AJ26" s="80"/>
       <c r="AK26" s="100"/>
-      <c r="AL26" s="30"/>
-      <c r="AM26" s="103"/>
+      <c r="AL26" s="101"/>
+      <c r="AM26" s="101"/>
       <c r="AN26" s="13"/>
       <c r="AO26" s="19"/>
       <c r="AP26" s="63"/>
@@ -5287,10 +5299,10 @@
       <c r="AX26" s="63"/>
       <c r="AY26" s="63"/>
       <c r="AZ26" s="63"/>
-      <c r="BA26" s="63"/>
+      <c r="BA26" s="30"/>
       <c r="BB26" s="13"/>
       <c r="BC26" s="19"/>
-      <c r="BD26" s="63"/>
+      <c r="BD26" s="30"/>
       <c r="BE26" s="63"/>
       <c r="BF26" s="63"/>
       <c r="BG26" s="63"/>
@@ -5303,12 +5315,12 @@
       <c r="BN26" s="80"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="121"/>
-      <c r="B27" s="105"/>
-      <c r="C27" s="142"/>
-      <c r="D27" s="143"/>
-      <c r="E27" s="163"/>
-      <c r="F27" s="128"/>
+      <c r="A27" s="119"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="160"/>
+      <c r="D27" s="161"/>
+      <c r="E27" s="173"/>
+      <c r="F27" s="175"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -5339,9 +5351,9 @@
       <c r="AH27" s="19"/>
       <c r="AI27" s="63"/>
       <c r="AJ27" s="80"/>
-      <c r="AK27" s="102"/>
-      <c r="AL27" s="103"/>
-      <c r="AM27" s="103"/>
+      <c r="AK27" s="100"/>
+      <c r="AL27" s="101"/>
+      <c r="AM27" s="101"/>
       <c r="AN27" s="13"/>
       <c r="AO27" s="19"/>
       <c r="AP27" s="63"/>
@@ -5371,16 +5383,16 @@
       <c r="BN27" s="80"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="120"/>
+      <c r="A28" s="118"/>
       <c r="B28" s="36"/>
-      <c r="C28" s="140" t="s">
+      <c r="C28" s="198" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="141"/>
-      <c r="E28" s="163" t="s">
+      <c r="D28" s="150"/>
+      <c r="E28" s="173" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="128"/>
+      <c r="F28" s="175"/>
       <c r="G28" s="51"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -5411,9 +5423,9 @@
       <c r="AH28" s="19"/>
       <c r="AI28" s="63"/>
       <c r="AJ28" s="80"/>
-      <c r="AK28" s="102"/>
-      <c r="AL28" s="30"/>
-      <c r="AM28" s="30"/>
+      <c r="AK28" s="100"/>
+      <c r="AL28" s="101"/>
+      <c r="AM28" s="101"/>
       <c r="AN28" s="13"/>
       <c r="AO28" s="19"/>
       <c r="AP28" s="63"/>
@@ -5431,8 +5443,8 @@
       <c r="BB28" s="13"/>
       <c r="BC28" s="19"/>
       <c r="BD28" s="63"/>
-      <c r="BE28" s="63"/>
-      <c r="BF28" s="63"/>
+      <c r="BE28" s="30"/>
+      <c r="BF28" s="30"/>
       <c r="BG28" s="63"/>
       <c r="BH28" s="63"/>
       <c r="BI28" s="13"/>
@@ -5443,12 +5455,12 @@
       <c r="BN28" s="80"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="120"/>
+      <c r="A29" s="118"/>
       <c r="B29" s="36"/>
-      <c r="C29" s="142"/>
-      <c r="D29" s="143"/>
-      <c r="E29" s="163"/>
-      <c r="F29" s="128"/>
+      <c r="C29" s="160"/>
+      <c r="D29" s="161"/>
+      <c r="E29" s="173"/>
+      <c r="F29" s="175"/>
       <c r="G29" s="51"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -5479,9 +5491,9 @@
       <c r="AH29" s="19"/>
       <c r="AI29" s="63"/>
       <c r="AJ29" s="80"/>
-      <c r="AK29" s="102"/>
-      <c r="AL29" s="103"/>
-      <c r="AM29" s="103"/>
+      <c r="AK29" s="100"/>
+      <c r="AL29" s="101"/>
+      <c r="AM29" s="101"/>
       <c r="AN29" s="13"/>
       <c r="AO29" s="19"/>
       <c r="AP29" s="63"/>
@@ -5511,16 +5523,16 @@
       <c r="BN29" s="80"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="120"/>
+      <c r="A30" s="118"/>
       <c r="B30" s="36"/>
-      <c r="C30" s="140" t="s">
+      <c r="C30" s="198" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="141"/>
-      <c r="E30" s="163" t="s">
+      <c r="D30" s="150"/>
+      <c r="E30" s="173" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="128"/>
+      <c r="F30" s="175"/>
       <c r="G30" s="51"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -5551,12 +5563,12 @@
       <c r="AH30" s="19"/>
       <c r="AI30" s="63"/>
       <c r="AJ30" s="80"/>
-      <c r="AK30" s="102"/>
-      <c r="AL30" s="103"/>
-      <c r="AM30" s="30"/>
+      <c r="AK30" s="100"/>
+      <c r="AL30" s="101"/>
+      <c r="AM30" s="101"/>
       <c r="AN30" s="13"/>
       <c r="AO30" s="19"/>
-      <c r="AP30" s="30"/>
+      <c r="AP30" s="101"/>
       <c r="AQ30" s="63"/>
       <c r="AR30" s="63"/>
       <c r="AS30" s="63"/>
@@ -5573,8 +5585,8 @@
       <c r="BD30" s="63"/>
       <c r="BE30" s="63"/>
       <c r="BF30" s="63"/>
-      <c r="BG30" s="63"/>
-      <c r="BH30" s="63"/>
+      <c r="BG30" s="30"/>
+      <c r="BH30" s="30"/>
       <c r="BI30" s="13"/>
       <c r="BJ30" s="19"/>
       <c r="BK30" s="63"/>
@@ -5583,12 +5595,12 @@
       <c r="BN30" s="80"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1">
-      <c r="A31" s="120"/>
+      <c r="A31" s="118"/>
       <c r="B31" s="36"/>
-      <c r="C31" s="142"/>
-      <c r="D31" s="143"/>
-      <c r="E31" s="163"/>
-      <c r="F31" s="128"/>
+      <c r="C31" s="160"/>
+      <c r="D31" s="161"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="175"/>
       <c r="G31" s="51"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -5619,9 +5631,9 @@
       <c r="AH31" s="19"/>
       <c r="AI31" s="63"/>
       <c r="AJ31" s="80"/>
-      <c r="AK31" s="102"/>
-      <c r="AL31" s="103"/>
-      <c r="AM31" s="103"/>
+      <c r="AK31" s="100"/>
+      <c r="AL31" s="101"/>
+      <c r="AM31" s="101"/>
       <c r="AN31" s="13"/>
       <c r="AO31" s="19"/>
       <c r="AP31" s="63"/>
@@ -5651,18 +5663,18 @@
       <c r="BN31" s="80"/>
     </row>
     <row r="32" spans="1:66" ht="12" customHeight="1">
-      <c r="A32" s="118">
+      <c r="A32" s="116">
         <v>11</v>
       </c>
       <c r="B32" s="36"/>
-      <c r="C32" s="140" t="s">
+      <c r="C32" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="141"/>
-      <c r="E32" s="163" t="s">
+      <c r="D32" s="150"/>
+      <c r="E32" s="173" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="128"/>
+      <c r="F32" s="175"/>
       <c r="G32" s="51"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -5693,16 +5705,16 @@
       <c r="AH32" s="19"/>
       <c r="AI32" s="63"/>
       <c r="AJ32" s="80"/>
-      <c r="AK32" s="102"/>
-      <c r="AL32" s="103"/>
-      <c r="AM32" s="103"/>
+      <c r="AK32" s="100"/>
+      <c r="AL32" s="101"/>
+      <c r="AM32" s="101"/>
       <c r="AN32" s="13"/>
       <c r="AO32" s="19"/>
-      <c r="AP32" s="30"/>
-      <c r="AQ32" s="30"/>
-      <c r="AR32" s="30"/>
-      <c r="AS32" s="103"/>
-      <c r="AT32" s="103"/>
+      <c r="AP32" s="101"/>
+      <c r="AQ32" s="101"/>
+      <c r="AR32" s="101"/>
+      <c r="AS32" s="101"/>
+      <c r="AT32" s="101"/>
       <c r="AU32" s="13"/>
       <c r="AV32" s="19"/>
       <c r="AW32" s="19"/>
@@ -5725,12 +5737,12 @@
       <c r="BN32" s="80"/>
     </row>
     <row r="33" spans="1:66" ht="12" customHeight="1">
-      <c r="A33" s="121"/>
-      <c r="B33" s="105"/>
-      <c r="C33" s="142"/>
-      <c r="D33" s="143"/>
-      <c r="E33" s="145"/>
-      <c r="F33" s="129"/>
+      <c r="A33" s="119"/>
+      <c r="B33" s="103"/>
+      <c r="C33" s="160"/>
+      <c r="D33" s="161"/>
+      <c r="E33" s="174"/>
+      <c r="F33" s="176"/>
       <c r="G33" s="51"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -5761,16 +5773,16 @@
       <c r="AH33" s="19"/>
       <c r="AI33" s="63"/>
       <c r="AJ33" s="80"/>
-      <c r="AK33" s="102"/>
-      <c r="AL33" s="103"/>
-      <c r="AM33" s="103"/>
+      <c r="AK33" s="100"/>
+      <c r="AL33" s="101"/>
+      <c r="AM33" s="101"/>
       <c r="AN33" s="13"/>
       <c r="AO33" s="19"/>
-      <c r="AP33" s="103"/>
-      <c r="AQ33" s="103"/>
-      <c r="AR33" s="103"/>
-      <c r="AS33" s="103"/>
-      <c r="AT33" s="103"/>
+      <c r="AP33" s="101"/>
+      <c r="AQ33" s="101"/>
+      <c r="AR33" s="101"/>
+      <c r="AS33" s="101"/>
+      <c r="AT33" s="101"/>
       <c r="AU33" s="13"/>
       <c r="AV33" s="19"/>
       <c r="AW33" s="19"/>
@@ -5793,16 +5805,16 @@
       <c r="BN33" s="80"/>
     </row>
     <row r="34" spans="1:66" ht="9.6" customHeight="1">
-      <c r="A34" s="121"/>
-      <c r="B34" s="105"/>
-      <c r="C34" s="140" t="s">
+      <c r="A34" s="119"/>
+      <c r="B34" s="103"/>
+      <c r="C34" s="198" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="141"/>
-      <c r="E34" s="144" t="s">
+      <c r="D34" s="150"/>
+      <c r="E34" s="195" t="s">
         <v>56</v>
       </c>
-      <c r="F34" s="146"/>
+      <c r="F34" s="187"/>
       <c r="G34" s="51"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -5833,16 +5845,16 @@
       <c r="AH34" s="19"/>
       <c r="AI34" s="63"/>
       <c r="AJ34" s="80"/>
-      <c r="AK34" s="102"/>
-      <c r="AL34" s="103"/>
-      <c r="AM34" s="103"/>
+      <c r="AK34" s="100"/>
+      <c r="AL34" s="101"/>
+      <c r="AM34" s="101"/>
       <c r="AN34" s="13"/>
       <c r="AO34" s="19"/>
-      <c r="AP34" s="103"/>
-      <c r="AQ34" s="103"/>
-      <c r="AR34" s="30"/>
-      <c r="AS34" s="30"/>
-      <c r="AT34" s="30"/>
+      <c r="AP34" s="101"/>
+      <c r="AQ34" s="101"/>
+      <c r="AR34" s="101"/>
+      <c r="AS34" s="101"/>
+      <c r="AT34" s="101"/>
       <c r="AU34" s="13"/>
       <c r="AV34" s="19"/>
       <c r="AW34" s="19"/>
@@ -5865,12 +5877,12 @@
       <c r="BN34" s="80"/>
     </row>
     <row r="35" spans="1:66">
-      <c r="A35" s="121"/>
-      <c r="B35" s="105"/>
-      <c r="C35" s="142"/>
-      <c r="D35" s="143"/>
-      <c r="E35" s="145"/>
-      <c r="F35" s="129"/>
+      <c r="A35" s="119"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="160"/>
+      <c r="D35" s="161"/>
+      <c r="E35" s="174"/>
+      <c r="F35" s="176"/>
       <c r="G35" s="51"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -5906,11 +5918,11 @@
       <c r="AM35" s="63"/>
       <c r="AN35" s="13"/>
       <c r="AO35" s="19"/>
-      <c r="AP35" s="103"/>
-      <c r="AQ35" s="103"/>
-      <c r="AR35" s="103"/>
-      <c r="AS35" s="103"/>
-      <c r="AT35" s="103"/>
+      <c r="AP35" s="101"/>
+      <c r="AQ35" s="101"/>
+      <c r="AR35" s="101"/>
+      <c r="AS35" s="101"/>
+      <c r="AT35" s="101"/>
       <c r="AU35" s="13"/>
       <c r="AV35" s="19"/>
       <c r="AW35" s="19"/>
@@ -5933,16 +5945,16 @@
       <c r="BN35" s="80"/>
     </row>
     <row r="36" spans="1:66">
-      <c r="A36" s="122"/>
-      <c r="B36" s="105"/>
-      <c r="C36" s="140" t="s">
+      <c r="A36" s="120"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="198" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="141"/>
-      <c r="E36" s="144" t="s">
+      <c r="D36" s="150"/>
+      <c r="E36" s="195" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="146"/>
+      <c r="F36" s="187"/>
       <c r="G36" s="52"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
@@ -5978,18 +5990,18 @@
       <c r="AM36" s="64"/>
       <c r="AN36" s="25"/>
       <c r="AO36" s="26"/>
-      <c r="AP36" s="104"/>
-      <c r="AQ36" s="104"/>
-      <c r="AR36" s="104"/>
-      <c r="AS36" s="104"/>
-      <c r="AT36" s="104"/>
+      <c r="AP36" s="102"/>
+      <c r="AQ36" s="102"/>
+      <c r="AR36" s="102"/>
+      <c r="AS36" s="102"/>
+      <c r="AT36" s="102"/>
       <c r="AU36" s="25"/>
       <c r="AV36" s="26"/>
       <c r="AW36" s="26"/>
-      <c r="AX36" s="42"/>
-      <c r="AY36" s="42"/>
-      <c r="AZ36" s="64"/>
-      <c r="BA36" s="64"/>
+      <c r="AX36" s="102"/>
+      <c r="AY36" s="102"/>
+      <c r="AZ36" s="102"/>
+      <c r="BA36" s="102"/>
       <c r="BB36" s="25"/>
       <c r="BC36" s="26"/>
       <c r="BD36" s="64"/>
@@ -6005,12 +6017,12 @@
       <c r="BN36" s="77"/>
     </row>
     <row r="37" spans="1:66">
-      <c r="A37" s="119"/>
+      <c r="A37" s="117"/>
       <c r="B37" s="37"/>
-      <c r="C37" s="142"/>
-      <c r="D37" s="143"/>
-      <c r="E37" s="145"/>
-      <c r="F37" s="147"/>
+      <c r="C37" s="160"/>
+      <c r="D37" s="161"/>
+      <c r="E37" s="174"/>
+      <c r="F37" s="188"/>
       <c r="G37" s="54"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
@@ -6054,10 +6066,10 @@
       <c r="AU37" s="17"/>
       <c r="AV37" s="23"/>
       <c r="AW37" s="23"/>
-      <c r="AX37" s="68"/>
-      <c r="AY37" s="68"/>
-      <c r="AZ37" s="68"/>
-      <c r="BA37" s="68"/>
+      <c r="AX37" s="220"/>
+      <c r="AY37" s="220"/>
+      <c r="AZ37" s="220"/>
+      <c r="BA37" s="220"/>
       <c r="BB37" s="17"/>
       <c r="BC37" s="23"/>
       <c r="BD37" s="68"/>
@@ -6073,20 +6085,20 @@
       <c r="BN37" s="78"/>
     </row>
     <row r="38" spans="1:66">
-      <c r="A38" s="130">
+      <c r="A38" s="147">
         <v>12</v>
       </c>
       <c r="B38" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C38" s="149" t="s">
+      <c r="C38" s="206" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="150"/>
-      <c r="E38" s="153" t="s">
+      <c r="D38" s="207"/>
+      <c r="E38" s="210" t="s">
         <v>56</v>
       </c>
-      <c r="F38" s="155"/>
+      <c r="F38" s="212"/>
       <c r="G38" s="38"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
@@ -6132,29 +6144,29 @@
       <c r="AW38" s="21"/>
       <c r="AX38" s="98"/>
       <c r="AY38" s="98"/>
-      <c r="AZ38" s="40"/>
-      <c r="BA38" s="40"/>
+      <c r="AZ38" s="98"/>
+      <c r="BA38" s="98"/>
       <c r="BB38" s="15"/>
       <c r="BC38" s="21"/>
-      <c r="BD38" s="40"/>
-      <c r="BE38" s="65"/>
-      <c r="BF38" s="65"/>
-      <c r="BG38" s="65"/>
-      <c r="BH38" s="65"/>
+      <c r="BD38" s="98"/>
+      <c r="BE38" s="98"/>
+      <c r="BF38" s="98"/>
+      <c r="BG38" s="98"/>
+      <c r="BH38" s="98"/>
       <c r="BI38" s="15"/>
       <c r="BJ38" s="21"/>
-      <c r="BK38" s="65"/>
-      <c r="BL38" s="65"/>
+      <c r="BK38" s="40"/>
+      <c r="BL38" s="40"/>
       <c r="BM38" s="65"/>
       <c r="BN38" s="79"/>
     </row>
     <row r="39" spans="1:66">
       <c r="A39" s="148"/>
       <c r="B39" s="34"/>
-      <c r="C39" s="151"/>
-      <c r="D39" s="152"/>
-      <c r="E39" s="154"/>
-      <c r="F39" s="156"/>
+      <c r="C39" s="208"/>
+      <c r="D39" s="209"/>
+      <c r="E39" s="211"/>
+      <c r="F39" s="213"/>
       <c r="G39" s="51"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
@@ -6204,33 +6216,33 @@
       <c r="BA39" s="63"/>
       <c r="BB39" s="13"/>
       <c r="BC39" s="19"/>
-      <c r="BD39" s="63"/>
-      <c r="BE39" s="63"/>
-      <c r="BF39" s="63"/>
-      <c r="BG39" s="63"/>
-      <c r="BH39" s="63"/>
+      <c r="BD39" s="101"/>
+      <c r="BE39" s="101"/>
+      <c r="BF39" s="101"/>
+      <c r="BG39" s="101"/>
+      <c r="BH39" s="101"/>
       <c r="BI39" s="13"/>
       <c r="BJ39" s="19"/>
       <c r="BK39" s="63"/>
       <c r="BL39" s="63"/>
-      <c r="BM39" s="63"/>
-      <c r="BN39" s="80"/>
+      <c r="BM39" s="30"/>
+      <c r="BN39" s="223"/>
     </row>
     <row r="40" spans="1:66">
-      <c r="A40" s="130">
+      <c r="A40" s="147">
         <v>14</v>
       </c>
-      <c r="B40" s="132" t="s">
+      <c r="B40" s="200" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="134" t="s">
+      <c r="C40" s="192" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="135"/>
-      <c r="E40" s="132" t="s">
+      <c r="D40" s="193"/>
+      <c r="E40" s="200" t="s">
         <v>56</v>
       </c>
-      <c r="F40" s="138"/>
+      <c r="F40" s="204"/>
       <c r="G40" s="38"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
@@ -6280,11 +6292,11 @@
       <c r="BA40" s="98"/>
       <c r="BB40" s="15"/>
       <c r="BC40" s="21"/>
-      <c r="BD40" s="65"/>
-      <c r="BE40" s="40"/>
-      <c r="BF40" s="40"/>
-      <c r="BG40" s="40"/>
-      <c r="BH40" s="40"/>
+      <c r="BD40" s="98"/>
+      <c r="BE40" s="98"/>
+      <c r="BF40" s="98"/>
+      <c r="BG40" s="98"/>
+      <c r="BH40" s="98"/>
       <c r="BI40" s="15"/>
       <c r="BJ40" s="21"/>
       <c r="BK40" s="65"/>
@@ -6293,12 +6305,12 @@
       <c r="BN40" s="79"/>
     </row>
     <row r="41" spans="1:66" ht="10.199999999999999" thickBot="1">
-      <c r="A41" s="131"/>
-      <c r="B41" s="133"/>
-      <c r="C41" s="136"/>
-      <c r="D41" s="137"/>
-      <c r="E41" s="133"/>
-      <c r="F41" s="139"/>
+      <c r="A41" s="199"/>
+      <c r="B41" s="201"/>
+      <c r="C41" s="202"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="201"/>
+      <c r="F41" s="205"/>
       <c r="G41" s="39"/>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -6378,51 +6390,21 @@
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="C24:D25"/>
     <mergeCell ref="E24:E25"/>
@@ -6439,21 +6421,51 @@
     <mergeCell ref="C30:D31"/>
     <mergeCell ref="C32:D33"/>
     <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
@@ -6489,54 +6501,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A1" s="198" t="s">
+      <c r="A1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="201" t="s">
+      <c r="B1" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="204" t="s">
+      <c r="C1" s="135" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="205"/>
-      <c r="E1" s="210" t="s">
+      <c r="D1" s="136"/>
+      <c r="E1" s="141" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="213" t="s">
+      <c r="F1" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="195"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="196"/>
-      <c r="M1" s="196"/>
-      <c r="N1" s="196"/>
-      <c r="O1" s="196"/>
-      <c r="P1" s="196"/>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="196"/>
-      <c r="T1" s="196"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="196"/>
-      <c r="W1" s="196"/>
-      <c r="X1" s="196"/>
-      <c r="Y1" s="196"/>
-      <c r="Z1" s="196"/>
-      <c r="AA1" s="196"/>
-      <c r="AB1" s="196"/>
-      <c r="AC1" s="196"/>
-      <c r="AD1" s="197"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="128"/>
     </row>
     <row r="2" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A2" s="199"/>
-      <c r="B2" s="202"/>
-      <c r="C2" s="206"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="211"/>
-      <c r="F2" s="214"/>
+      <c r="A2" s="130"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="145"/>
       <c r="G2" s="46">
         <v>22</v>
       </c>
@@ -6611,12 +6623,12 @@
       </c>
     </row>
     <row r="3" spans="1:30" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="200"/>
-      <c r="B3" s="203"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="209"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="215"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="146"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -6691,20 +6703,20 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A4" s="188">
+      <c r="A4" s="157">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="191" t="s">
+      <c r="D4" s="159"/>
+      <c r="E4" s="162" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="193"/>
+      <c r="F4" s="164"/>
       <c r="G4" s="49"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -6727,20 +6739,20 @@
       <c r="Z4" s="12"/>
       <c r="AA4" s="18"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="219" t="s">
+      <c r="AC4" s="217" t="s">
         <v>14</v>
       </c>
-      <c r="AD4" s="216" t="s">
+      <c r="AD4" s="214" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="13.5" customHeight="1">
       <c r="A5" s="148"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="192"/>
-      <c r="F5" s="194"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="163"/>
+      <c r="F5" s="165"/>
       <c r="G5" s="50"/>
       <c r="H5" s="31"/>
       <c r="I5" s="9"/>
@@ -6763,22 +6775,22 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="9"/>
-      <c r="AC5" s="220"/>
-      <c r="AD5" s="217"/>
+      <c r="AC5" s="218"/>
+      <c r="AD5" s="215"/>
     </row>
     <row r="6" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A6" s="130">
+      <c r="A6" s="147">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="165" t="s">
+      <c r="C6" s="149" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="141"/>
-      <c r="E6" s="184" t="s">
+      <c r="D6" s="150"/>
+      <c r="E6" s="153" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="186"/>
+      <c r="F6" s="155"/>
       <c r="G6" s="51"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -6801,16 +6813,16 @@
       <c r="Z6" s="13"/>
       <c r="AA6" s="19"/>
       <c r="AB6" s="7"/>
-      <c r="AC6" s="220"/>
-      <c r="AD6" s="217"/>
+      <c r="AC6" s="218"/>
+      <c r="AD6" s="215"/>
     </row>
     <row r="7" spans="1:30" ht="13.5" customHeight="1">
       <c r="A7" s="148"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="166"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="185"/>
-      <c r="F7" s="187"/>
+      <c r="C7" s="151"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="156"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="24"/>
@@ -6833,11 +6845,11 @@
       <c r="Z7" s="25"/>
       <c r="AA7" s="26"/>
       <c r="AB7" s="24"/>
-      <c r="AC7" s="220"/>
-      <c r="AD7" s="217"/>
+      <c r="AC7" s="218"/>
+      <c r="AD7" s="215"/>
     </row>
     <row r="8" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A8" s="157">
+      <c r="A8" s="166">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
@@ -6850,7 +6862,7 @@
       <c r="E8" s="183" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="172"/>
+      <c r="F8" s="186"/>
       <c r="G8" s="38"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -6873,16 +6885,16 @@
       <c r="Z8" s="15"/>
       <c r="AA8" s="21"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="220"/>
-      <c r="AD8" s="217"/>
+      <c r="AC8" s="218"/>
+      <c r="AD8" s="215"/>
     </row>
     <row r="9" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A9" s="158"/>
+      <c r="A9" s="168"/>
       <c r="B9" s="37"/>
       <c r="C9" s="181"/>
       <c r="D9" s="182"/>
-      <c r="E9" s="168"/>
-      <c r="F9" s="147"/>
+      <c r="E9" s="185"/>
+      <c r="F9" s="188"/>
       <c r="G9" s="53"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
@@ -6905,24 +6917,24 @@
       <c r="Z9" s="44"/>
       <c r="AA9" s="45"/>
       <c r="AB9" s="43"/>
-      <c r="AC9" s="220"/>
-      <c r="AD9" s="217"/>
+      <c r="AC9" s="218"/>
+      <c r="AD9" s="215"/>
     </row>
     <row r="10" spans="1:30" ht="12" customHeight="1">
-      <c r="A10" s="169">
+      <c r="A10" s="167">
         <v>4</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="173" t="s">
+      <c r="C10" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="174"/>
-      <c r="E10" s="163" t="s">
+      <c r="D10" s="170"/>
+      <c r="E10" s="173" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="128"/>
+      <c r="F10" s="175"/>
       <c r="G10" s="50"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -6945,16 +6957,16 @@
       <c r="Z10" s="16"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="220"/>
-      <c r="AD10" s="217"/>
+      <c r="AC10" s="218"/>
+      <c r="AD10" s="215"/>
     </row>
     <row r="11" spans="1:30" ht="12" customHeight="1">
-      <c r="A11" s="158"/>
+      <c r="A11" s="168"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="175"/>
-      <c r="D11" s="176"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="129"/>
+      <c r="C11" s="171"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="174"/>
+      <c r="F11" s="176"/>
       <c r="G11" s="50"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -6977,22 +6989,22 @@
       <c r="Z11" s="16"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="220"/>
-      <c r="AD11" s="217"/>
+      <c r="AC11" s="218"/>
+      <c r="AD11" s="215"/>
     </row>
     <row r="12" spans="1:30" ht="12" customHeight="1">
-      <c r="A12" s="157">
+      <c r="A12" s="166">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="165" t="s">
+      <c r="C12" s="149" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="141"/>
-      <c r="E12" s="162" t="s">
+      <c r="D12" s="150"/>
+      <c r="E12" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="146"/>
+      <c r="F12" s="187"/>
       <c r="G12" s="51"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -7015,16 +7027,16 @@
       <c r="Z12" s="13"/>
       <c r="AA12" s="19"/>
       <c r="AB12" s="7"/>
-      <c r="AC12" s="220"/>
-      <c r="AD12" s="217"/>
+      <c r="AC12" s="218"/>
+      <c r="AD12" s="215"/>
     </row>
     <row r="13" spans="1:30" ht="12" customHeight="1">
-      <c r="A13" s="169"/>
+      <c r="A13" s="167"/>
       <c r="B13" s="36"/>
-      <c r="C13" s="170"/>
-      <c r="D13" s="171"/>
-      <c r="E13" s="163"/>
-      <c r="F13" s="128"/>
+      <c r="C13" s="189"/>
+      <c r="D13" s="190"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="175"/>
       <c r="G13" s="52"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
@@ -7047,24 +7059,24 @@
       <c r="Z13" s="25"/>
       <c r="AA13" s="26"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="220"/>
-      <c r="AD13" s="217"/>
+      <c r="AC13" s="218"/>
+      <c r="AD13" s="215"/>
     </row>
     <row r="14" spans="1:30" ht="12" customHeight="1">
-      <c r="A14" s="164">
+      <c r="A14" s="191">
         <v>6</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="134" t="s">
+      <c r="C14" s="192" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="135"/>
-      <c r="E14" s="159" t="s">
+      <c r="D14" s="193"/>
+      <c r="E14" s="194" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="172"/>
+      <c r="F14" s="186"/>
       <c r="G14" s="38"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -7087,16 +7099,16 @@
       <c r="Z14" s="15"/>
       <c r="AA14" s="21"/>
       <c r="AB14" s="6"/>
-      <c r="AC14" s="220"/>
-      <c r="AD14" s="217"/>
+      <c r="AC14" s="218"/>
+      <c r="AD14" s="215"/>
     </row>
     <row r="15" spans="1:30" ht="12" customHeight="1">
-      <c r="A15" s="164"/>
+      <c r="A15" s="191"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="142"/>
-      <c r="D15" s="143"/>
-      <c r="E15" s="145"/>
-      <c r="F15" s="129"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="161"/>
+      <c r="E15" s="174"/>
+      <c r="F15" s="176"/>
       <c r="G15" s="52"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
@@ -7119,22 +7131,22 @@
       <c r="Z15" s="25"/>
       <c r="AA15" s="26"/>
       <c r="AB15" s="24"/>
-      <c r="AC15" s="220"/>
-      <c r="AD15" s="217"/>
+      <c r="AC15" s="218"/>
+      <c r="AD15" s="215"/>
     </row>
     <row r="16" spans="1:30" ht="12" customHeight="1">
-      <c r="A16" s="164">
+      <c r="A16" s="191">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="165" t="s">
+      <c r="C16" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="141"/>
-      <c r="E16" s="144" t="s">
+      <c r="D16" s="150"/>
+      <c r="E16" s="195" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="146"/>
+      <c r="F16" s="187"/>
       <c r="G16" s="51"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -7157,16 +7169,16 @@
       <c r="Z16" s="13"/>
       <c r="AA16" s="19"/>
       <c r="AB16" s="7"/>
-      <c r="AC16" s="220"/>
-      <c r="AD16" s="217"/>
+      <c r="AC16" s="218"/>
+      <c r="AD16" s="215"/>
     </row>
     <row r="17" spans="1:30" ht="12" customHeight="1">
-      <c r="A17" s="164"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="142"/>
-      <c r="D17" s="143"/>
-      <c r="E17" s="145"/>
-      <c r="F17" s="129"/>
+      <c r="C17" s="160"/>
+      <c r="D17" s="161"/>
+      <c r="E17" s="174"/>
+      <c r="F17" s="176"/>
       <c r="G17" s="52"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -7189,22 +7201,22 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="220"/>
-      <c r="AD17" s="217"/>
+      <c r="AC17" s="218"/>
+      <c r="AD17" s="215"/>
     </row>
     <row r="18" spans="1:30" ht="12" customHeight="1">
-      <c r="A18" s="164">
+      <c r="A18" s="191">
         <v>8</v>
       </c>
       <c r="B18" s="36"/>
-      <c r="C18" s="165" t="s">
+      <c r="C18" s="149" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="141"/>
-      <c r="E18" s="144" t="s">
+      <c r="D18" s="150"/>
+      <c r="E18" s="195" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="146"/>
+      <c r="F18" s="187"/>
       <c r="G18" s="52"/>
       <c r="H18" s="24"/>
       <c r="I18" s="24"/>
@@ -7227,16 +7239,16 @@
       <c r="Z18" s="25"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="220"/>
-      <c r="AD18" s="217"/>
+      <c r="AC18" s="218"/>
+      <c r="AD18" s="215"/>
     </row>
     <row r="19" spans="1:30" ht="12" customHeight="1">
-      <c r="A19" s="164"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="37"/>
-      <c r="C19" s="166"/>
-      <c r="D19" s="167"/>
-      <c r="E19" s="168"/>
-      <c r="F19" s="147"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="152"/>
+      <c r="E19" s="185"/>
+      <c r="F19" s="188"/>
       <c r="G19" s="54"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -7259,24 +7271,24 @@
       <c r="Z19" s="17"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="220"/>
-      <c r="AD19" s="217"/>
+      <c r="AC19" s="218"/>
+      <c r="AD19" s="215"/>
     </row>
     <row r="20" spans="1:30" ht="12" customHeight="1">
-      <c r="A20" s="157">
+      <c r="A20" s="166">
         <v>9</v>
       </c>
       <c r="B20" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="134" t="s">
+      <c r="C20" s="192" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="135"/>
-      <c r="E20" s="159" t="s">
+      <c r="D20" s="193"/>
+      <c r="E20" s="194" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="172"/>
+      <c r="F20" s="186"/>
       <c r="G20" s="38"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -7299,18 +7311,18 @@
       <c r="Z20" s="15"/>
       <c r="AA20" s="21"/>
       <c r="AB20" s="6"/>
-      <c r="AC20" s="220"/>
-      <c r="AD20" s="217"/>
+      <c r="AC20" s="218"/>
+      <c r="AD20" s="215"/>
     </row>
     <row r="21" spans="1:30" ht="12" customHeight="1">
-      <c r="A21" s="158"/>
+      <c r="A21" s="168"/>
       <c r="B21" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="142"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="145"/>
-      <c r="F21" s="129"/>
+      <c r="C21" s="160"/>
+      <c r="D21" s="161"/>
+      <c r="E21" s="174"/>
+      <c r="F21" s="176"/>
       <c r="G21" s="51"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -7333,22 +7345,22 @@
       <c r="Z21" s="13"/>
       <c r="AA21" s="19"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="220"/>
-      <c r="AD21" s="217"/>
+      <c r="AC21" s="218"/>
+      <c r="AD21" s="215"/>
     </row>
     <row r="22" spans="1:30" ht="12" customHeight="1">
-      <c r="A22" s="157">
+      <c r="A22" s="166">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="140" t="s">
+      <c r="C22" s="198" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="141"/>
-      <c r="E22" s="144" t="s">
+      <c r="D22" s="150"/>
+      <c r="E22" s="195" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="146"/>
+      <c r="F22" s="187"/>
       <c r="G22" s="51"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -7371,16 +7383,16 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="19"/>
       <c r="AB22" s="7"/>
-      <c r="AC22" s="220"/>
-      <c r="AD22" s="217"/>
+      <c r="AC22" s="218"/>
+      <c r="AD22" s="215"/>
     </row>
     <row r="23" spans="1:30" ht="12" customHeight="1">
-      <c r="A23" s="158"/>
+      <c r="A23" s="168"/>
       <c r="B23" s="36"/>
-      <c r="C23" s="142"/>
-      <c r="D23" s="143"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="129"/>
+      <c r="C23" s="160"/>
+      <c r="D23" s="161"/>
+      <c r="E23" s="174"/>
+      <c r="F23" s="176"/>
       <c r="G23" s="51"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -7403,22 +7415,22 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="19"/>
       <c r="AB23" s="7"/>
-      <c r="AC23" s="220"/>
-      <c r="AD23" s="217"/>
+      <c r="AC23" s="218"/>
+      <c r="AD23" s="215"/>
     </row>
     <row r="24" spans="1:30" ht="12" customHeight="1">
-      <c r="A24" s="157">
+      <c r="A24" s="166">
         <v>11</v>
       </c>
       <c r="B24" s="36"/>
-      <c r="C24" s="140" t="s">
+      <c r="C24" s="198" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="141"/>
-      <c r="E24" s="144" t="s">
+      <c r="D24" s="150"/>
+      <c r="E24" s="195" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="146"/>
+      <c r="F24" s="187"/>
       <c r="G24" s="52"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -7441,16 +7453,16 @@
       <c r="Z24" s="25"/>
       <c r="AA24" s="26"/>
       <c r="AB24" s="24"/>
-      <c r="AC24" s="220"/>
-      <c r="AD24" s="217"/>
+      <c r="AC24" s="218"/>
+      <c r="AD24" s="215"/>
     </row>
     <row r="25" spans="1:30" ht="12" customHeight="1">
-      <c r="A25" s="158"/>
+      <c r="A25" s="168"/>
       <c r="B25" s="37"/>
-      <c r="C25" s="142"/>
-      <c r="D25" s="143"/>
-      <c r="E25" s="145"/>
-      <c r="F25" s="147"/>
+      <c r="C25" s="160"/>
+      <c r="D25" s="161"/>
+      <c r="E25" s="174"/>
+      <c r="F25" s="188"/>
       <c r="G25" s="54"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -7473,24 +7485,24 @@
       <c r="Z25" s="17"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="220"/>
-      <c r="AD25" s="217"/>
+      <c r="AC25" s="218"/>
+      <c r="AD25" s="215"/>
     </row>
     <row r="26" spans="1:30" ht="12" customHeight="1">
-      <c r="A26" s="130">
+      <c r="A26" s="147">
         <v>12</v>
       </c>
       <c r="B26" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="149" t="s">
+      <c r="C26" s="206" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="150"/>
-      <c r="E26" s="153" t="s">
+      <c r="D26" s="207"/>
+      <c r="E26" s="210" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="155"/>
+      <c r="F26" s="212"/>
       <c r="G26" s="38"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -7513,16 +7525,16 @@
       <c r="Z26" s="15"/>
       <c r="AA26" s="21"/>
       <c r="AB26" s="6"/>
-      <c r="AC26" s="220"/>
-      <c r="AD26" s="217"/>
+      <c r="AC26" s="218"/>
+      <c r="AD26" s="215"/>
     </row>
     <row r="27" spans="1:30" ht="12" customHeight="1">
       <c r="A27" s="148"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="154"/>
-      <c r="F27" s="156"/>
+      <c r="C27" s="208"/>
+      <c r="D27" s="209"/>
+      <c r="E27" s="211"/>
+      <c r="F27" s="213"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -7545,24 +7557,24 @@
       <c r="Z27" s="13"/>
       <c r="AA27" s="19"/>
       <c r="AB27" s="7"/>
-      <c r="AC27" s="220"/>
-      <c r="AD27" s="217"/>
+      <c r="AC27" s="218"/>
+      <c r="AD27" s="215"/>
     </row>
     <row r="28" spans="1:30" ht="12" customHeight="1">
-      <c r="A28" s="130">
+      <c r="A28" s="147">
         <v>14</v>
       </c>
-      <c r="B28" s="132" t="s">
+      <c r="B28" s="200" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="134" t="s">
+      <c r="C28" s="192" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="135"/>
-      <c r="E28" s="132" t="s">
+      <c r="D28" s="193"/>
+      <c r="E28" s="200" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="138"/>
+      <c r="F28" s="204"/>
       <c r="G28" s="38"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -7585,16 +7597,16 @@
       <c r="Z28" s="15"/>
       <c r="AA28" s="21"/>
       <c r="AB28" s="40"/>
-      <c r="AC28" s="220"/>
-      <c r="AD28" s="217"/>
+      <c r="AC28" s="218"/>
+      <c r="AD28" s="215"/>
     </row>
     <row r="29" spans="1:30" ht="12" customHeight="1" thickBot="1">
-      <c r="A29" s="131"/>
-      <c r="B29" s="133"/>
-      <c r="C29" s="136"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="139"/>
+      <c r="A29" s="199"/>
+      <c r="B29" s="201"/>
+      <c r="C29" s="202"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="201"/>
+      <c r="F29" s="205"/>
       <c r="G29" s="39"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -7617,8 +7629,8 @@
       <c r="Z29" s="14"/>
       <c r="AA29" s="20"/>
       <c r="AB29" s="11"/>
-      <c r="AC29" s="221"/>
-      <c r="AD29" s="218"/>
+      <c r="AC29" s="219"/>
+      <c r="AD29" s="216"/>
     </row>
     <row r="30" spans="1:30">
       <c r="Z30" s="5"/>
@@ -7638,45 +7650,12 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G1:AD1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
     <mergeCell ref="AD4:AD29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C6:D7"/>
@@ -7693,12 +7672,45 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="C10:D11"/>
-    <mergeCell ref="G1:AD1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/システム開発演習/000-要件定義/003-WBS.xlsx
+++ b/システム開発演習/000-要件定義/003-WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\システム開発演習\000-要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA15A06D-9CDE-4CEF-912F-D03F3F6B9A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EDB04E-8F63-4119-BA03-A67551D9F8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1762,7 +1762,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2133,6 +2133,225 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2196,207 +2415,6 @@
     <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2415,22 +2433,10 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3150,94 +3156,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="132" t="s">
+      <c r="B1" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="135" t="s">
+      <c r="C1" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="136"/>
-      <c r="E1" s="141" t="s">
+      <c r="D1" s="209"/>
+      <c r="E1" s="214" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="144" t="s">
+      <c r="F1" s="217" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="126">
+      <c r="G1" s="199">
         <v>45536</v>
       </c>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="127"/>
-      <c r="S1" s="127"/>
-      <c r="T1" s="127"/>
-      <c r="U1" s="127"/>
-      <c r="V1" s="127"/>
-      <c r="W1" s="127"/>
-      <c r="X1" s="127"/>
-      <c r="Y1" s="127"/>
-      <c r="Z1" s="127"/>
-      <c r="AA1" s="127"/>
-      <c r="AB1" s="127"/>
-      <c r="AC1" s="127"/>
-      <c r="AD1" s="127"/>
-      <c r="AE1" s="127"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="127"/>
-      <c r="AH1" s="127"/>
-      <c r="AI1" s="127"/>
-      <c r="AJ1" s="128"/>
-      <c r="AK1" s="126">
+      <c r="H1" s="200"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="200"/>
+      <c r="K1" s="200"/>
+      <c r="L1" s="200"/>
+      <c r="M1" s="200"/>
+      <c r="N1" s="200"/>
+      <c r="O1" s="200"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="200"/>
+      <c r="AA1" s="200"/>
+      <c r="AB1" s="200"/>
+      <c r="AC1" s="200"/>
+      <c r="AD1" s="200"/>
+      <c r="AE1" s="200"/>
+      <c r="AF1" s="200"/>
+      <c r="AG1" s="200"/>
+      <c r="AH1" s="200"/>
+      <c r="AI1" s="200"/>
+      <c r="AJ1" s="201"/>
+      <c r="AK1" s="199">
         <v>45566</v>
       </c>
-      <c r="AL1" s="127"/>
-      <c r="AM1" s="127"/>
-      <c r="AN1" s="127"/>
-      <c r="AO1" s="127"/>
-      <c r="AP1" s="127"/>
-      <c r="AQ1" s="127"/>
-      <c r="AR1" s="127"/>
-      <c r="AS1" s="127"/>
-      <c r="AT1" s="127"/>
-      <c r="AU1" s="127"/>
-      <c r="AV1" s="127"/>
-      <c r="AW1" s="127"/>
-      <c r="AX1" s="127"/>
-      <c r="AY1" s="127"/>
-      <c r="AZ1" s="127"/>
-      <c r="BA1" s="127"/>
-      <c r="BB1" s="127"/>
-      <c r="BC1" s="127"/>
-      <c r="BD1" s="127"/>
-      <c r="BE1" s="127"/>
-      <c r="BF1" s="127"/>
-      <c r="BG1" s="127"/>
-      <c r="BH1" s="127"/>
-      <c r="BI1" s="127"/>
-      <c r="BJ1" s="127"/>
-      <c r="BK1" s="127"/>
-      <c r="BL1" s="127"/>
-      <c r="BM1" s="127"/>
-      <c r="BN1" s="128"/>
+      <c r="AL1" s="200"/>
+      <c r="AM1" s="200"/>
+      <c r="AN1" s="200"/>
+      <c r="AO1" s="200"/>
+      <c r="AP1" s="200"/>
+      <c r="AQ1" s="200"/>
+      <c r="AR1" s="200"/>
+      <c r="AS1" s="200"/>
+      <c r="AT1" s="200"/>
+      <c r="AU1" s="200"/>
+      <c r="AV1" s="200"/>
+      <c r="AW1" s="200"/>
+      <c r="AX1" s="200"/>
+      <c r="AY1" s="200"/>
+      <c r="AZ1" s="200"/>
+      <c r="BA1" s="200"/>
+      <c r="BB1" s="200"/>
+      <c r="BC1" s="200"/>
+      <c r="BD1" s="200"/>
+      <c r="BE1" s="200"/>
+      <c r="BF1" s="200"/>
+      <c r="BG1" s="200"/>
+      <c r="BH1" s="200"/>
+      <c r="BI1" s="200"/>
+      <c r="BJ1" s="200"/>
+      <c r="BK1" s="200"/>
+      <c r="BL1" s="200"/>
+      <c r="BM1" s="200"/>
+      <c r="BN1" s="201"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="130"/>
-      <c r="B2" s="133"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="145"/>
+      <c r="A2" s="203"/>
+      <c r="B2" s="206"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="211"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="218"/>
       <c r="G2" s="46">
         <v>45537</v>
       </c>
@@ -3479,12 +3485,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="146"/>
+      <c r="A3" s="204"/>
+      <c r="B3" s="207"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="213"/>
+      <c r="E3" s="216"/>
+      <c r="F3" s="219"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -3667,20 +3673,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="157">
+      <c r="A4" s="192">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="158" t="s">
+      <c r="C4" s="193" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="159"/>
-      <c r="E4" s="162" t="s">
+      <c r="D4" s="194"/>
+      <c r="E4" s="195" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="164"/>
+      <c r="F4" s="197"/>
       <c r="G4" s="95"/>
       <c r="H4" s="29"/>
       <c r="I4" s="125"/>
@@ -3743,12 +3749,12 @@
       <c r="BN4" s="71"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="148"/>
+      <c r="A5" s="152"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="160"/>
-      <c r="D5" s="161"/>
-      <c r="E5" s="163"/>
-      <c r="F5" s="165"/>
+      <c r="C5" s="146"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="196"/>
+      <c r="F5" s="198"/>
       <c r="G5" s="96"/>
       <c r="H5" s="31"/>
       <c r="I5" s="97"/>
@@ -3811,18 +3817,18 @@
       <c r="BN5" s="72"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="147">
+      <c r="A6" s="134">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="149" t="s">
+      <c r="C6" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="150"/>
-      <c r="E6" s="153" t="s">
+      <c r="D6" s="145"/>
+      <c r="E6" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="155"/>
+      <c r="F6" s="190"/>
       <c r="G6" s="51"/>
       <c r="H6" s="63"/>
       <c r="I6" s="30"/>
@@ -3885,12 +3891,12 @@
       <c r="BN6" s="73"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="148"/>
+      <c r="A7" s="152"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="154"/>
-      <c r="F7" s="156"/>
+      <c r="C7" s="170"/>
+      <c r="D7" s="171"/>
+      <c r="E7" s="189"/>
+      <c r="F7" s="191"/>
       <c r="G7" s="52"/>
       <c r="H7" s="64"/>
       <c r="I7" s="32"/>
@@ -3953,20 +3959,20 @@
       <c r="BN7" s="74"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="166">
+      <c r="A8" s="161">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="177" t="s">
+      <c r="C8" s="181" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="178"/>
-      <c r="E8" s="183" t="s">
+      <c r="D8" s="182"/>
+      <c r="E8" s="187" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="186"/>
+      <c r="F8" s="176"/>
       <c r="G8" s="38"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65"/>
@@ -4029,12 +4035,12 @@
       <c r="BN8" s="75"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="167"/>
+      <c r="A9" s="173"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="169"/>
-      <c r="D9" s="170"/>
-      <c r="E9" s="173"/>
-      <c r="F9" s="175"/>
+      <c r="C9" s="177"/>
+      <c r="D9" s="178"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="132"/>
       <c r="G9" s="104"/>
       <c r="H9" s="105"/>
       <c r="I9" s="105"/>
@@ -4097,16 +4103,16 @@
       <c r="BN9" s="110"/>
     </row>
     <row r="10" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A10" s="167"/>
+      <c r="A10" s="173"/>
       <c r="B10" s="36"/>
-      <c r="C10" s="179" t="s">
+      <c r="C10" s="183" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="180"/>
-      <c r="E10" s="184" t="s">
+      <c r="D10" s="184"/>
+      <c r="E10" s="166" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="187"/>
+      <c r="F10" s="150"/>
       <c r="G10" s="115"/>
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
@@ -4169,12 +4175,12 @@
       <c r="BN10" s="73"/>
     </row>
     <row r="11" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A11" s="167"/>
+      <c r="A11" s="173"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="171"/>
-      <c r="D11" s="172"/>
-      <c r="E11" s="174"/>
-      <c r="F11" s="176"/>
+      <c r="C11" s="179"/>
+      <c r="D11" s="180"/>
+      <c r="E11" s="149"/>
+      <c r="F11" s="133"/>
       <c r="G11" s="104"/>
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
@@ -4237,16 +4243,16 @@
       <c r="BN11" s="110"/>
     </row>
     <row r="12" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A12" s="167"/>
+      <c r="A12" s="173"/>
       <c r="B12" s="36"/>
-      <c r="C12" s="169" t="s">
+      <c r="C12" s="177" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="170"/>
-      <c r="E12" s="173" t="s">
+      <c r="D12" s="178"/>
+      <c r="E12" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="175"/>
+      <c r="F12" s="132"/>
       <c r="G12" s="115"/>
       <c r="H12" s="62"/>
       <c r="I12" s="62"/>
@@ -4311,12 +4317,12 @@
       <c r="BN12" s="73"/>
     </row>
     <row r="13" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A13" s="168"/>
+      <c r="A13" s="162"/>
       <c r="B13" s="37"/>
-      <c r="C13" s="181"/>
-      <c r="D13" s="182"/>
-      <c r="E13" s="185"/>
-      <c r="F13" s="188"/>
+      <c r="C13" s="185"/>
+      <c r="D13" s="186"/>
+      <c r="E13" s="172"/>
+      <c r="F13" s="151"/>
       <c r="G13" s="53"/>
       <c r="H13" s="66"/>
       <c r="I13" s="66"/>
@@ -4379,20 +4385,20 @@
       <c r="BN13" s="76"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="167">
+      <c r="A14" s="173">
         <v>4</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="169" t="s">
+      <c r="C14" s="177" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="170"/>
-      <c r="E14" s="173" t="s">
+      <c r="D14" s="178"/>
+      <c r="E14" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="175"/>
+      <c r="F14" s="132"/>
       <c r="G14" s="50"/>
       <c r="H14" s="62"/>
       <c r="I14" s="62"/>
@@ -4457,12 +4463,12 @@
       <c r="BN14" s="72"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="168"/>
+      <c r="A15" s="162"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="171"/>
-      <c r="D15" s="172"/>
-      <c r="E15" s="174"/>
-      <c r="F15" s="176"/>
+      <c r="C15" s="179"/>
+      <c r="D15" s="180"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="133"/>
       <c r="G15" s="50"/>
       <c r="H15" s="62"/>
       <c r="I15" s="62"/>
@@ -4525,18 +4531,18 @@
       <c r="BN15" s="72"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="166">
+      <c r="A16" s="161">
         <v>5</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="149" t="s">
+      <c r="C16" s="169" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="150"/>
-      <c r="E16" s="184" t="s">
+      <c r="D16" s="145"/>
+      <c r="E16" s="166" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="187"/>
+      <c r="F16" s="150"/>
       <c r="G16" s="51"/>
       <c r="H16" s="63"/>
       <c r="I16" s="63"/>
@@ -4566,7 +4572,7 @@
       <c r="AG16" s="13"/>
       <c r="AH16" s="19"/>
       <c r="AI16" s="30"/>
-      <c r="AJ16" s="223"/>
+      <c r="AJ16" s="129"/>
       <c r="AK16" s="84"/>
       <c r="AL16" s="7"/>
       <c r="AM16" s="7"/>
@@ -4599,12 +4605,12 @@
       <c r="BN16" s="73"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="167"/>
+      <c r="A17" s="173"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="189"/>
-      <c r="D17" s="190"/>
-      <c r="E17" s="173"/>
-      <c r="F17" s="175"/>
+      <c r="C17" s="174"/>
+      <c r="D17" s="175"/>
+      <c r="E17" s="167"/>
+      <c r="F17" s="132"/>
       <c r="G17" s="52"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
@@ -4634,8 +4640,8 @@
       <c r="AG17" s="25"/>
       <c r="AH17" s="26"/>
       <c r="AI17" s="32"/>
-      <c r="AJ17" s="225"/>
-      <c r="AK17" s="224"/>
+      <c r="AJ17" s="131"/>
+      <c r="AK17" s="130"/>
       <c r="AL17" s="32"/>
       <c r="AM17" s="32"/>
       <c r="AN17" s="25"/>
@@ -4667,20 +4673,20 @@
       <c r="BN17" s="74"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="191">
+      <c r="A18" s="168">
         <v>6</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="192" t="s">
+      <c r="C18" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="193"/>
-      <c r="E18" s="194" t="s">
+      <c r="D18" s="139"/>
+      <c r="E18" s="163" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="186"/>
+      <c r="F18" s="176"/>
       <c r="G18" s="38"/>
       <c r="H18" s="65"/>
       <c r="I18" s="65"/>
@@ -4711,7 +4717,7 @@
       <c r="AH18" s="21"/>
       <c r="AI18" s="6"/>
       <c r="AJ18" s="75"/>
-      <c r="AK18" s="222"/>
+      <c r="AK18" s="128"/>
       <c r="AL18" s="40"/>
       <c r="AM18" s="40"/>
       <c r="AN18" s="15"/>
@@ -4743,12 +4749,12 @@
       <c r="BN18" s="75"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="191"/>
+      <c r="A19" s="168"/>
       <c r="B19" s="36"/>
-      <c r="C19" s="160"/>
-      <c r="D19" s="161"/>
-      <c r="E19" s="174"/>
-      <c r="F19" s="176"/>
+      <c r="C19" s="146"/>
+      <c r="D19" s="147"/>
+      <c r="E19" s="149"/>
+      <c r="F19" s="133"/>
       <c r="G19" s="52"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
@@ -4779,7 +4785,7 @@
       <c r="AH19" s="26"/>
       <c r="AI19" s="24"/>
       <c r="AJ19" s="74"/>
-      <c r="AK19" s="224"/>
+      <c r="AK19" s="130"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="32"/>
       <c r="AN19" s="25"/>
@@ -4811,18 +4817,18 @@
       <c r="BN19" s="74"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="191">
+      <c r="A20" s="168">
         <v>7</v>
       </c>
       <c r="B20" s="36"/>
-      <c r="C20" s="149" t="s">
+      <c r="C20" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="150"/>
-      <c r="E20" s="195" t="s">
+      <c r="D20" s="145"/>
+      <c r="E20" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="187"/>
+      <c r="F20" s="150"/>
       <c r="G20" s="51"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -4885,12 +4891,12 @@
       <c r="BN20" s="73"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="191"/>
+      <c r="A21" s="168"/>
       <c r="B21" s="36"/>
-      <c r="C21" s="160"/>
-      <c r="D21" s="161"/>
-      <c r="E21" s="174"/>
-      <c r="F21" s="176"/>
+      <c r="C21" s="146"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="133"/>
       <c r="G21" s="52"/>
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
@@ -4929,8 +4935,8 @@
       <c r="AP21" s="102"/>
       <c r="AQ21" s="102"/>
       <c r="AR21" s="102"/>
-      <c r="AS21" s="102"/>
-      <c r="AT21" s="24"/>
+      <c r="AS21" s="32"/>
+      <c r="AT21" s="32"/>
       <c r="AU21" s="25"/>
       <c r="AV21" s="26"/>
       <c r="AW21" s="26"/>
@@ -4953,18 +4959,18 @@
       <c r="BN21" s="74"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="191">
+      <c r="A22" s="168">
         <v>8</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="149" t="s">
+      <c r="C22" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="150"/>
-      <c r="E22" s="195" t="s">
+      <c r="D22" s="145"/>
+      <c r="E22" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="187"/>
+      <c r="F22" s="150"/>
       <c r="G22" s="52"/>
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
@@ -5027,12 +5033,12 @@
       <c r="BN22" s="77"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="191"/>
+      <c r="A23" s="168"/>
       <c r="B23" s="37"/>
-      <c r="C23" s="151"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="185"/>
-      <c r="F23" s="188"/>
+      <c r="C23" s="170"/>
+      <c r="D23" s="171"/>
+      <c r="E23" s="172"/>
+      <c r="F23" s="151"/>
       <c r="G23" s="54"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -5076,7 +5082,7 @@
       <c r="AU23" s="17"/>
       <c r="AV23" s="23"/>
       <c r="AW23" s="23"/>
-      <c r="AX23" s="68"/>
+      <c r="AX23" s="226"/>
       <c r="AY23" s="68"/>
       <c r="AZ23" s="68"/>
       <c r="BA23" s="68"/>
@@ -5095,20 +5101,20 @@
       <c r="BN23" s="78"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="166">
+      <c r="A24" s="161">
         <v>9</v>
       </c>
       <c r="B24" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="192" t="s">
+      <c r="C24" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="193"/>
-      <c r="E24" s="194" t="s">
+      <c r="D24" s="139"/>
+      <c r="E24" s="163" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="196"/>
+      <c r="F24" s="164"/>
       <c r="G24" s="38"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -5138,7 +5144,7 @@
       <c r="AG24" s="15"/>
       <c r="AH24" s="21"/>
       <c r="AI24" s="98"/>
-      <c r="AJ24" s="221"/>
+      <c r="AJ24" s="127"/>
       <c r="AK24" s="99"/>
       <c r="AL24" s="98"/>
       <c r="AM24" s="98"/>
@@ -5171,14 +5177,14 @@
       <c r="BN24" s="79"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="168"/>
+      <c r="A25" s="162"/>
       <c r="B25" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="160"/>
-      <c r="D25" s="161"/>
-      <c r="E25" s="174"/>
-      <c r="F25" s="197"/>
+      <c r="C25" s="146"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="165"/>
       <c r="G25" s="51"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -5223,8 +5229,8 @@
       <c r="AV25" s="19"/>
       <c r="AW25" s="19"/>
       <c r="AX25" s="63"/>
-      <c r="AY25" s="63"/>
-      <c r="AZ25" s="63"/>
+      <c r="AY25" s="122"/>
+      <c r="AZ25" s="122"/>
       <c r="BA25" s="63"/>
       <c r="BB25" s="13"/>
       <c r="BC25" s="19"/>
@@ -5245,14 +5251,14 @@
         <v>10</v>
       </c>
       <c r="B26" s="36"/>
-      <c r="C26" s="198" t="s">
+      <c r="C26" s="144" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="150"/>
-      <c r="E26" s="184" t="s">
+      <c r="D26" s="145"/>
+      <c r="E26" s="166" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="187"/>
+      <c r="F26" s="150"/>
       <c r="G26" s="51"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -5317,10 +5323,10 @@
     <row r="27" spans="1:66" ht="12" customHeight="1">
       <c r="A27" s="119"/>
       <c r="B27" s="103"/>
-      <c r="C27" s="160"/>
-      <c r="D27" s="161"/>
-      <c r="E27" s="173"/>
-      <c r="F27" s="175"/>
+      <c r="C27" s="146"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="167"/>
+      <c r="F27" s="132"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -5367,10 +5373,10 @@
       <c r="AX27" s="63"/>
       <c r="AY27" s="63"/>
       <c r="AZ27" s="63"/>
-      <c r="BA27" s="63"/>
+      <c r="BA27" s="122"/>
       <c r="BB27" s="13"/>
       <c r="BC27" s="19"/>
-      <c r="BD27" s="63"/>
+      <c r="BD27" s="122"/>
       <c r="BE27" s="63"/>
       <c r="BF27" s="63"/>
       <c r="BG27" s="63"/>
@@ -5385,14 +5391,14 @@
     <row r="28" spans="1:66" ht="12" customHeight="1">
       <c r="A28" s="118"/>
       <c r="B28" s="36"/>
-      <c r="C28" s="198" t="s">
+      <c r="C28" s="144" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="150"/>
-      <c r="E28" s="173" t="s">
+      <c r="D28" s="145"/>
+      <c r="E28" s="167" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="175"/>
+      <c r="F28" s="132"/>
       <c r="G28" s="51"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -5457,10 +5463,10 @@
     <row r="29" spans="1:66" ht="12" customHeight="1">
       <c r="A29" s="118"/>
       <c r="B29" s="36"/>
-      <c r="C29" s="160"/>
-      <c r="D29" s="161"/>
-      <c r="E29" s="173"/>
-      <c r="F29" s="175"/>
+      <c r="C29" s="146"/>
+      <c r="D29" s="147"/>
+      <c r="E29" s="167"/>
+      <c r="F29" s="132"/>
       <c r="G29" s="51"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -5525,14 +5531,14 @@
     <row r="30" spans="1:66" ht="12" customHeight="1">
       <c r="A30" s="118"/>
       <c r="B30" s="36"/>
-      <c r="C30" s="198" t="s">
+      <c r="C30" s="144" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="150"/>
-      <c r="E30" s="173" t="s">
+      <c r="D30" s="145"/>
+      <c r="E30" s="167" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="175"/>
+      <c r="F30" s="132"/>
       <c r="G30" s="51"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -5585,8 +5591,8 @@
       <c r="BD30" s="63"/>
       <c r="BE30" s="63"/>
       <c r="BF30" s="63"/>
-      <c r="BG30" s="30"/>
-      <c r="BH30" s="30"/>
+      <c r="BG30" s="101"/>
+      <c r="BH30" s="101"/>
       <c r="BI30" s="13"/>
       <c r="BJ30" s="19"/>
       <c r="BK30" s="63"/>
@@ -5597,10 +5603,10 @@
     <row r="31" spans="1:66" ht="12" customHeight="1">
       <c r="A31" s="118"/>
       <c r="B31" s="36"/>
-      <c r="C31" s="160"/>
-      <c r="D31" s="161"/>
-      <c r="E31" s="173"/>
-      <c r="F31" s="175"/>
+      <c r="C31" s="146"/>
+      <c r="D31" s="147"/>
+      <c r="E31" s="167"/>
+      <c r="F31" s="132"/>
       <c r="G31" s="51"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -5667,14 +5673,14 @@
         <v>11</v>
       </c>
       <c r="B32" s="36"/>
-      <c r="C32" s="198" t="s">
+      <c r="C32" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="150"/>
-      <c r="E32" s="173" t="s">
+      <c r="D32" s="145"/>
+      <c r="E32" s="167" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="175"/>
+      <c r="F32" s="132"/>
       <c r="G32" s="51"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -5739,10 +5745,10 @@
     <row r="33" spans="1:66" ht="12" customHeight="1">
       <c r="A33" s="119"/>
       <c r="B33" s="103"/>
-      <c r="C33" s="160"/>
-      <c r="D33" s="161"/>
-      <c r="E33" s="174"/>
-      <c r="F33" s="176"/>
+      <c r="C33" s="146"/>
+      <c r="D33" s="147"/>
+      <c r="E33" s="149"/>
+      <c r="F33" s="133"/>
       <c r="G33" s="51"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -5807,14 +5813,14 @@
     <row r="34" spans="1:66" ht="9.6" customHeight="1">
       <c r="A34" s="119"/>
       <c r="B34" s="103"/>
-      <c r="C34" s="198" t="s">
+      <c r="C34" s="144" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="150"/>
-      <c r="E34" s="195" t="s">
+      <c r="D34" s="145"/>
+      <c r="E34" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="F34" s="187"/>
+      <c r="F34" s="150"/>
       <c r="G34" s="51"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -5879,10 +5885,10 @@
     <row r="35" spans="1:66">
       <c r="A35" s="119"/>
       <c r="B35" s="103"/>
-      <c r="C35" s="160"/>
-      <c r="D35" s="161"/>
-      <c r="E35" s="174"/>
-      <c r="F35" s="176"/>
+      <c r="C35" s="146"/>
+      <c r="D35" s="147"/>
+      <c r="E35" s="149"/>
+      <c r="F35" s="133"/>
       <c r="G35" s="51"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -5947,14 +5953,14 @@
     <row r="36" spans="1:66">
       <c r="A36" s="120"/>
       <c r="B36" s="103"/>
-      <c r="C36" s="198" t="s">
+      <c r="C36" s="144" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="150"/>
-      <c r="E36" s="195" t="s">
+      <c r="D36" s="145"/>
+      <c r="E36" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="187"/>
+      <c r="F36" s="150"/>
       <c r="G36" s="52"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
@@ -6019,10 +6025,10 @@
     <row r="37" spans="1:66">
       <c r="A37" s="117"/>
       <c r="B37" s="37"/>
-      <c r="C37" s="160"/>
-      <c r="D37" s="161"/>
-      <c r="E37" s="174"/>
-      <c r="F37" s="188"/>
+      <c r="C37" s="146"/>
+      <c r="D37" s="147"/>
+      <c r="E37" s="149"/>
+      <c r="F37" s="151"/>
       <c r="G37" s="54"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
@@ -6066,10 +6072,10 @@
       <c r="AU37" s="17"/>
       <c r="AV37" s="23"/>
       <c r="AW37" s="23"/>
-      <c r="AX37" s="220"/>
-      <c r="AY37" s="220"/>
-      <c r="AZ37" s="220"/>
-      <c r="BA37" s="220"/>
+      <c r="AX37" s="126"/>
+      <c r="AY37" s="126"/>
+      <c r="AZ37" s="126"/>
+      <c r="BA37" s="126"/>
       <c r="BB37" s="17"/>
       <c r="BC37" s="23"/>
       <c r="BD37" s="68"/>
@@ -6085,20 +6091,20 @@
       <c r="BN37" s="78"/>
     </row>
     <row r="38" spans="1:66">
-      <c r="A38" s="147">
+      <c r="A38" s="134">
         <v>12</v>
       </c>
       <c r="B38" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C38" s="206" t="s">
+      <c r="C38" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="207"/>
-      <c r="E38" s="210" t="s">
+      <c r="D38" s="154"/>
+      <c r="E38" s="157" t="s">
         <v>56</v>
       </c>
-      <c r="F38" s="212"/>
+      <c r="F38" s="159"/>
       <c r="G38" s="38"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
@@ -6151,22 +6157,22 @@
       <c r="BD38" s="98"/>
       <c r="BE38" s="98"/>
       <c r="BF38" s="98"/>
-      <c r="BG38" s="98"/>
-      <c r="BH38" s="98"/>
+      <c r="BG38" s="40"/>
+      <c r="BH38" s="40"/>
       <c r="BI38" s="15"/>
       <c r="BJ38" s="21"/>
-      <c r="BK38" s="40"/>
-      <c r="BL38" s="40"/>
+      <c r="BK38" s="98"/>
+      <c r="BL38" s="98"/>
       <c r="BM38" s="65"/>
       <c r="BN38" s="79"/>
     </row>
     <row r="39" spans="1:66">
-      <c r="A39" s="148"/>
+      <c r="A39" s="152"/>
       <c r="B39" s="34"/>
-      <c r="C39" s="208"/>
-      <c r="D39" s="209"/>
-      <c r="E39" s="211"/>
-      <c r="F39" s="213"/>
+      <c r="C39" s="155"/>
+      <c r="D39" s="156"/>
+      <c r="E39" s="158"/>
+      <c r="F39" s="160"/>
       <c r="G39" s="51"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
@@ -6223,26 +6229,26 @@
       <c r="BH39" s="101"/>
       <c r="BI39" s="13"/>
       <c r="BJ39" s="19"/>
-      <c r="BK39" s="63"/>
-      <c r="BL39" s="63"/>
-      <c r="BM39" s="30"/>
-      <c r="BN39" s="223"/>
+      <c r="BK39" s="30"/>
+      <c r="BL39" s="30"/>
+      <c r="BM39" s="101"/>
+      <c r="BN39" s="227"/>
     </row>
     <row r="40" spans="1:66">
-      <c r="A40" s="147">
+      <c r="A40" s="134">
         <v>14</v>
       </c>
-      <c r="B40" s="200" t="s">
+      <c r="B40" s="136" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="192" t="s">
+      <c r="C40" s="138" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="193"/>
-      <c r="E40" s="200" t="s">
+      <c r="D40" s="139"/>
+      <c r="E40" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="F40" s="204"/>
+      <c r="F40" s="142"/>
       <c r="G40" s="38"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
@@ -6305,12 +6311,12 @@
       <c r="BN40" s="79"/>
     </row>
     <row r="41" spans="1:66" ht="10.199999999999999" thickBot="1">
-      <c r="A41" s="199"/>
-      <c r="B41" s="201"/>
-      <c r="C41" s="202"/>
-      <c r="D41" s="203"/>
-      <c r="E41" s="201"/>
-      <c r="F41" s="205"/>
+      <c r="A41" s="135"/>
+      <c r="B41" s="137"/>
+      <c r="C41" s="140"/>
+      <c r="D41" s="141"/>
+      <c r="E41" s="137"/>
+      <c r="F41" s="143"/>
       <c r="G41" s="39"/>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -6390,21 +6396,51 @@
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="C24:D25"/>
     <mergeCell ref="E24:E25"/>
@@ -6421,51 +6457,21 @@
     <mergeCell ref="C30:D31"/>
     <mergeCell ref="C32:D33"/>
     <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
@@ -6501,54 +6507,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="132" t="s">
+      <c r="B1" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="135" t="s">
+      <c r="C1" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="136"/>
-      <c r="E1" s="141" t="s">
+      <c r="D1" s="209"/>
+      <c r="E1" s="214" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="144" t="s">
+      <c r="F1" s="217" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="126"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="127"/>
-      <c r="S1" s="127"/>
-      <c r="T1" s="127"/>
-      <c r="U1" s="127"/>
-      <c r="V1" s="127"/>
-      <c r="W1" s="127"/>
-      <c r="X1" s="127"/>
-      <c r="Y1" s="127"/>
-      <c r="Z1" s="127"/>
-      <c r="AA1" s="127"/>
-      <c r="AB1" s="127"/>
-      <c r="AC1" s="127"/>
-      <c r="AD1" s="128"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="200"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="200"/>
+      <c r="K1" s="200"/>
+      <c r="L1" s="200"/>
+      <c r="M1" s="200"/>
+      <c r="N1" s="200"/>
+      <c r="O1" s="200"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="200"/>
+      <c r="AA1" s="200"/>
+      <c r="AB1" s="200"/>
+      <c r="AC1" s="200"/>
+      <c r="AD1" s="201"/>
     </row>
     <row r="2" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A2" s="130"/>
-      <c r="B2" s="133"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="145"/>
+      <c r="A2" s="203"/>
+      <c r="B2" s="206"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="211"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="218"/>
       <c r="G2" s="46">
         <v>22</v>
       </c>
@@ -6623,12 +6629,12 @@
       </c>
     </row>
     <row r="3" spans="1:30" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="146"/>
+      <c r="A3" s="204"/>
+      <c r="B3" s="207"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="213"/>
+      <c r="E3" s="216"/>
+      <c r="F3" s="219"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -6703,20 +6709,20 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A4" s="157">
+      <c r="A4" s="192">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="158" t="s">
+      <c r="C4" s="193" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="159"/>
-      <c r="E4" s="162" t="s">
+      <c r="D4" s="194"/>
+      <c r="E4" s="195" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="164"/>
+      <c r="F4" s="197"/>
       <c r="G4" s="49"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -6739,20 +6745,20 @@
       <c r="Z4" s="12"/>
       <c r="AA4" s="18"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="217" t="s">
+      <c r="AC4" s="223" t="s">
         <v>14</v>
       </c>
-      <c r="AD4" s="214" t="s">
+      <c r="AD4" s="220" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A5" s="148"/>
+      <c r="A5" s="152"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="160"/>
-      <c r="D5" s="161"/>
-      <c r="E5" s="163"/>
-      <c r="F5" s="165"/>
+      <c r="C5" s="146"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="196"/>
+      <c r="F5" s="198"/>
       <c r="G5" s="50"/>
       <c r="H5" s="31"/>
       <c r="I5" s="9"/>
@@ -6775,22 +6781,22 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="9"/>
-      <c r="AC5" s="218"/>
-      <c r="AD5" s="215"/>
+      <c r="AC5" s="224"/>
+      <c r="AD5" s="221"/>
     </row>
     <row r="6" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A6" s="147">
+      <c r="A6" s="134">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="149" t="s">
+      <c r="C6" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="150"/>
-      <c r="E6" s="153" t="s">
+      <c r="D6" s="145"/>
+      <c r="E6" s="188" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="155"/>
+      <c r="F6" s="190"/>
       <c r="G6" s="51"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -6813,16 +6819,16 @@
       <c r="Z6" s="13"/>
       <c r="AA6" s="19"/>
       <c r="AB6" s="7"/>
-      <c r="AC6" s="218"/>
-      <c r="AD6" s="215"/>
+      <c r="AC6" s="224"/>
+      <c r="AD6" s="221"/>
     </row>
     <row r="7" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A7" s="148"/>
+      <c r="A7" s="152"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="154"/>
-      <c r="F7" s="156"/>
+      <c r="C7" s="170"/>
+      <c r="D7" s="171"/>
+      <c r="E7" s="189"/>
+      <c r="F7" s="191"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="24"/>
@@ -6845,24 +6851,24 @@
       <c r="Z7" s="25"/>
       <c r="AA7" s="26"/>
       <c r="AB7" s="24"/>
-      <c r="AC7" s="218"/>
-      <c r="AD7" s="215"/>
+      <c r="AC7" s="224"/>
+      <c r="AD7" s="221"/>
     </row>
     <row r="8" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A8" s="166">
+      <c r="A8" s="161">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="177" t="s">
+      <c r="C8" s="181" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="178"/>
-      <c r="E8" s="183" t="s">
+      <c r="D8" s="182"/>
+      <c r="E8" s="187" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="186"/>
+      <c r="F8" s="176"/>
       <c r="G8" s="38"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -6885,16 +6891,16 @@
       <c r="Z8" s="15"/>
       <c r="AA8" s="21"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="218"/>
-      <c r="AD8" s="215"/>
+      <c r="AC8" s="224"/>
+      <c r="AD8" s="221"/>
     </row>
     <row r="9" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A9" s="168"/>
+      <c r="A9" s="162"/>
       <c r="B9" s="37"/>
-      <c r="C9" s="181"/>
-      <c r="D9" s="182"/>
-      <c r="E9" s="185"/>
-      <c r="F9" s="188"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="186"/>
+      <c r="E9" s="172"/>
+      <c r="F9" s="151"/>
       <c r="G9" s="53"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
@@ -6917,24 +6923,24 @@
       <c r="Z9" s="44"/>
       <c r="AA9" s="45"/>
       <c r="AB9" s="43"/>
-      <c r="AC9" s="218"/>
-      <c r="AD9" s="215"/>
+      <c r="AC9" s="224"/>
+      <c r="AD9" s="221"/>
     </row>
     <row r="10" spans="1:30" ht="12" customHeight="1">
-      <c r="A10" s="167">
+      <c r="A10" s="173">
         <v>4</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="169" t="s">
+      <c r="C10" s="177" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="170"/>
-      <c r="E10" s="173" t="s">
+      <c r="D10" s="178"/>
+      <c r="E10" s="167" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="175"/>
+      <c r="F10" s="132"/>
       <c r="G10" s="50"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -6957,16 +6963,16 @@
       <c r="Z10" s="16"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="218"/>
-      <c r="AD10" s="215"/>
+      <c r="AC10" s="224"/>
+      <c r="AD10" s="221"/>
     </row>
     <row r="11" spans="1:30" ht="12" customHeight="1">
-      <c r="A11" s="168"/>
+      <c r="A11" s="162"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="171"/>
-      <c r="D11" s="172"/>
-      <c r="E11" s="174"/>
-      <c r="F11" s="176"/>
+      <c r="C11" s="179"/>
+      <c r="D11" s="180"/>
+      <c r="E11" s="149"/>
+      <c r="F11" s="133"/>
       <c r="G11" s="50"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -6989,22 +6995,22 @@
       <c r="Z11" s="16"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="218"/>
-      <c r="AD11" s="215"/>
+      <c r="AC11" s="224"/>
+      <c r="AD11" s="221"/>
     </row>
     <row r="12" spans="1:30" ht="12" customHeight="1">
-      <c r="A12" s="166">
+      <c r="A12" s="161">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="149" t="s">
+      <c r="C12" s="169" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="150"/>
-      <c r="E12" s="184" t="s">
+      <c r="D12" s="145"/>
+      <c r="E12" s="166" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="187"/>
+      <c r="F12" s="150"/>
       <c r="G12" s="51"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -7027,16 +7033,16 @@
       <c r="Z12" s="13"/>
       <c r="AA12" s="19"/>
       <c r="AB12" s="7"/>
-      <c r="AC12" s="218"/>
-      <c r="AD12" s="215"/>
+      <c r="AC12" s="224"/>
+      <c r="AD12" s="221"/>
     </row>
     <row r="13" spans="1:30" ht="12" customHeight="1">
-      <c r="A13" s="167"/>
+      <c r="A13" s="173"/>
       <c r="B13" s="36"/>
-      <c r="C13" s="189"/>
-      <c r="D13" s="190"/>
-      <c r="E13" s="173"/>
-      <c r="F13" s="175"/>
+      <c r="C13" s="174"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="132"/>
       <c r="G13" s="52"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
@@ -7059,24 +7065,24 @@
       <c r="Z13" s="25"/>
       <c r="AA13" s="26"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="218"/>
-      <c r="AD13" s="215"/>
+      <c r="AC13" s="224"/>
+      <c r="AD13" s="221"/>
     </row>
     <row r="14" spans="1:30" ht="12" customHeight="1">
-      <c r="A14" s="191">
+      <c r="A14" s="168">
         <v>6</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="192" t="s">
+      <c r="C14" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="193"/>
-      <c r="E14" s="194" t="s">
+      <c r="D14" s="139"/>
+      <c r="E14" s="163" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="186"/>
+      <c r="F14" s="176"/>
       <c r="G14" s="38"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -7099,16 +7105,16 @@
       <c r="Z14" s="15"/>
       <c r="AA14" s="21"/>
       <c r="AB14" s="6"/>
-      <c r="AC14" s="218"/>
-      <c r="AD14" s="215"/>
+      <c r="AC14" s="224"/>
+      <c r="AD14" s="221"/>
     </row>
     <row r="15" spans="1:30" ht="12" customHeight="1">
-      <c r="A15" s="191"/>
+      <c r="A15" s="168"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="160"/>
-      <c r="D15" s="161"/>
-      <c r="E15" s="174"/>
-      <c r="F15" s="176"/>
+      <c r="C15" s="146"/>
+      <c r="D15" s="147"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="133"/>
       <c r="G15" s="52"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
@@ -7131,22 +7137,22 @@
       <c r="Z15" s="25"/>
       <c r="AA15" s="26"/>
       <c r="AB15" s="24"/>
-      <c r="AC15" s="218"/>
-      <c r="AD15" s="215"/>
+      <c r="AC15" s="224"/>
+      <c r="AD15" s="221"/>
     </row>
     <row r="16" spans="1:30" ht="12" customHeight="1">
-      <c r="A16" s="191">
+      <c r="A16" s="168">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="149" t="s">
+      <c r="C16" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="150"/>
-      <c r="E16" s="195" t="s">
+      <c r="D16" s="145"/>
+      <c r="E16" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="187"/>
+      <c r="F16" s="150"/>
       <c r="G16" s="51"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -7169,16 +7175,16 @@
       <c r="Z16" s="13"/>
       <c r="AA16" s="19"/>
       <c r="AB16" s="7"/>
-      <c r="AC16" s="218"/>
-      <c r="AD16" s="215"/>
+      <c r="AC16" s="224"/>
+      <c r="AD16" s="221"/>
     </row>
     <row r="17" spans="1:30" ht="12" customHeight="1">
-      <c r="A17" s="191"/>
+      <c r="A17" s="168"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="160"/>
-      <c r="D17" s="161"/>
-      <c r="E17" s="174"/>
-      <c r="F17" s="176"/>
+      <c r="C17" s="146"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="133"/>
       <c r="G17" s="52"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -7201,22 +7207,22 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="218"/>
-      <c r="AD17" s="215"/>
+      <c r="AC17" s="224"/>
+      <c r="AD17" s="221"/>
     </row>
     <row r="18" spans="1:30" ht="12" customHeight="1">
-      <c r="A18" s="191">
+      <c r="A18" s="168">
         <v>8</v>
       </c>
       <c r="B18" s="36"/>
-      <c r="C18" s="149" t="s">
+      <c r="C18" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="150"/>
-      <c r="E18" s="195" t="s">
+      <c r="D18" s="145"/>
+      <c r="E18" s="148" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="187"/>
+      <c r="F18" s="150"/>
       <c r="G18" s="52"/>
       <c r="H18" s="24"/>
       <c r="I18" s="24"/>
@@ -7239,16 +7245,16 @@
       <c r="Z18" s="25"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="218"/>
-      <c r="AD18" s="215"/>
+      <c r="AC18" s="224"/>
+      <c r="AD18" s="221"/>
     </row>
     <row r="19" spans="1:30" ht="12" customHeight="1">
-      <c r="A19" s="191"/>
+      <c r="A19" s="168"/>
       <c r="B19" s="37"/>
-      <c r="C19" s="151"/>
-      <c r="D19" s="152"/>
-      <c r="E19" s="185"/>
-      <c r="F19" s="188"/>
+      <c r="C19" s="170"/>
+      <c r="D19" s="171"/>
+      <c r="E19" s="172"/>
+      <c r="F19" s="151"/>
       <c r="G19" s="54"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -7271,24 +7277,24 @@
       <c r="Z19" s="17"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="218"/>
-      <c r="AD19" s="215"/>
+      <c r="AC19" s="224"/>
+      <c r="AD19" s="221"/>
     </row>
     <row r="20" spans="1:30" ht="12" customHeight="1">
-      <c r="A20" s="166">
+      <c r="A20" s="161">
         <v>9</v>
       </c>
       <c r="B20" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="192" t="s">
+      <c r="C20" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="193"/>
-      <c r="E20" s="194" t="s">
+      <c r="D20" s="139"/>
+      <c r="E20" s="163" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="186"/>
+      <c r="F20" s="176"/>
       <c r="G20" s="38"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -7311,18 +7317,18 @@
       <c r="Z20" s="15"/>
       <c r="AA20" s="21"/>
       <c r="AB20" s="6"/>
-      <c r="AC20" s="218"/>
-      <c r="AD20" s="215"/>
+      <c r="AC20" s="224"/>
+      <c r="AD20" s="221"/>
     </row>
     <row r="21" spans="1:30" ht="12" customHeight="1">
-      <c r="A21" s="168"/>
+      <c r="A21" s="162"/>
       <c r="B21" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="160"/>
-      <c r="D21" s="161"/>
-      <c r="E21" s="174"/>
-      <c r="F21" s="176"/>
+      <c r="C21" s="146"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="133"/>
       <c r="G21" s="51"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -7345,22 +7351,22 @@
       <c r="Z21" s="13"/>
       <c r="AA21" s="19"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="218"/>
-      <c r="AD21" s="215"/>
+      <c r="AC21" s="224"/>
+      <c r="AD21" s="221"/>
     </row>
     <row r="22" spans="1:30" ht="12" customHeight="1">
-      <c r="A22" s="166">
+      <c r="A22" s="161">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="198" t="s">
+      <c r="C22" s="144" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="150"/>
-      <c r="E22" s="195" t="s">
+      <c r="D22" s="145"/>
+      <c r="E22" s="148" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="187"/>
+      <c r="F22" s="150"/>
       <c r="G22" s="51"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -7383,16 +7389,16 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="19"/>
       <c r="AB22" s="7"/>
-      <c r="AC22" s="218"/>
-      <c r="AD22" s="215"/>
+      <c r="AC22" s="224"/>
+      <c r="AD22" s="221"/>
     </row>
     <row r="23" spans="1:30" ht="12" customHeight="1">
-      <c r="A23" s="168"/>
+      <c r="A23" s="162"/>
       <c r="B23" s="36"/>
-      <c r="C23" s="160"/>
-      <c r="D23" s="161"/>
-      <c r="E23" s="174"/>
-      <c r="F23" s="176"/>
+      <c r="C23" s="146"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="149"/>
+      <c r="F23" s="133"/>
       <c r="G23" s="51"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -7415,22 +7421,22 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="19"/>
       <c r="AB23" s="7"/>
-      <c r="AC23" s="218"/>
-      <c r="AD23" s="215"/>
+      <c r="AC23" s="224"/>
+      <c r="AD23" s="221"/>
     </row>
     <row r="24" spans="1:30" ht="12" customHeight="1">
-      <c r="A24" s="166">
+      <c r="A24" s="161">
         <v>11</v>
       </c>
       <c r="B24" s="36"/>
-      <c r="C24" s="198" t="s">
+      <c r="C24" s="144" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="150"/>
-      <c r="E24" s="195" t="s">
+      <c r="D24" s="145"/>
+      <c r="E24" s="148" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="187"/>
+      <c r="F24" s="150"/>
       <c r="G24" s="52"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -7453,16 +7459,16 @@
       <c r="Z24" s="25"/>
       <c r="AA24" s="26"/>
       <c r="AB24" s="24"/>
-      <c r="AC24" s="218"/>
-      <c r="AD24" s="215"/>
+      <c r="AC24" s="224"/>
+      <c r="AD24" s="221"/>
     </row>
     <row r="25" spans="1:30" ht="12" customHeight="1">
-      <c r="A25" s="168"/>
+      <c r="A25" s="162"/>
       <c r="B25" s="37"/>
-      <c r="C25" s="160"/>
-      <c r="D25" s="161"/>
-      <c r="E25" s="174"/>
-      <c r="F25" s="188"/>
+      <c r="C25" s="146"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="151"/>
       <c r="G25" s="54"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -7485,24 +7491,24 @@
       <c r="Z25" s="17"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="218"/>
-      <c r="AD25" s="215"/>
+      <c r="AC25" s="224"/>
+      <c r="AD25" s="221"/>
     </row>
     <row r="26" spans="1:30" ht="12" customHeight="1">
-      <c r="A26" s="147">
+      <c r="A26" s="134">
         <v>12</v>
       </c>
       <c r="B26" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="206" t="s">
+      <c r="C26" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="207"/>
-      <c r="E26" s="210" t="s">
+      <c r="D26" s="154"/>
+      <c r="E26" s="157" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="212"/>
+      <c r="F26" s="159"/>
       <c r="G26" s="38"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -7525,16 +7531,16 @@
       <c r="Z26" s="15"/>
       <c r="AA26" s="21"/>
       <c r="AB26" s="6"/>
-      <c r="AC26" s="218"/>
-      <c r="AD26" s="215"/>
+      <c r="AC26" s="224"/>
+      <c r="AD26" s="221"/>
     </row>
     <row r="27" spans="1:30" ht="12" customHeight="1">
-      <c r="A27" s="148"/>
+      <c r="A27" s="152"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="208"/>
-      <c r="D27" s="209"/>
-      <c r="E27" s="211"/>
-      <c r="F27" s="213"/>
+      <c r="C27" s="155"/>
+      <c r="D27" s="156"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="160"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -7557,24 +7563,24 @@
       <c r="Z27" s="13"/>
       <c r="AA27" s="19"/>
       <c r="AB27" s="7"/>
-      <c r="AC27" s="218"/>
-      <c r="AD27" s="215"/>
+      <c r="AC27" s="224"/>
+      <c r="AD27" s="221"/>
     </row>
     <row r="28" spans="1:30" ht="12" customHeight="1">
-      <c r="A28" s="147">
+      <c r="A28" s="134">
         <v>14</v>
       </c>
-      <c r="B28" s="200" t="s">
+      <c r="B28" s="136" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="192" t="s">
+      <c r="C28" s="138" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="193"/>
-      <c r="E28" s="200" t="s">
+      <c r="D28" s="139"/>
+      <c r="E28" s="136" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="204"/>
+      <c r="F28" s="142"/>
       <c r="G28" s="38"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -7597,16 +7603,16 @@
       <c r="Z28" s="15"/>
       <c r="AA28" s="21"/>
       <c r="AB28" s="40"/>
-      <c r="AC28" s="218"/>
-      <c r="AD28" s="215"/>
+      <c r="AC28" s="224"/>
+      <c r="AD28" s="221"/>
     </row>
     <row r="29" spans="1:30" ht="12" customHeight="1" thickBot="1">
-      <c r="A29" s="199"/>
-      <c r="B29" s="201"/>
-      <c r="C29" s="202"/>
-      <c r="D29" s="203"/>
-      <c r="E29" s="201"/>
-      <c r="F29" s="205"/>
+      <c r="A29" s="135"/>
+      <c r="B29" s="137"/>
+      <c r="C29" s="140"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="143"/>
       <c r="G29" s="39"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -7629,8 +7635,8 @@
       <c r="Z29" s="14"/>
       <c r="AA29" s="20"/>
       <c r="AB29" s="11"/>
-      <c r="AC29" s="219"/>
-      <c r="AD29" s="216"/>
+      <c r="AC29" s="225"/>
+      <c r="AD29" s="222"/>
     </row>
     <row r="30" spans="1:30">
       <c r="Z30" s="5"/>
@@ -7650,12 +7656,45 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="G1:AD1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="AD4:AD29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C6:D7"/>
@@ -7672,45 +7711,12 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G1:AD1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/システム開発演習/000-要件定義/003-WBS.xlsx
+++ b/システム開発演習/000-要件定義/003-WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\システム開発演習\000-要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EDB04E-8F63-4119-BA03-A67551D9F8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D999765-83B9-437D-B242-D9F15A7870F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="61">
   <si>
     <t>進捗</t>
     <rPh sb="0" eb="2">
@@ -605,6 +605,16 @@
     <t>午後</t>
     <rPh sb="0" eb="2">
       <t>ゴゴ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>単体試験</t>
+  </si>
+  <si>
+    <t>検索画面</t>
+    <rPh sb="0" eb="4">
+      <t>ケンサクガメン</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -1762,7 +1772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2154,11 +2164,248 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2169,12 +2416,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2187,33 +2428,6 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2238,183 +2452,6 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2433,10 +2470,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3141,7 +3181,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BN44"/>
+  <dimension ref="A1:BN46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="9.6"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -3156,94 +3196,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="205" t="s">
+      <c r="B1" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="208" t="s">
+      <c r="C1" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="209"/>
-      <c r="E1" s="214" t="s">
+      <c r="D1" s="151"/>
+      <c r="E1" s="156" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="217" t="s">
+      <c r="F1" s="159" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="199">
+      <c r="G1" s="141">
         <v>45536</v>
       </c>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
-      <c r="L1" s="200"/>
-      <c r="M1" s="200"/>
-      <c r="N1" s="200"/>
-      <c r="O1" s="200"/>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="200"/>
-      <c r="Y1" s="200"/>
-      <c r="Z1" s="200"/>
-      <c r="AA1" s="200"/>
-      <c r="AB1" s="200"/>
-      <c r="AC1" s="200"/>
-      <c r="AD1" s="200"/>
-      <c r="AE1" s="200"/>
-      <c r="AF1" s="200"/>
-      <c r="AG1" s="200"/>
-      <c r="AH1" s="200"/>
-      <c r="AI1" s="200"/>
-      <c r="AJ1" s="201"/>
-      <c r="AK1" s="199">
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="142"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="142"/>
+      <c r="S1" s="142"/>
+      <c r="T1" s="142"/>
+      <c r="U1" s="142"/>
+      <c r="V1" s="142"/>
+      <c r="W1" s="142"/>
+      <c r="X1" s="142"/>
+      <c r="Y1" s="142"/>
+      <c r="Z1" s="142"/>
+      <c r="AA1" s="142"/>
+      <c r="AB1" s="142"/>
+      <c r="AC1" s="142"/>
+      <c r="AD1" s="142"/>
+      <c r="AE1" s="142"/>
+      <c r="AF1" s="142"/>
+      <c r="AG1" s="142"/>
+      <c r="AH1" s="142"/>
+      <c r="AI1" s="142"/>
+      <c r="AJ1" s="143"/>
+      <c r="AK1" s="141">
         <v>45566</v>
       </c>
-      <c r="AL1" s="200"/>
-      <c r="AM1" s="200"/>
-      <c r="AN1" s="200"/>
-      <c r="AO1" s="200"/>
-      <c r="AP1" s="200"/>
-      <c r="AQ1" s="200"/>
-      <c r="AR1" s="200"/>
-      <c r="AS1" s="200"/>
-      <c r="AT1" s="200"/>
-      <c r="AU1" s="200"/>
-      <c r="AV1" s="200"/>
-      <c r="AW1" s="200"/>
-      <c r="AX1" s="200"/>
-      <c r="AY1" s="200"/>
-      <c r="AZ1" s="200"/>
-      <c r="BA1" s="200"/>
-      <c r="BB1" s="200"/>
-      <c r="BC1" s="200"/>
-      <c r="BD1" s="200"/>
-      <c r="BE1" s="200"/>
-      <c r="BF1" s="200"/>
-      <c r="BG1" s="200"/>
-      <c r="BH1" s="200"/>
-      <c r="BI1" s="200"/>
-      <c r="BJ1" s="200"/>
-      <c r="BK1" s="200"/>
-      <c r="BL1" s="200"/>
-      <c r="BM1" s="200"/>
-      <c r="BN1" s="201"/>
+      <c r="AL1" s="142"/>
+      <c r="AM1" s="142"/>
+      <c r="AN1" s="142"/>
+      <c r="AO1" s="142"/>
+      <c r="AP1" s="142"/>
+      <c r="AQ1" s="142"/>
+      <c r="AR1" s="142"/>
+      <c r="AS1" s="142"/>
+      <c r="AT1" s="142"/>
+      <c r="AU1" s="142"/>
+      <c r="AV1" s="142"/>
+      <c r="AW1" s="142"/>
+      <c r="AX1" s="142"/>
+      <c r="AY1" s="142"/>
+      <c r="AZ1" s="142"/>
+      <c r="BA1" s="142"/>
+      <c r="BB1" s="142"/>
+      <c r="BC1" s="142"/>
+      <c r="BD1" s="142"/>
+      <c r="BE1" s="142"/>
+      <c r="BF1" s="142"/>
+      <c r="BG1" s="142"/>
+      <c r="BH1" s="142"/>
+      <c r="BI1" s="142"/>
+      <c r="BJ1" s="142"/>
+      <c r="BK1" s="142"/>
+      <c r="BL1" s="142"/>
+      <c r="BM1" s="142"/>
+      <c r="BN1" s="143"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="203"/>
-      <c r="B2" s="206"/>
-      <c r="C2" s="210"/>
-      <c r="D2" s="211"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="218"/>
+      <c r="A2" s="145"/>
+      <c r="B2" s="148"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="160"/>
       <c r="G2" s="46">
         <v>45537</v>
       </c>
@@ -3485,12 +3525,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="204"/>
-      <c r="B3" s="207"/>
-      <c r="C3" s="212"/>
-      <c r="D3" s="213"/>
-      <c r="E3" s="216"/>
-      <c r="F3" s="219"/>
+      <c r="A3" s="146"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="154"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="161"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -3673,20 +3713,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="192">
+      <c r="A4" s="172">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="193" t="s">
+      <c r="C4" s="173" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="194"/>
-      <c r="E4" s="195" t="s">
+      <c r="D4" s="174"/>
+      <c r="E4" s="177" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="197"/>
+      <c r="F4" s="179"/>
       <c r="G4" s="95"/>
       <c r="H4" s="29"/>
       <c r="I4" s="125"/>
@@ -3749,12 +3789,12 @@
       <c r="BN4" s="71"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="152"/>
+      <c r="A5" s="163"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="198"/>
+      <c r="C5" s="175"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="178"/>
+      <c r="F5" s="180"/>
       <c r="G5" s="96"/>
       <c r="H5" s="31"/>
       <c r="I5" s="97"/>
@@ -3817,18 +3857,18 @@
       <c r="BN5" s="72"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="134">
+      <c r="A6" s="162">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="169" t="s">
+      <c r="C6" s="164" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="145"/>
-      <c r="E6" s="188" t="s">
+      <c r="D6" s="165"/>
+      <c r="E6" s="168" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="190"/>
+      <c r="F6" s="170"/>
       <c r="G6" s="51"/>
       <c r="H6" s="63"/>
       <c r="I6" s="30"/>
@@ -3891,12 +3931,12 @@
       <c r="BN6" s="73"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="152"/>
+      <c r="A7" s="163"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="170"/>
-      <c r="D7" s="171"/>
-      <c r="E7" s="189"/>
-      <c r="F7" s="191"/>
+      <c r="C7" s="166"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="171"/>
       <c r="G7" s="52"/>
       <c r="H7" s="64"/>
       <c r="I7" s="32"/>
@@ -3959,20 +3999,20 @@
       <c r="BN7" s="74"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="161">
+      <c r="A8" s="181">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="181" t="s">
+      <c r="C8" s="192" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="182"/>
-      <c r="E8" s="187" t="s">
+      <c r="D8" s="193"/>
+      <c r="E8" s="198" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="176"/>
+      <c r="F8" s="201"/>
       <c r="G8" s="38"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65"/>
@@ -4035,12 +4075,12 @@
       <c r="BN8" s="75"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="173"/>
+      <c r="A9" s="182"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="177"/>
-      <c r="D9" s="178"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="132"/>
+      <c r="C9" s="184"/>
+      <c r="D9" s="185"/>
+      <c r="E9" s="188"/>
+      <c r="F9" s="190"/>
       <c r="G9" s="104"/>
       <c r="H9" s="105"/>
       <c r="I9" s="105"/>
@@ -4103,16 +4143,16 @@
       <c r="BN9" s="110"/>
     </row>
     <row r="10" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A10" s="173"/>
+      <c r="A10" s="182"/>
       <c r="B10" s="36"/>
-      <c r="C10" s="183" t="s">
+      <c r="C10" s="194" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="184"/>
-      <c r="E10" s="166" t="s">
+      <c r="D10" s="195"/>
+      <c r="E10" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="150"/>
+      <c r="F10" s="202"/>
       <c r="G10" s="115"/>
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
@@ -4175,12 +4215,12 @@
       <c r="BN10" s="73"/>
     </row>
     <row r="11" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A11" s="173"/>
+      <c r="A11" s="182"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="179"/>
-      <c r="D11" s="180"/>
-      <c r="E11" s="149"/>
-      <c r="F11" s="133"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="189"/>
+      <c r="F11" s="191"/>
       <c r="G11" s="104"/>
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
@@ -4243,16 +4283,16 @@
       <c r="BN11" s="110"/>
     </row>
     <row r="12" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A12" s="173"/>
+      <c r="A12" s="182"/>
       <c r="B12" s="36"/>
-      <c r="C12" s="177" t="s">
+      <c r="C12" s="184" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="178"/>
-      <c r="E12" s="167" t="s">
+      <c r="D12" s="185"/>
+      <c r="E12" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="132"/>
+      <c r="F12" s="190"/>
       <c r="G12" s="115"/>
       <c r="H12" s="62"/>
       <c r="I12" s="62"/>
@@ -4317,12 +4357,12 @@
       <c r="BN12" s="73"/>
     </row>
     <row r="13" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A13" s="162"/>
+      <c r="A13" s="183"/>
       <c r="B13" s="37"/>
-      <c r="C13" s="185"/>
-      <c r="D13" s="186"/>
-      <c r="E13" s="172"/>
-      <c r="F13" s="151"/>
+      <c r="C13" s="196"/>
+      <c r="D13" s="197"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="203"/>
       <c r="G13" s="53"/>
       <c r="H13" s="66"/>
       <c r="I13" s="66"/>
@@ -4385,20 +4425,20 @@
       <c r="BN13" s="76"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="173">
+      <c r="A14" s="182">
         <v>4</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="177" t="s">
+      <c r="C14" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="178"/>
-      <c r="E14" s="167" t="s">
+      <c r="D14" s="185"/>
+      <c r="E14" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="132"/>
+      <c r="F14" s="190"/>
       <c r="G14" s="50"/>
       <c r="H14" s="62"/>
       <c r="I14" s="62"/>
@@ -4463,12 +4503,12 @@
       <c r="BN14" s="72"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="162"/>
+      <c r="A15" s="183"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="179"/>
-      <c r="D15" s="180"/>
-      <c r="E15" s="149"/>
-      <c r="F15" s="133"/>
+      <c r="C15" s="186"/>
+      <c r="D15" s="187"/>
+      <c r="E15" s="189"/>
+      <c r="F15" s="191"/>
       <c r="G15" s="50"/>
       <c r="H15" s="62"/>
       <c r="I15" s="62"/>
@@ -4531,18 +4571,18 @@
       <c r="BN15" s="72"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="161">
+      <c r="A16" s="181">
         <v>5</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="169" t="s">
+      <c r="C16" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="145"/>
-      <c r="E16" s="166" t="s">
+      <c r="D16" s="165"/>
+      <c r="E16" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="150"/>
+      <c r="F16" s="202"/>
       <c r="G16" s="51"/>
       <c r="H16" s="63"/>
       <c r="I16" s="63"/>
@@ -4605,12 +4645,12 @@
       <c r="BN16" s="73"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="173"/>
+      <c r="A17" s="182"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="174"/>
-      <c r="D17" s="175"/>
-      <c r="E17" s="167"/>
-      <c r="F17" s="132"/>
+      <c r="C17" s="204"/>
+      <c r="D17" s="205"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="190"/>
       <c r="G17" s="52"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
@@ -4673,20 +4713,20 @@
       <c r="BN17" s="74"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="168">
+      <c r="A18" s="206">
         <v>6</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="138" t="s">
+      <c r="C18" s="207" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="139"/>
-      <c r="E18" s="163" t="s">
+      <c r="D18" s="208"/>
+      <c r="E18" s="209" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="176"/>
+      <c r="F18" s="201"/>
       <c r="G18" s="38"/>
       <c r="H18" s="65"/>
       <c r="I18" s="65"/>
@@ -4749,12 +4789,12 @@
       <c r="BN18" s="75"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="168"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="36"/>
-      <c r="C19" s="146"/>
-      <c r="D19" s="147"/>
-      <c r="E19" s="149"/>
-      <c r="F19" s="133"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="176"/>
+      <c r="E19" s="189"/>
+      <c r="F19" s="191"/>
       <c r="G19" s="52"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
@@ -4817,18 +4857,18 @@
       <c r="BN19" s="74"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="168">
+      <c r="A20" s="206">
         <v>7</v>
       </c>
       <c r="B20" s="36"/>
-      <c r="C20" s="169" t="s">
+      <c r="C20" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="145"/>
-      <c r="E20" s="148" t="s">
+      <c r="D20" s="165"/>
+      <c r="E20" s="210" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="150"/>
+      <c r="F20" s="202"/>
       <c r="G20" s="51"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -4891,12 +4931,12 @@
       <c r="BN20" s="73"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="168"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="36"/>
-      <c r="C21" s="146"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="133"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="176"/>
+      <c r="E21" s="189"/>
+      <c r="F21" s="191"/>
       <c r="G21" s="52"/>
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
@@ -4959,18 +4999,18 @@
       <c r="BN21" s="74"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="168">
+      <c r="A22" s="206">
         <v>8</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="169" t="s">
+      <c r="C22" s="164" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="145"/>
-      <c r="E22" s="148" t="s">
+      <c r="D22" s="165"/>
+      <c r="E22" s="210" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="150"/>
+      <c r="F22" s="202"/>
       <c r="G22" s="52"/>
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
@@ -5033,12 +5073,12 @@
       <c r="BN22" s="77"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="168"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="37"/>
-      <c r="C23" s="170"/>
-      <c r="D23" s="171"/>
-      <c r="E23" s="172"/>
-      <c r="F23" s="151"/>
+      <c r="C23" s="166"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="200"/>
+      <c r="F23" s="203"/>
       <c r="G23" s="54"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -5082,7 +5122,7 @@
       <c r="AU23" s="17"/>
       <c r="AV23" s="23"/>
       <c r="AW23" s="23"/>
-      <c r="AX23" s="226"/>
+      <c r="AX23" s="139"/>
       <c r="AY23" s="68"/>
       <c r="AZ23" s="68"/>
       <c r="BA23" s="68"/>
@@ -5101,20 +5141,20 @@
       <c r="BN23" s="78"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="161">
+      <c r="A24" s="181">
         <v>9</v>
       </c>
       <c r="B24" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="138" t="s">
+      <c r="C24" s="207" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="139"/>
-      <c r="E24" s="163" t="s">
+      <c r="D24" s="208"/>
+      <c r="E24" s="209" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="164"/>
+      <c r="F24" s="211"/>
       <c r="G24" s="38"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -5177,14 +5217,12 @@
       <c r="BN24" s="79"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="162"/>
-      <c r="B25" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="146"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="149"/>
-      <c r="F25" s="165"/>
+      <c r="A25" s="183"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="175"/>
+      <c r="D25" s="176"/>
+      <c r="E25" s="189"/>
+      <c r="F25" s="212"/>
       <c r="G25" s="51"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -5251,14 +5289,14 @@
         <v>10</v>
       </c>
       <c r="B26" s="36"/>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="213" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="145"/>
-      <c r="E26" s="166" t="s">
+      <c r="D26" s="165"/>
+      <c r="E26" s="199" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="150"/>
+      <c r="F26" s="202"/>
       <c r="G26" s="51"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -5323,10 +5361,10 @@
     <row r="27" spans="1:66" ht="12" customHeight="1">
       <c r="A27" s="119"/>
       <c r="B27" s="103"/>
-      <c r="C27" s="146"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="167"/>
-      <c r="F27" s="132"/>
+      <c r="C27" s="175"/>
+      <c r="D27" s="176"/>
+      <c r="E27" s="188"/>
+      <c r="F27" s="190"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -5391,14 +5429,14 @@
     <row r="28" spans="1:66" ht="12" customHeight="1">
       <c r="A28" s="118"/>
       <c r="B28" s="36"/>
-      <c r="C28" s="144" t="s">
+      <c r="C28" s="213" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="145"/>
-      <c r="E28" s="167" t="s">
+      <c r="D28" s="165"/>
+      <c r="E28" s="188" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="132"/>
+      <c r="F28" s="190"/>
       <c r="G28" s="51"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -5463,10 +5501,10 @@
     <row r="29" spans="1:66" ht="12" customHeight="1">
       <c r="A29" s="118"/>
       <c r="B29" s="36"/>
-      <c r="C29" s="146"/>
-      <c r="D29" s="147"/>
-      <c r="E29" s="167"/>
-      <c r="F29" s="132"/>
+      <c r="C29" s="175"/>
+      <c r="D29" s="176"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="190"/>
       <c r="G29" s="51"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -5517,8 +5555,8 @@
       <c r="BB29" s="13"/>
       <c r="BC29" s="19"/>
       <c r="BD29" s="63"/>
-      <c r="BE29" s="63"/>
-      <c r="BF29" s="63"/>
+      <c r="BE29" s="122"/>
+      <c r="BF29" s="122"/>
       <c r="BG29" s="63"/>
       <c r="BH29" s="63"/>
       <c r="BI29" s="13"/>
@@ -5531,14 +5569,14 @@
     <row r="30" spans="1:66" ht="12" customHeight="1">
       <c r="A30" s="118"/>
       <c r="B30" s="36"/>
-      <c r="C30" s="144" t="s">
+      <c r="C30" s="213" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="145"/>
-      <c r="E30" s="167" t="s">
+      <c r="D30" s="165"/>
+      <c r="E30" s="188" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="132"/>
+      <c r="F30" s="190"/>
       <c r="G30" s="51"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -5603,10 +5641,10 @@
     <row r="31" spans="1:66" ht="12" customHeight="1">
       <c r="A31" s="118"/>
       <c r="B31" s="36"/>
-      <c r="C31" s="146"/>
-      <c r="D31" s="147"/>
-      <c r="E31" s="167"/>
-      <c r="F31" s="132"/>
+      <c r="C31" s="175"/>
+      <c r="D31" s="176"/>
+      <c r="E31" s="188"/>
+      <c r="F31" s="190"/>
       <c r="G31" s="51"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -5673,14 +5711,14 @@
         <v>11</v>
       </c>
       <c r="B32" s="36"/>
-      <c r="C32" s="144" t="s">
+      <c r="C32" s="213" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="145"/>
-      <c r="E32" s="167" t="s">
+      <c r="D32" s="165"/>
+      <c r="E32" s="188" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="132"/>
+      <c r="F32" s="190"/>
       <c r="G32" s="51"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -5745,10 +5783,10 @@
     <row r="33" spans="1:66" ht="12" customHeight="1">
       <c r="A33" s="119"/>
       <c r="B33" s="103"/>
-      <c r="C33" s="146"/>
-      <c r="D33" s="147"/>
-      <c r="E33" s="149"/>
-      <c r="F33" s="133"/>
+      <c r="C33" s="175"/>
+      <c r="D33" s="176"/>
+      <c r="E33" s="189"/>
+      <c r="F33" s="191"/>
       <c r="G33" s="51"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -5813,14 +5851,14 @@
     <row r="34" spans="1:66" ht="9.6" customHeight="1">
       <c r="A34" s="119"/>
       <c r="B34" s="103"/>
-      <c r="C34" s="144" t="s">
+      <c r="C34" s="213" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="145"/>
-      <c r="E34" s="148" t="s">
+      <c r="D34" s="165"/>
+      <c r="E34" s="210" t="s">
         <v>56</v>
       </c>
-      <c r="F34" s="150"/>
+      <c r="F34" s="202"/>
       <c r="G34" s="51"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -5885,10 +5923,10 @@
     <row r="35" spans="1:66">
       <c r="A35" s="119"/>
       <c r="B35" s="103"/>
-      <c r="C35" s="146"/>
-      <c r="D35" s="147"/>
-      <c r="E35" s="149"/>
-      <c r="F35" s="133"/>
+      <c r="C35" s="175"/>
+      <c r="D35" s="176"/>
+      <c r="E35" s="189"/>
+      <c r="F35" s="191"/>
       <c r="G35" s="51"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -5953,14 +5991,14 @@
     <row r="36" spans="1:66">
       <c r="A36" s="120"/>
       <c r="B36" s="103"/>
-      <c r="C36" s="144" t="s">
+      <c r="C36" s="213" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="145"/>
-      <c r="E36" s="148" t="s">
+      <c r="D36" s="165"/>
+      <c r="E36" s="210" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="150"/>
+      <c r="F36" s="202"/>
       <c r="G36" s="52"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
@@ -6025,10 +6063,10 @@
     <row r="37" spans="1:66">
       <c r="A37" s="117"/>
       <c r="B37" s="37"/>
-      <c r="C37" s="146"/>
-      <c r="D37" s="147"/>
-      <c r="E37" s="149"/>
-      <c r="F37" s="151"/>
+      <c r="C37" s="175"/>
+      <c r="D37" s="205"/>
+      <c r="E37" s="188"/>
+      <c r="F37" s="203"/>
       <c r="G37" s="54"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
@@ -6091,164 +6129,164 @@
       <c r="BN37" s="78"/>
     </row>
     <row r="38" spans="1:66">
-      <c r="A38" s="134">
+      <c r="A38" s="120">
         <v>12</v>
       </c>
-      <c r="B38" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="153" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="154"/>
-      <c r="E38" s="157" t="s">
-        <v>56</v>
-      </c>
-      <c r="F38" s="159"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="21"/>
-      <c r="N38" s="65"/>
-      <c r="O38" s="65"/>
-      <c r="P38" s="65"/>
-      <c r="Q38" s="65"/>
-      <c r="R38" s="65"/>
-      <c r="S38" s="15"/>
-      <c r="T38" s="21"/>
-      <c r="U38" s="21"/>
-      <c r="V38" s="65"/>
-      <c r="W38" s="65"/>
-      <c r="X38" s="65"/>
-      <c r="Y38" s="65"/>
-      <c r="Z38" s="15"/>
-      <c r="AA38" s="21"/>
-      <c r="AB38" s="21"/>
-      <c r="AC38" s="65"/>
-      <c r="AD38" s="65"/>
-      <c r="AE38" s="65"/>
-      <c r="AF38" s="65"/>
-      <c r="AG38" s="15"/>
-      <c r="AH38" s="21"/>
-      <c r="AI38" s="65"/>
-      <c r="AJ38" s="79"/>
-      <c r="AK38" s="90"/>
-      <c r="AL38" s="65"/>
-      <c r="AM38" s="65"/>
-      <c r="AN38" s="15"/>
-      <c r="AO38" s="21"/>
-      <c r="AP38" s="65"/>
-      <c r="AQ38" s="65"/>
-      <c r="AR38" s="65"/>
-      <c r="AS38" s="65"/>
-      <c r="AT38" s="98"/>
-      <c r="AU38" s="15"/>
-      <c r="AV38" s="21"/>
-      <c r="AW38" s="21"/>
-      <c r="AX38" s="98"/>
-      <c r="AY38" s="98"/>
-      <c r="AZ38" s="98"/>
-      <c r="BA38" s="98"/>
-      <c r="BB38" s="15"/>
-      <c r="BC38" s="21"/>
-      <c r="BD38" s="98"/>
-      <c r="BE38" s="98"/>
-      <c r="BF38" s="98"/>
-      <c r="BG38" s="40"/>
-      <c r="BH38" s="40"/>
-      <c r="BI38" s="15"/>
-      <c r="BJ38" s="21"/>
-      <c r="BK38" s="98"/>
-      <c r="BL38" s="98"/>
-      <c r="BM38" s="65"/>
-      <c r="BN38" s="79"/>
+      <c r="B38" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="137" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="133"/>
+      <c r="E38" s="138" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="132"/>
+      <c r="G38" s="104"/>
+      <c r="H38" s="109"/>
+      <c r="I38" s="109"/>
+      <c r="J38" s="109"/>
+      <c r="K38" s="109"/>
+      <c r="L38" s="106"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="105"/>
+      <c r="O38" s="105"/>
+      <c r="P38" s="105"/>
+      <c r="Q38" s="105"/>
+      <c r="R38" s="105"/>
+      <c r="S38" s="106"/>
+      <c r="T38" s="107"/>
+      <c r="U38" s="107"/>
+      <c r="V38" s="105"/>
+      <c r="W38" s="105"/>
+      <c r="X38" s="105"/>
+      <c r="Y38" s="105"/>
+      <c r="Z38" s="106"/>
+      <c r="AA38" s="107"/>
+      <c r="AB38" s="107"/>
+      <c r="AC38" s="105"/>
+      <c r="AD38" s="105"/>
+      <c r="AE38" s="105"/>
+      <c r="AF38" s="105"/>
+      <c r="AG38" s="106"/>
+      <c r="AH38" s="107"/>
+      <c r="AI38" s="105"/>
+      <c r="AJ38" s="235"/>
+      <c r="AK38" s="236"/>
+      <c r="AL38" s="105"/>
+      <c r="AM38" s="105"/>
+      <c r="AN38" s="106"/>
+      <c r="AO38" s="107"/>
+      <c r="AP38" s="105"/>
+      <c r="AQ38" s="105"/>
+      <c r="AR38" s="105"/>
+      <c r="AS38" s="105"/>
+      <c r="AT38" s="105"/>
+      <c r="AU38" s="106"/>
+      <c r="AV38" s="107"/>
+      <c r="AW38" s="107"/>
+      <c r="AX38" s="108"/>
+      <c r="AY38" s="108"/>
+      <c r="AZ38" s="108"/>
+      <c r="BA38" s="108"/>
+      <c r="BB38" s="106"/>
+      <c r="BC38" s="107"/>
+      <c r="BD38" s="105"/>
+      <c r="BE38" s="105"/>
+      <c r="BF38" s="105"/>
+      <c r="BG38" s="237"/>
+      <c r="BH38" s="237"/>
+      <c r="BI38" s="106"/>
+      <c r="BJ38" s="107"/>
+      <c r="BK38" s="105"/>
+      <c r="BL38" s="105"/>
+      <c r="BM38" s="105"/>
+      <c r="BN38" s="235"/>
     </row>
     <row r="39" spans="1:66">
-      <c r="A39" s="152"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="155"/>
-      <c r="D39" s="156"/>
-      <c r="E39" s="158"/>
-      <c r="F39" s="160"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="63"/>
-      <c r="O39" s="63"/>
-      <c r="P39" s="63"/>
-      <c r="Q39" s="63"/>
-      <c r="R39" s="63"/>
-      <c r="S39" s="13"/>
-      <c r="T39" s="19"/>
-      <c r="U39" s="19"/>
-      <c r="V39" s="63"/>
-      <c r="W39" s="63"/>
-      <c r="X39" s="63"/>
-      <c r="Y39" s="63"/>
-      <c r="Z39" s="13"/>
-      <c r="AA39" s="19"/>
-      <c r="AB39" s="19"/>
-      <c r="AC39" s="63"/>
-      <c r="AD39" s="63"/>
-      <c r="AE39" s="63"/>
-      <c r="AF39" s="63"/>
-      <c r="AG39" s="13"/>
-      <c r="AH39" s="19"/>
-      <c r="AI39" s="63"/>
-      <c r="AJ39" s="80"/>
-      <c r="AK39" s="91"/>
-      <c r="AL39" s="63"/>
-      <c r="AM39" s="63"/>
-      <c r="AN39" s="13"/>
-      <c r="AO39" s="19"/>
-      <c r="AP39" s="63"/>
-      <c r="AQ39" s="63"/>
-      <c r="AR39" s="63"/>
-      <c r="AS39" s="63"/>
-      <c r="AT39" s="63"/>
-      <c r="AU39" s="13"/>
-      <c r="AV39" s="19"/>
-      <c r="AW39" s="19"/>
-      <c r="AX39" s="63"/>
-      <c r="AY39" s="63"/>
-      <c r="AZ39" s="63"/>
-      <c r="BA39" s="63"/>
-      <c r="BB39" s="13"/>
-      <c r="BC39" s="19"/>
-      <c r="BD39" s="101"/>
-      <c r="BE39" s="101"/>
-      <c r="BF39" s="101"/>
-      <c r="BG39" s="101"/>
-      <c r="BH39" s="101"/>
-      <c r="BI39" s="13"/>
-      <c r="BJ39" s="19"/>
-      <c r="BK39" s="30"/>
-      <c r="BL39" s="30"/>
-      <c r="BM39" s="101"/>
-      <c r="BN39" s="227"/>
+      <c r="A39" s="120"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="134"/>
+      <c r="D39" s="135"/>
+      <c r="E39" s="136"/>
+      <c r="F39" s="132"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="68"/>
+      <c r="O39" s="68"/>
+      <c r="P39" s="68"/>
+      <c r="Q39" s="68"/>
+      <c r="R39" s="68"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="23"/>
+      <c r="U39" s="23"/>
+      <c r="V39" s="68"/>
+      <c r="W39" s="68"/>
+      <c r="X39" s="68"/>
+      <c r="Y39" s="68"/>
+      <c r="Z39" s="17"/>
+      <c r="AA39" s="23"/>
+      <c r="AB39" s="23"/>
+      <c r="AC39" s="68"/>
+      <c r="AD39" s="68"/>
+      <c r="AE39" s="68"/>
+      <c r="AF39" s="68"/>
+      <c r="AG39" s="17"/>
+      <c r="AH39" s="23"/>
+      <c r="AI39" s="68"/>
+      <c r="AJ39" s="78"/>
+      <c r="AK39" s="89"/>
+      <c r="AL39" s="68"/>
+      <c r="AM39" s="68"/>
+      <c r="AN39" s="17"/>
+      <c r="AO39" s="23"/>
+      <c r="AP39" s="68"/>
+      <c r="AQ39" s="68"/>
+      <c r="AR39" s="68"/>
+      <c r="AS39" s="68"/>
+      <c r="AT39" s="68"/>
+      <c r="AU39" s="17"/>
+      <c r="AV39" s="23"/>
+      <c r="AW39" s="23"/>
+      <c r="AX39" s="126"/>
+      <c r="AY39" s="126"/>
+      <c r="AZ39" s="126"/>
+      <c r="BA39" s="126"/>
+      <c r="BB39" s="17"/>
+      <c r="BC39" s="23"/>
+      <c r="BD39" s="68"/>
+      <c r="BE39" s="68"/>
+      <c r="BF39" s="68"/>
+      <c r="BG39" s="139"/>
+      <c r="BH39" s="139"/>
+      <c r="BI39" s="17"/>
+      <c r="BJ39" s="23"/>
+      <c r="BK39" s="68"/>
+      <c r="BL39" s="68"/>
+      <c r="BM39" s="68"/>
+      <c r="BN39" s="78"/>
     </row>
     <row r="40" spans="1:66">
-      <c r="A40" s="134">
-        <v>14</v>
-      </c>
-      <c r="B40" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="138" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="139"/>
-      <c r="E40" s="136" t="s">
+      <c r="A40" s="162">
+        <v>13</v>
+      </c>
+      <c r="B40" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="221" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="222"/>
+      <c r="E40" s="225" t="s">
         <v>56</v>
       </c>
-      <c r="F40" s="142"/>
+      <c r="F40" s="227"/>
       <c r="G40" s="38"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
@@ -6256,11 +6294,11 @@
       <c r="K40" s="6"/>
       <c r="L40" s="15"/>
       <c r="M40" s="21"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="6"/>
-      <c r="P40" s="6"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="65"/>
+      <c r="Q40" s="65"/>
+      <c r="R40" s="65"/>
       <c r="S40" s="15"/>
       <c r="T40" s="21"/>
       <c r="U40" s="21"/>
@@ -6288,12 +6326,12 @@
       <c r="AQ40" s="65"/>
       <c r="AR40" s="65"/>
       <c r="AS40" s="65"/>
-      <c r="AT40" s="65"/>
+      <c r="AT40" s="98"/>
       <c r="AU40" s="15"/>
       <c r="AV40" s="21"/>
       <c r="AW40" s="21"/>
-      <c r="AX40" s="65"/>
-      <c r="AY40" s="65"/>
+      <c r="AX40" s="98"/>
+      <c r="AY40" s="98"/>
       <c r="AZ40" s="98"/>
       <c r="BA40" s="98"/>
       <c r="BB40" s="15"/>
@@ -6305,142 +6343,256 @@
       <c r="BH40" s="98"/>
       <c r="BI40" s="15"/>
       <c r="BJ40" s="21"/>
-      <c r="BK40" s="65"/>
-      <c r="BL40" s="65"/>
+      <c r="BK40" s="40"/>
+      <c r="BL40" s="98"/>
       <c r="BM40" s="65"/>
       <c r="BN40" s="79"/>
     </row>
-    <row r="41" spans="1:66" ht="10.199999999999999" thickBot="1">
-      <c r="A41" s="135"/>
-      <c r="B41" s="137"/>
-      <c r="C41" s="140"/>
-      <c r="D41" s="141"/>
-      <c r="E41" s="137"/>
-      <c r="F41" s="143"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="11"/>
-      <c r="S41" s="14"/>
-      <c r="T41" s="20"/>
-      <c r="U41" s="20"/>
-      <c r="V41" s="69"/>
-      <c r="W41" s="69"/>
-      <c r="X41" s="69"/>
-      <c r="Y41" s="69"/>
-      <c r="Z41" s="14"/>
-      <c r="AA41" s="20"/>
-      <c r="AB41" s="20"/>
-      <c r="AC41" s="69"/>
-      <c r="AD41" s="69"/>
-      <c r="AE41" s="69"/>
-      <c r="AF41" s="69"/>
-      <c r="AG41" s="14"/>
-      <c r="AH41" s="20"/>
-      <c r="AI41" s="69"/>
-      <c r="AJ41" s="81"/>
-      <c r="AK41" s="92"/>
-      <c r="AL41" s="69"/>
-      <c r="AM41" s="69"/>
-      <c r="AN41" s="14"/>
-      <c r="AO41" s="20"/>
-      <c r="AP41" s="69"/>
-      <c r="AQ41" s="69"/>
-      <c r="AR41" s="69"/>
-      <c r="AS41" s="69"/>
-      <c r="AT41" s="69"/>
-      <c r="AU41" s="14"/>
-      <c r="AV41" s="20"/>
-      <c r="AW41" s="20"/>
-      <c r="AX41" s="69"/>
-      <c r="AY41" s="69"/>
-      <c r="AZ41" s="69"/>
-      <c r="BA41" s="69"/>
-      <c r="BB41" s="14"/>
-      <c r="BC41" s="20"/>
-      <c r="BD41" s="69"/>
-      <c r="BE41" s="69"/>
-      <c r="BF41" s="69"/>
-      <c r="BG41" s="69"/>
-      <c r="BH41" s="69"/>
-      <c r="BI41" s="14"/>
-      <c r="BJ41" s="20"/>
-      <c r="BK41" s="69"/>
-      <c r="BL41" s="69"/>
-      <c r="BM41" s="69"/>
-      <c r="BN41" s="81"/>
+    <row r="41" spans="1:66">
+      <c r="A41" s="163"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="223"/>
+      <c r="D41" s="224"/>
+      <c r="E41" s="226"/>
+      <c r="F41" s="228"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="63"/>
+      <c r="O41" s="63"/>
+      <c r="P41" s="63"/>
+      <c r="Q41" s="63"/>
+      <c r="R41" s="63"/>
+      <c r="S41" s="13"/>
+      <c r="T41" s="19"/>
+      <c r="U41" s="19"/>
+      <c r="V41" s="63"/>
+      <c r="W41" s="63"/>
+      <c r="X41" s="63"/>
+      <c r="Y41" s="63"/>
+      <c r="Z41" s="13"/>
+      <c r="AA41" s="19"/>
+      <c r="AB41" s="19"/>
+      <c r="AC41" s="63"/>
+      <c r="AD41" s="63"/>
+      <c r="AE41" s="63"/>
+      <c r="AF41" s="63"/>
+      <c r="AG41" s="13"/>
+      <c r="AH41" s="19"/>
+      <c r="AI41" s="63"/>
+      <c r="AJ41" s="80"/>
+      <c r="AK41" s="91"/>
+      <c r="AL41" s="63"/>
+      <c r="AM41" s="63"/>
+      <c r="AN41" s="13"/>
+      <c r="AO41" s="19"/>
+      <c r="AP41" s="63"/>
+      <c r="AQ41" s="63"/>
+      <c r="AR41" s="63"/>
+      <c r="AS41" s="63"/>
+      <c r="AT41" s="63"/>
+      <c r="AU41" s="13"/>
+      <c r="AV41" s="19"/>
+      <c r="AW41" s="19"/>
+      <c r="AX41" s="63"/>
+      <c r="AY41" s="63"/>
+      <c r="AZ41" s="63"/>
+      <c r="BA41" s="63"/>
+      <c r="BB41" s="13"/>
+      <c r="BC41" s="19"/>
+      <c r="BD41" s="101"/>
+      <c r="BE41" s="101"/>
+      <c r="BF41" s="101"/>
+      <c r="BG41" s="101"/>
+      <c r="BH41" s="101"/>
+      <c r="BI41" s="13"/>
+      <c r="BJ41" s="19"/>
+      <c r="BK41" s="101"/>
+      <c r="BL41" s="30"/>
+      <c r="BM41" s="101"/>
+      <c r="BN41" s="140"/>
     </row>
     <row r="42" spans="1:66">
-      <c r="Z42" s="5"/>
-      <c r="AA42" s="5"/>
+      <c r="A42" s="162">
+        <v>14</v>
+      </c>
+      <c r="B42" s="215" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="207" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="208"/>
+      <c r="E42" s="215" t="s">
+        <v>56</v>
+      </c>
+      <c r="F42" s="219"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="21"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="15"/>
+      <c r="T42" s="21"/>
+      <c r="U42" s="21"/>
+      <c r="V42" s="65"/>
+      <c r="W42" s="65"/>
+      <c r="X42" s="65"/>
+      <c r="Y42" s="65"/>
+      <c r="Z42" s="15"/>
+      <c r="AA42" s="21"/>
+      <c r="AB42" s="21"/>
+      <c r="AC42" s="65"/>
+      <c r="AD42" s="65"/>
+      <c r="AE42" s="65"/>
+      <c r="AF42" s="65"/>
+      <c r="AG42" s="15"/>
+      <c r="AH42" s="21"/>
+      <c r="AI42" s="65"/>
+      <c r="AJ42" s="79"/>
+      <c r="AK42" s="90"/>
+      <c r="AL42" s="65"/>
+      <c r="AM42" s="65"/>
+      <c r="AN42" s="15"/>
+      <c r="AO42" s="21"/>
+      <c r="AP42" s="65"/>
+      <c r="AQ42" s="65"/>
+      <c r="AR42" s="65"/>
+      <c r="AS42" s="65"/>
+      <c r="AT42" s="65"/>
+      <c r="AU42" s="15"/>
+      <c r="AV42" s="21"/>
+      <c r="AW42" s="21"/>
+      <c r="AX42" s="65"/>
+      <c r="AY42" s="65"/>
+      <c r="AZ42" s="98"/>
+      <c r="BA42" s="98"/>
+      <c r="BB42" s="15"/>
+      <c r="BC42" s="21"/>
+      <c r="BD42" s="98"/>
+      <c r="BE42" s="98"/>
+      <c r="BF42" s="98"/>
+      <c r="BG42" s="98"/>
+      <c r="BH42" s="98"/>
+      <c r="BI42" s="15"/>
+      <c r="BJ42" s="21"/>
+      <c r="BK42" s="65"/>
+      <c r="BL42" s="65"/>
+      <c r="BM42" s="65"/>
+      <c r="BN42" s="79"/>
     </row>
-    <row r="43" spans="1:66">
-      <c r="A43" s="27"/>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
+    <row r="43" spans="1:66" ht="10.199999999999999" thickBot="1">
+      <c r="A43" s="214"/>
+      <c r="B43" s="216"/>
+      <c r="C43" s="217"/>
+      <c r="D43" s="218"/>
+      <c r="E43" s="216"/>
+      <c r="F43" s="220"/>
+      <c r="G43" s="39"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="11"/>
+      <c r="R43" s="11"/>
+      <c r="S43" s="14"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="20"/>
+      <c r="V43" s="69"/>
+      <c r="W43" s="69"/>
+      <c r="X43" s="69"/>
+      <c r="Y43" s="69"/>
+      <c r="Z43" s="14"/>
+      <c r="AA43" s="20"/>
+      <c r="AB43" s="20"/>
+      <c r="AC43" s="69"/>
+      <c r="AD43" s="69"/>
+      <c r="AE43" s="69"/>
+      <c r="AF43" s="69"/>
+      <c r="AG43" s="14"/>
+      <c r="AH43" s="20"/>
+      <c r="AI43" s="69"/>
+      <c r="AJ43" s="81"/>
+      <c r="AK43" s="92"/>
+      <c r="AL43" s="69"/>
+      <c r="AM43" s="69"/>
+      <c r="AN43" s="14"/>
+      <c r="AO43" s="20"/>
+      <c r="AP43" s="69"/>
+      <c r="AQ43" s="69"/>
+      <c r="AR43" s="69"/>
+      <c r="AS43" s="69"/>
+      <c r="AT43" s="69"/>
+      <c r="AU43" s="14"/>
+      <c r="AV43" s="20"/>
+      <c r="AW43" s="20"/>
+      <c r="AX43" s="69"/>
+      <c r="AY43" s="69"/>
+      <c r="AZ43" s="69"/>
+      <c r="BA43" s="69"/>
+      <c r="BB43" s="14"/>
+      <c r="BC43" s="20"/>
+      <c r="BD43" s="69"/>
+      <c r="BE43" s="69"/>
+      <c r="BF43" s="69"/>
+      <c r="BG43" s="69"/>
+      <c r="BH43" s="69"/>
+      <c r="BI43" s="14"/>
+      <c r="BJ43" s="20"/>
+      <c r="BK43" s="69"/>
+      <c r="BL43" s="69"/>
+      <c r="BM43" s="69"/>
+      <c r="BN43" s="81"/>
     </row>
     <row r="44" spans="1:66">
-      <c r="A44" s="28"/>
-      <c r="B44" s="1" t="s">
+      <c r="Z44" s="5"/>
+      <c r="AA44" s="5"/>
+    </row>
+    <row r="45" spans="1:66">
+      <c r="A45" s="27"/>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:66">
+      <c r="A46" s="28"/>
+      <c r="B46" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="C24:D25"/>
     <mergeCell ref="E24:E25"/>
@@ -6457,21 +6609,51 @@
     <mergeCell ref="C30:D31"/>
     <mergeCell ref="C32:D33"/>
     <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
@@ -6507,54 +6689,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="205" t="s">
+      <c r="B1" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="208" t="s">
+      <c r="C1" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="209"/>
-      <c r="E1" s="214" t="s">
+      <c r="D1" s="151"/>
+      <c r="E1" s="156" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="217" t="s">
+      <c r="F1" s="159" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="199"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
-      <c r="L1" s="200"/>
-      <c r="M1" s="200"/>
-      <c r="N1" s="200"/>
-      <c r="O1" s="200"/>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="200"/>
-      <c r="Y1" s="200"/>
-      <c r="Z1" s="200"/>
-      <c r="AA1" s="200"/>
-      <c r="AB1" s="200"/>
-      <c r="AC1" s="200"/>
-      <c r="AD1" s="201"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="142"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="142"/>
+      <c r="S1" s="142"/>
+      <c r="T1" s="142"/>
+      <c r="U1" s="142"/>
+      <c r="V1" s="142"/>
+      <c r="W1" s="142"/>
+      <c r="X1" s="142"/>
+      <c r="Y1" s="142"/>
+      <c r="Z1" s="142"/>
+      <c r="AA1" s="142"/>
+      <c r="AB1" s="142"/>
+      <c r="AC1" s="142"/>
+      <c r="AD1" s="143"/>
     </row>
     <row r="2" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A2" s="203"/>
-      <c r="B2" s="206"/>
-      <c r="C2" s="210"/>
-      <c r="D2" s="211"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="218"/>
+      <c r="A2" s="145"/>
+      <c r="B2" s="148"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="160"/>
       <c r="G2" s="46">
         <v>22</v>
       </c>
@@ -6629,12 +6811,12 @@
       </c>
     </row>
     <row r="3" spans="1:30" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="204"/>
-      <c r="B3" s="207"/>
-      <c r="C3" s="212"/>
-      <c r="D3" s="213"/>
-      <c r="E3" s="216"/>
-      <c r="F3" s="219"/>
+      <c r="A3" s="146"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="154"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="161"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -6709,20 +6891,20 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A4" s="192">
+      <c r="A4" s="172">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="193" t="s">
+      <c r="C4" s="173" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="194"/>
-      <c r="E4" s="195" t="s">
+      <c r="D4" s="174"/>
+      <c r="E4" s="177" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="197"/>
+      <c r="F4" s="179"/>
       <c r="G4" s="49"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -6745,20 +6927,20 @@
       <c r="Z4" s="12"/>
       <c r="AA4" s="18"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="223" t="s">
+      <c r="AC4" s="232" t="s">
         <v>14</v>
       </c>
-      <c r="AD4" s="220" t="s">
+      <c r="AD4" s="229" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A5" s="152"/>
+      <c r="A5" s="163"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="198"/>
+      <c r="C5" s="175"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="178"/>
+      <c r="F5" s="180"/>
       <c r="G5" s="50"/>
       <c r="H5" s="31"/>
       <c r="I5" s="9"/>
@@ -6781,22 +6963,22 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="9"/>
-      <c r="AC5" s="224"/>
-      <c r="AD5" s="221"/>
+      <c r="AC5" s="233"/>
+      <c r="AD5" s="230"/>
     </row>
     <row r="6" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A6" s="134">
+      <c r="A6" s="162">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="169" t="s">
+      <c r="C6" s="164" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="145"/>
-      <c r="E6" s="188" t="s">
+      <c r="D6" s="165"/>
+      <c r="E6" s="168" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="190"/>
+      <c r="F6" s="170"/>
       <c r="G6" s="51"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -6819,16 +7001,16 @@
       <c r="Z6" s="13"/>
       <c r="AA6" s="19"/>
       <c r="AB6" s="7"/>
-      <c r="AC6" s="224"/>
-      <c r="AD6" s="221"/>
+      <c r="AC6" s="233"/>
+      <c r="AD6" s="230"/>
     </row>
     <row r="7" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A7" s="152"/>
+      <c r="A7" s="163"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="170"/>
-      <c r="D7" s="171"/>
-      <c r="E7" s="189"/>
-      <c r="F7" s="191"/>
+      <c r="C7" s="166"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="171"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="24"/>
@@ -6851,24 +7033,24 @@
       <c r="Z7" s="25"/>
       <c r="AA7" s="26"/>
       <c r="AB7" s="24"/>
-      <c r="AC7" s="224"/>
-      <c r="AD7" s="221"/>
+      <c r="AC7" s="233"/>
+      <c r="AD7" s="230"/>
     </row>
     <row r="8" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A8" s="161">
+      <c r="A8" s="181">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="181" t="s">
+      <c r="C8" s="192" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="182"/>
-      <c r="E8" s="187" t="s">
+      <c r="D8" s="193"/>
+      <c r="E8" s="198" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="176"/>
+      <c r="F8" s="201"/>
       <c r="G8" s="38"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -6891,16 +7073,16 @@
       <c r="Z8" s="15"/>
       <c r="AA8" s="21"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="224"/>
-      <c r="AD8" s="221"/>
+      <c r="AC8" s="233"/>
+      <c r="AD8" s="230"/>
     </row>
     <row r="9" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A9" s="162"/>
+      <c r="A9" s="183"/>
       <c r="B9" s="37"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="186"/>
-      <c r="E9" s="172"/>
-      <c r="F9" s="151"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="197"/>
+      <c r="E9" s="200"/>
+      <c r="F9" s="203"/>
       <c r="G9" s="53"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
@@ -6923,24 +7105,24 @@
       <c r="Z9" s="44"/>
       <c r="AA9" s="45"/>
       <c r="AB9" s="43"/>
-      <c r="AC9" s="224"/>
-      <c r="AD9" s="221"/>
+      <c r="AC9" s="233"/>
+      <c r="AD9" s="230"/>
     </row>
     <row r="10" spans="1:30" ht="12" customHeight="1">
-      <c r="A10" s="173">
+      <c r="A10" s="182">
         <v>4</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="177" t="s">
+      <c r="C10" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="178"/>
-      <c r="E10" s="167" t="s">
+      <c r="D10" s="185"/>
+      <c r="E10" s="188" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="132"/>
+      <c r="F10" s="190"/>
       <c r="G10" s="50"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -6963,16 +7145,16 @@
       <c r="Z10" s="16"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="224"/>
-      <c r="AD10" s="221"/>
+      <c r="AC10" s="233"/>
+      <c r="AD10" s="230"/>
     </row>
     <row r="11" spans="1:30" ht="12" customHeight="1">
-      <c r="A11" s="162"/>
+      <c r="A11" s="183"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="179"/>
-      <c r="D11" s="180"/>
-      <c r="E11" s="149"/>
-      <c r="F11" s="133"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="189"/>
+      <c r="F11" s="191"/>
       <c r="G11" s="50"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -6995,22 +7177,22 @@
       <c r="Z11" s="16"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="224"/>
-      <c r="AD11" s="221"/>
+      <c r="AC11" s="233"/>
+      <c r="AD11" s="230"/>
     </row>
     <row r="12" spans="1:30" ht="12" customHeight="1">
-      <c r="A12" s="161">
+      <c r="A12" s="181">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="169" t="s">
+      <c r="C12" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="145"/>
-      <c r="E12" s="166" t="s">
+      <c r="D12" s="165"/>
+      <c r="E12" s="199" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="150"/>
+      <c r="F12" s="202"/>
       <c r="G12" s="51"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -7033,16 +7215,16 @@
       <c r="Z12" s="13"/>
       <c r="AA12" s="19"/>
       <c r="AB12" s="7"/>
-      <c r="AC12" s="224"/>
-      <c r="AD12" s="221"/>
+      <c r="AC12" s="233"/>
+      <c r="AD12" s="230"/>
     </row>
     <row r="13" spans="1:30" ht="12" customHeight="1">
-      <c r="A13" s="173"/>
+      <c r="A13" s="182"/>
       <c r="B13" s="36"/>
-      <c r="C13" s="174"/>
-      <c r="D13" s="175"/>
-      <c r="E13" s="167"/>
-      <c r="F13" s="132"/>
+      <c r="C13" s="204"/>
+      <c r="D13" s="205"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="190"/>
       <c r="G13" s="52"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
@@ -7065,24 +7247,24 @@
       <c r="Z13" s="25"/>
       <c r="AA13" s="26"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="224"/>
-      <c r="AD13" s="221"/>
+      <c r="AC13" s="233"/>
+      <c r="AD13" s="230"/>
     </row>
     <row r="14" spans="1:30" ht="12" customHeight="1">
-      <c r="A14" s="168">
+      <c r="A14" s="206">
         <v>6</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="138" t="s">
+      <c r="C14" s="207" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="139"/>
-      <c r="E14" s="163" t="s">
+      <c r="D14" s="208"/>
+      <c r="E14" s="209" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="176"/>
+      <c r="F14" s="201"/>
       <c r="G14" s="38"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -7105,16 +7287,16 @@
       <c r="Z14" s="15"/>
       <c r="AA14" s="21"/>
       <c r="AB14" s="6"/>
-      <c r="AC14" s="224"/>
-      <c r="AD14" s="221"/>
+      <c r="AC14" s="233"/>
+      <c r="AD14" s="230"/>
     </row>
     <row r="15" spans="1:30" ht="12" customHeight="1">
-      <c r="A15" s="168"/>
+      <c r="A15" s="206"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="146"/>
-      <c r="D15" s="147"/>
-      <c r="E15" s="149"/>
-      <c r="F15" s="133"/>
+      <c r="C15" s="175"/>
+      <c r="D15" s="176"/>
+      <c r="E15" s="189"/>
+      <c r="F15" s="191"/>
       <c r="G15" s="52"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
@@ -7137,22 +7319,22 @@
       <c r="Z15" s="25"/>
       <c r="AA15" s="26"/>
       <c r="AB15" s="24"/>
-      <c r="AC15" s="224"/>
-      <c r="AD15" s="221"/>
+      <c r="AC15" s="233"/>
+      <c r="AD15" s="230"/>
     </row>
     <row r="16" spans="1:30" ht="12" customHeight="1">
-      <c r="A16" s="168">
+      <c r="A16" s="206">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="169" t="s">
+      <c r="C16" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="145"/>
-      <c r="E16" s="148" t="s">
+      <c r="D16" s="165"/>
+      <c r="E16" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="150"/>
+      <c r="F16" s="202"/>
       <c r="G16" s="51"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -7175,16 +7357,16 @@
       <c r="Z16" s="13"/>
       <c r="AA16" s="19"/>
       <c r="AB16" s="7"/>
-      <c r="AC16" s="224"/>
-      <c r="AD16" s="221"/>
+      <c r="AC16" s="233"/>
+      <c r="AD16" s="230"/>
     </row>
     <row r="17" spans="1:30" ht="12" customHeight="1">
-      <c r="A17" s="168"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="146"/>
-      <c r="D17" s="147"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="133"/>
+      <c r="C17" s="175"/>
+      <c r="D17" s="176"/>
+      <c r="E17" s="189"/>
+      <c r="F17" s="191"/>
       <c r="G17" s="52"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -7207,22 +7389,22 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="224"/>
-      <c r="AD17" s="221"/>
+      <c r="AC17" s="233"/>
+      <c r="AD17" s="230"/>
     </row>
     <row r="18" spans="1:30" ht="12" customHeight="1">
-      <c r="A18" s="168">
+      <c r="A18" s="206">
         <v>8</v>
       </c>
       <c r="B18" s="36"/>
-      <c r="C18" s="169" t="s">
+      <c r="C18" s="164" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="145"/>
-      <c r="E18" s="148" t="s">
+      <c r="D18" s="165"/>
+      <c r="E18" s="210" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="150"/>
+      <c r="F18" s="202"/>
       <c r="G18" s="52"/>
       <c r="H18" s="24"/>
       <c r="I18" s="24"/>
@@ -7245,16 +7427,16 @@
       <c r="Z18" s="25"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="224"/>
-      <c r="AD18" s="221"/>
+      <c r="AC18" s="233"/>
+      <c r="AD18" s="230"/>
     </row>
     <row r="19" spans="1:30" ht="12" customHeight="1">
-      <c r="A19" s="168"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="37"/>
-      <c r="C19" s="170"/>
-      <c r="D19" s="171"/>
-      <c r="E19" s="172"/>
-      <c r="F19" s="151"/>
+      <c r="C19" s="166"/>
+      <c r="D19" s="167"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="203"/>
       <c r="G19" s="54"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -7277,24 +7459,24 @@
       <c r="Z19" s="17"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="224"/>
-      <c r="AD19" s="221"/>
+      <c r="AC19" s="233"/>
+      <c r="AD19" s="230"/>
     </row>
     <row r="20" spans="1:30" ht="12" customHeight="1">
-      <c r="A20" s="161">
+      <c r="A20" s="181">
         <v>9</v>
       </c>
       <c r="B20" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="138" t="s">
+      <c r="C20" s="207" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="139"/>
-      <c r="E20" s="163" t="s">
+      <c r="D20" s="208"/>
+      <c r="E20" s="209" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="176"/>
+      <c r="F20" s="201"/>
       <c r="G20" s="38"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -7317,18 +7499,18 @@
       <c r="Z20" s="15"/>
       <c r="AA20" s="21"/>
       <c r="AB20" s="6"/>
-      <c r="AC20" s="224"/>
-      <c r="AD20" s="221"/>
+      <c r="AC20" s="233"/>
+      <c r="AD20" s="230"/>
     </row>
     <row r="21" spans="1:30" ht="12" customHeight="1">
-      <c r="A21" s="162"/>
+      <c r="A21" s="183"/>
       <c r="B21" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="146"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="133"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="176"/>
+      <c r="E21" s="189"/>
+      <c r="F21" s="191"/>
       <c r="G21" s="51"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -7351,22 +7533,22 @@
       <c r="Z21" s="13"/>
       <c r="AA21" s="19"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="224"/>
-      <c r="AD21" s="221"/>
+      <c r="AC21" s="233"/>
+      <c r="AD21" s="230"/>
     </row>
     <row r="22" spans="1:30" ht="12" customHeight="1">
-      <c r="A22" s="161">
+      <c r="A22" s="181">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="144" t="s">
+      <c r="C22" s="213" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="145"/>
-      <c r="E22" s="148" t="s">
+      <c r="D22" s="165"/>
+      <c r="E22" s="210" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="150"/>
+      <c r="F22" s="202"/>
       <c r="G22" s="51"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -7389,16 +7571,16 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="19"/>
       <c r="AB22" s="7"/>
-      <c r="AC22" s="224"/>
-      <c r="AD22" s="221"/>
+      <c r="AC22" s="233"/>
+      <c r="AD22" s="230"/>
     </row>
     <row r="23" spans="1:30" ht="12" customHeight="1">
-      <c r="A23" s="162"/>
+      <c r="A23" s="183"/>
       <c r="B23" s="36"/>
-      <c r="C23" s="146"/>
-      <c r="D23" s="147"/>
-      <c r="E23" s="149"/>
-      <c r="F23" s="133"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="176"/>
+      <c r="E23" s="189"/>
+      <c r="F23" s="191"/>
       <c r="G23" s="51"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -7421,22 +7603,22 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="19"/>
       <c r="AB23" s="7"/>
-      <c r="AC23" s="224"/>
-      <c r="AD23" s="221"/>
+      <c r="AC23" s="233"/>
+      <c r="AD23" s="230"/>
     </row>
     <row r="24" spans="1:30" ht="12" customHeight="1">
-      <c r="A24" s="161">
+      <c r="A24" s="181">
         <v>11</v>
       </c>
       <c r="B24" s="36"/>
-      <c r="C24" s="144" t="s">
+      <c r="C24" s="213" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="145"/>
-      <c r="E24" s="148" t="s">
+      <c r="D24" s="165"/>
+      <c r="E24" s="210" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="150"/>
+      <c r="F24" s="202"/>
       <c r="G24" s="52"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -7459,16 +7641,16 @@
       <c r="Z24" s="25"/>
       <c r="AA24" s="26"/>
       <c r="AB24" s="24"/>
-      <c r="AC24" s="224"/>
-      <c r="AD24" s="221"/>
+      <c r="AC24" s="233"/>
+      <c r="AD24" s="230"/>
     </row>
     <row r="25" spans="1:30" ht="12" customHeight="1">
-      <c r="A25" s="162"/>
+      <c r="A25" s="183"/>
       <c r="B25" s="37"/>
-      <c r="C25" s="146"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="149"/>
-      <c r="F25" s="151"/>
+      <c r="C25" s="175"/>
+      <c r="D25" s="176"/>
+      <c r="E25" s="189"/>
+      <c r="F25" s="203"/>
       <c r="G25" s="54"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -7491,24 +7673,24 @@
       <c r="Z25" s="17"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="224"/>
-      <c r="AD25" s="221"/>
+      <c r="AC25" s="233"/>
+      <c r="AD25" s="230"/>
     </row>
     <row r="26" spans="1:30" ht="12" customHeight="1">
-      <c r="A26" s="134">
+      <c r="A26" s="162">
         <v>12</v>
       </c>
       <c r="B26" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="153" t="s">
+      <c r="C26" s="221" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="154"/>
-      <c r="E26" s="157" t="s">
+      <c r="D26" s="222"/>
+      <c r="E26" s="225" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="159"/>
+      <c r="F26" s="227"/>
       <c r="G26" s="38"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -7531,16 +7713,16 @@
       <c r="Z26" s="15"/>
       <c r="AA26" s="21"/>
       <c r="AB26" s="6"/>
-      <c r="AC26" s="224"/>
-      <c r="AD26" s="221"/>
+      <c r="AC26" s="233"/>
+      <c r="AD26" s="230"/>
     </row>
     <row r="27" spans="1:30" ht="12" customHeight="1">
-      <c r="A27" s="152"/>
+      <c r="A27" s="163"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="155"/>
-      <c r="D27" s="156"/>
-      <c r="E27" s="158"/>
-      <c r="F27" s="160"/>
+      <c r="C27" s="223"/>
+      <c r="D27" s="224"/>
+      <c r="E27" s="226"/>
+      <c r="F27" s="228"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -7563,24 +7745,24 @@
       <c r="Z27" s="13"/>
       <c r="AA27" s="19"/>
       <c r="AB27" s="7"/>
-      <c r="AC27" s="224"/>
-      <c r="AD27" s="221"/>
+      <c r="AC27" s="233"/>
+      <c r="AD27" s="230"/>
     </row>
     <row r="28" spans="1:30" ht="12" customHeight="1">
-      <c r="A28" s="134">
+      <c r="A28" s="162">
         <v>14</v>
       </c>
-      <c r="B28" s="136" t="s">
+      <c r="B28" s="215" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="138" t="s">
+      <c r="C28" s="207" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="139"/>
-      <c r="E28" s="136" t="s">
+      <c r="D28" s="208"/>
+      <c r="E28" s="215" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="142"/>
+      <c r="F28" s="219"/>
       <c r="G28" s="38"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -7603,16 +7785,16 @@
       <c r="Z28" s="15"/>
       <c r="AA28" s="21"/>
       <c r="AB28" s="40"/>
-      <c r="AC28" s="224"/>
-      <c r="AD28" s="221"/>
+      <c r="AC28" s="233"/>
+      <c r="AD28" s="230"/>
     </row>
     <row r="29" spans="1:30" ht="12" customHeight="1" thickBot="1">
-      <c r="A29" s="135"/>
-      <c r="B29" s="137"/>
-      <c r="C29" s="140"/>
-      <c r="D29" s="141"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="143"/>
+      <c r="A29" s="214"/>
+      <c r="B29" s="216"/>
+      <c r="C29" s="217"/>
+      <c r="D29" s="218"/>
+      <c r="E29" s="216"/>
+      <c r="F29" s="220"/>
       <c r="G29" s="39"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -7635,8 +7817,8 @@
       <c r="Z29" s="14"/>
       <c r="AA29" s="20"/>
       <c r="AB29" s="11"/>
-      <c r="AC29" s="225"/>
-      <c r="AD29" s="222"/>
+      <c r="AC29" s="234"/>
+      <c r="AD29" s="231"/>
     </row>
     <row r="30" spans="1:30">
       <c r="Z30" s="5"/>
@@ -7656,45 +7838,12 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G1:AD1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
     <mergeCell ref="AD4:AD29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C6:D7"/>
@@ -7711,12 +7860,45 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="C10:D11"/>
-    <mergeCell ref="G1:AD1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/システム開発演習/000-要件定義/003-WBS.xlsx
+++ b/システム開発演習/000-要件定義/003-WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\システム開発演習\000-要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D999765-83B9-437D-B242-D9F15A7870F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D587EE37-7E74-47C9-89C7-02229ADFD7D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1772,7 +1772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2188,6 +2188,216 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2251,207 +2461,6 @@
     <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2470,13 +2479,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3196,94 +3199,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="144" t="s">
+      <c r="A1" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="217" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="220" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="151"/>
-      <c r="E1" s="156" t="s">
+      <c r="D1" s="221"/>
+      <c r="E1" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="159" t="s">
+      <c r="F1" s="229" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="141">
+      <c r="G1" s="211">
         <v>45536</v>
       </c>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="142"/>
-      <c r="L1" s="142"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
-      <c r="R1" s="142"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="142"/>
-      <c r="V1" s="142"/>
-      <c r="W1" s="142"/>
-      <c r="X1" s="142"/>
-      <c r="Y1" s="142"/>
-      <c r="Z1" s="142"/>
-      <c r="AA1" s="142"/>
-      <c r="AB1" s="142"/>
-      <c r="AC1" s="142"/>
-      <c r="AD1" s="142"/>
-      <c r="AE1" s="142"/>
-      <c r="AF1" s="142"/>
-      <c r="AG1" s="142"/>
-      <c r="AH1" s="142"/>
-      <c r="AI1" s="142"/>
-      <c r="AJ1" s="143"/>
-      <c r="AK1" s="141">
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="212"/>
+      <c r="S1" s="212"/>
+      <c r="T1" s="212"/>
+      <c r="U1" s="212"/>
+      <c r="V1" s="212"/>
+      <c r="W1" s="212"/>
+      <c r="X1" s="212"/>
+      <c r="Y1" s="212"/>
+      <c r="Z1" s="212"/>
+      <c r="AA1" s="212"/>
+      <c r="AB1" s="212"/>
+      <c r="AC1" s="212"/>
+      <c r="AD1" s="212"/>
+      <c r="AE1" s="212"/>
+      <c r="AF1" s="212"/>
+      <c r="AG1" s="212"/>
+      <c r="AH1" s="212"/>
+      <c r="AI1" s="212"/>
+      <c r="AJ1" s="213"/>
+      <c r="AK1" s="211">
         <v>45566</v>
       </c>
-      <c r="AL1" s="142"/>
-      <c r="AM1" s="142"/>
-      <c r="AN1" s="142"/>
-      <c r="AO1" s="142"/>
-      <c r="AP1" s="142"/>
-      <c r="AQ1" s="142"/>
-      <c r="AR1" s="142"/>
-      <c r="AS1" s="142"/>
-      <c r="AT1" s="142"/>
-      <c r="AU1" s="142"/>
-      <c r="AV1" s="142"/>
-      <c r="AW1" s="142"/>
-      <c r="AX1" s="142"/>
-      <c r="AY1" s="142"/>
-      <c r="AZ1" s="142"/>
-      <c r="BA1" s="142"/>
-      <c r="BB1" s="142"/>
-      <c r="BC1" s="142"/>
-      <c r="BD1" s="142"/>
-      <c r="BE1" s="142"/>
-      <c r="BF1" s="142"/>
-      <c r="BG1" s="142"/>
-      <c r="BH1" s="142"/>
-      <c r="BI1" s="142"/>
-      <c r="BJ1" s="142"/>
-      <c r="BK1" s="142"/>
-      <c r="BL1" s="142"/>
-      <c r="BM1" s="142"/>
-      <c r="BN1" s="143"/>
+      <c r="AL1" s="212"/>
+      <c r="AM1" s="212"/>
+      <c r="AN1" s="212"/>
+      <c r="AO1" s="212"/>
+      <c r="AP1" s="212"/>
+      <c r="AQ1" s="212"/>
+      <c r="AR1" s="212"/>
+      <c r="AS1" s="212"/>
+      <c r="AT1" s="212"/>
+      <c r="AU1" s="212"/>
+      <c r="AV1" s="212"/>
+      <c r="AW1" s="212"/>
+      <c r="AX1" s="212"/>
+      <c r="AY1" s="212"/>
+      <c r="AZ1" s="212"/>
+      <c r="BA1" s="212"/>
+      <c r="BB1" s="212"/>
+      <c r="BC1" s="212"/>
+      <c r="BD1" s="212"/>
+      <c r="BE1" s="212"/>
+      <c r="BF1" s="212"/>
+      <c r="BG1" s="212"/>
+      <c r="BH1" s="212"/>
+      <c r="BI1" s="212"/>
+      <c r="BJ1" s="212"/>
+      <c r="BK1" s="212"/>
+      <c r="BL1" s="212"/>
+      <c r="BM1" s="212"/>
+      <c r="BN1" s="213"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="145"/>
-      <c r="B2" s="148"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="160"/>
+      <c r="A2" s="215"/>
+      <c r="B2" s="218"/>
+      <c r="C2" s="222"/>
+      <c r="D2" s="223"/>
+      <c r="E2" s="227"/>
+      <c r="F2" s="230"/>
       <c r="G2" s="46">
         <v>45537</v>
       </c>
@@ -3525,12 +3528,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="146"/>
-      <c r="B3" s="149"/>
-      <c r="C3" s="154"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="161"/>
+      <c r="A3" s="216"/>
+      <c r="B3" s="219"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
+      <c r="E3" s="228"/>
+      <c r="F3" s="231"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -3713,20 +3716,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="172">
+      <c r="A4" s="204">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="173" t="s">
+      <c r="C4" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="174"/>
-      <c r="E4" s="177" t="s">
+      <c r="D4" s="206"/>
+      <c r="E4" s="207" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="179"/>
+      <c r="F4" s="209"/>
       <c r="G4" s="95"/>
       <c r="H4" s="29"/>
       <c r="I4" s="125"/>
@@ -3789,12 +3792,12 @@
       <c r="BN4" s="71"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="163"/>
+      <c r="A5" s="164"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="175"/>
-      <c r="D5" s="176"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="180"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="210"/>
       <c r="G5" s="96"/>
       <c r="H5" s="31"/>
       <c r="I5" s="97"/>
@@ -3857,18 +3860,18 @@
       <c r="BN5" s="72"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="162">
+      <c r="A6" s="146">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="164" t="s">
+      <c r="C6" s="182" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="165"/>
-      <c r="E6" s="168" t="s">
+      <c r="D6" s="157"/>
+      <c r="E6" s="200" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="170"/>
+      <c r="F6" s="202"/>
       <c r="G6" s="51"/>
       <c r="H6" s="63"/>
       <c r="I6" s="30"/>
@@ -3931,12 +3934,12 @@
       <c r="BN6" s="73"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="163"/>
+      <c r="A7" s="164"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="166"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="169"/>
-      <c r="F7" s="171"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="203"/>
       <c r="G7" s="52"/>
       <c r="H7" s="64"/>
       <c r="I7" s="32"/>
@@ -3999,20 +4002,20 @@
       <c r="BN7" s="74"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="181">
+      <c r="A8" s="173">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="192" t="s">
+      <c r="C8" s="193" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="193"/>
-      <c r="E8" s="198" t="s">
+      <c r="D8" s="194"/>
+      <c r="E8" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="201"/>
+      <c r="F8" s="188"/>
       <c r="G8" s="38"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65"/>
@@ -4075,12 +4078,12 @@
       <c r="BN8" s="75"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="182"/>
+      <c r="A9" s="186"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="184"/>
-      <c r="D9" s="185"/>
-      <c r="E9" s="188"/>
-      <c r="F9" s="190"/>
+      <c r="C9" s="189"/>
+      <c r="D9" s="190"/>
+      <c r="E9" s="161"/>
+      <c r="F9" s="144"/>
       <c r="G9" s="104"/>
       <c r="H9" s="105"/>
       <c r="I9" s="105"/>
@@ -4143,16 +4146,16 @@
       <c r="BN9" s="110"/>
     </row>
     <row r="10" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A10" s="182"/>
+      <c r="A10" s="186"/>
       <c r="B10" s="36"/>
-      <c r="C10" s="194" t="s">
+      <c r="C10" s="195" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="195"/>
-      <c r="E10" s="199" t="s">
+      <c r="D10" s="196"/>
+      <c r="E10" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="202"/>
+      <c r="F10" s="162"/>
       <c r="G10" s="115"/>
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
@@ -4215,12 +4218,12 @@
       <c r="BN10" s="73"/>
     </row>
     <row r="11" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A11" s="182"/>
+      <c r="A11" s="186"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="189"/>
-      <c r="F11" s="191"/>
+      <c r="C11" s="191"/>
+      <c r="D11" s="192"/>
+      <c r="E11" s="177"/>
+      <c r="F11" s="145"/>
       <c r="G11" s="104"/>
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
@@ -4283,16 +4286,16 @@
       <c r="BN11" s="110"/>
     </row>
     <row r="12" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A12" s="182"/>
+      <c r="A12" s="186"/>
       <c r="B12" s="36"/>
-      <c r="C12" s="184" t="s">
+      <c r="C12" s="189" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="185"/>
-      <c r="E12" s="188" t="s">
+      <c r="D12" s="190"/>
+      <c r="E12" s="161" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="190"/>
+      <c r="F12" s="144"/>
       <c r="G12" s="115"/>
       <c r="H12" s="62"/>
       <c r="I12" s="62"/>
@@ -4357,12 +4360,12 @@
       <c r="BN12" s="73"/>
     </row>
     <row r="13" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A13" s="183"/>
+      <c r="A13" s="174"/>
       <c r="B13" s="37"/>
-      <c r="C13" s="196"/>
-      <c r="D13" s="197"/>
-      <c r="E13" s="200"/>
-      <c r="F13" s="203"/>
+      <c r="C13" s="197"/>
+      <c r="D13" s="198"/>
+      <c r="E13" s="185"/>
+      <c r="F13" s="163"/>
       <c r="G13" s="53"/>
       <c r="H13" s="66"/>
       <c r="I13" s="66"/>
@@ -4425,20 +4428,20 @@
       <c r="BN13" s="76"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="182">
+      <c r="A14" s="186">
         <v>4</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="184" t="s">
+      <c r="C14" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="185"/>
-      <c r="E14" s="188" t="s">
+      <c r="D14" s="190"/>
+      <c r="E14" s="161" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="190"/>
+      <c r="F14" s="144"/>
       <c r="G14" s="50"/>
       <c r="H14" s="62"/>
       <c r="I14" s="62"/>
@@ -4503,12 +4506,12 @@
       <c r="BN14" s="72"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="183"/>
+      <c r="A15" s="174"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="186"/>
-      <c r="D15" s="187"/>
-      <c r="E15" s="189"/>
-      <c r="F15" s="191"/>
+      <c r="C15" s="191"/>
+      <c r="D15" s="192"/>
+      <c r="E15" s="177"/>
+      <c r="F15" s="145"/>
       <c r="G15" s="50"/>
       <c r="H15" s="62"/>
       <c r="I15" s="62"/>
@@ -4571,18 +4574,18 @@
       <c r="BN15" s="72"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="181">
+      <c r="A16" s="173">
         <v>5</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="164" t="s">
+      <c r="C16" s="182" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="165"/>
-      <c r="E16" s="199" t="s">
+      <c r="D16" s="157"/>
+      <c r="E16" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="202"/>
+      <c r="F16" s="162"/>
       <c r="G16" s="51"/>
       <c r="H16" s="63"/>
       <c r="I16" s="63"/>
@@ -4645,12 +4648,12 @@
       <c r="BN16" s="73"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="182"/>
+      <c r="A17" s="186"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="204"/>
-      <c r="D17" s="205"/>
-      <c r="E17" s="188"/>
-      <c r="F17" s="190"/>
+      <c r="C17" s="187"/>
+      <c r="D17" s="159"/>
+      <c r="E17" s="161"/>
+      <c r="F17" s="144"/>
       <c r="G17" s="52"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
@@ -4713,20 +4716,20 @@
       <c r="BN17" s="74"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="206">
+      <c r="A18" s="181">
         <v>6</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="207" t="s">
+      <c r="C18" s="150" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="208"/>
-      <c r="E18" s="209" t="s">
+      <c r="D18" s="151"/>
+      <c r="E18" s="176" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="201"/>
+      <c r="F18" s="188"/>
       <c r="G18" s="38"/>
       <c r="H18" s="65"/>
       <c r="I18" s="65"/>
@@ -4789,12 +4792,12 @@
       <c r="BN18" s="75"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="206"/>
+      <c r="A19" s="181"/>
       <c r="B19" s="36"/>
-      <c r="C19" s="175"/>
-      <c r="D19" s="176"/>
-      <c r="E19" s="189"/>
-      <c r="F19" s="191"/>
+      <c r="C19" s="158"/>
+      <c r="D19" s="175"/>
+      <c r="E19" s="177"/>
+      <c r="F19" s="145"/>
       <c r="G19" s="52"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
@@ -4857,18 +4860,18 @@
       <c r="BN19" s="74"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="206">
+      <c r="A20" s="181">
         <v>7</v>
       </c>
       <c r="B20" s="36"/>
-      <c r="C20" s="164" t="s">
+      <c r="C20" s="182" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="165"/>
-      <c r="E20" s="210" t="s">
+      <c r="D20" s="157"/>
+      <c r="E20" s="160" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="202"/>
+      <c r="F20" s="162"/>
       <c r="G20" s="51"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -4931,12 +4934,12 @@
       <c r="BN20" s="73"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="206"/>
+      <c r="A21" s="181"/>
       <c r="B21" s="36"/>
-      <c r="C21" s="175"/>
-      <c r="D21" s="176"/>
-      <c r="E21" s="189"/>
-      <c r="F21" s="191"/>
+      <c r="C21" s="158"/>
+      <c r="D21" s="175"/>
+      <c r="E21" s="177"/>
+      <c r="F21" s="145"/>
       <c r="G21" s="52"/>
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
@@ -4999,18 +5002,18 @@
       <c r="BN21" s="74"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="206">
+      <c r="A22" s="181">
         <v>8</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="164" t="s">
+      <c r="C22" s="182" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="165"/>
-      <c r="E22" s="210" t="s">
+      <c r="D22" s="157"/>
+      <c r="E22" s="160" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="202"/>
+      <c r="F22" s="162"/>
       <c r="G22" s="52"/>
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
@@ -5073,12 +5076,12 @@
       <c r="BN22" s="77"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="206"/>
+      <c r="A23" s="181"/>
       <c r="B23" s="37"/>
-      <c r="C23" s="166"/>
-      <c r="D23" s="167"/>
-      <c r="E23" s="200"/>
-      <c r="F23" s="203"/>
+      <c r="C23" s="183"/>
+      <c r="D23" s="184"/>
+      <c r="E23" s="185"/>
+      <c r="F23" s="163"/>
       <c r="G23" s="54"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -5141,20 +5144,20 @@
       <c r="BN23" s="78"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="181">
+      <c r="A24" s="173">
         <v>9</v>
       </c>
       <c r="B24" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="207" t="s">
+      <c r="C24" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="208"/>
-      <c r="E24" s="209" t="s">
+      <c r="D24" s="151"/>
+      <c r="E24" s="176" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="211"/>
+      <c r="F24" s="178"/>
       <c r="G24" s="38"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -5217,12 +5220,12 @@
       <c r="BN24" s="79"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="183"/>
+      <c r="A25" s="174"/>
       <c r="B25" s="36"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="176"/>
-      <c r="E25" s="189"/>
-      <c r="F25" s="212"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="175"/>
+      <c r="E25" s="177"/>
+      <c r="F25" s="179"/>
       <c r="G25" s="51"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -5289,14 +5292,14 @@
         <v>10</v>
       </c>
       <c r="B26" s="36"/>
-      <c r="C26" s="213" t="s">
+      <c r="C26" s="156" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="165"/>
-      <c r="E26" s="199" t="s">
+      <c r="D26" s="157"/>
+      <c r="E26" s="180" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="202"/>
+      <c r="F26" s="162"/>
       <c r="G26" s="51"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -5361,10 +5364,10 @@
     <row r="27" spans="1:66" ht="12" customHeight="1">
       <c r="A27" s="119"/>
       <c r="B27" s="103"/>
-      <c r="C27" s="175"/>
-      <c r="D27" s="176"/>
-      <c r="E27" s="188"/>
-      <c r="F27" s="190"/>
+      <c r="C27" s="158"/>
+      <c r="D27" s="175"/>
+      <c r="E27" s="161"/>
+      <c r="F27" s="144"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -5429,14 +5432,14 @@
     <row r="28" spans="1:66" ht="12" customHeight="1">
       <c r="A28" s="118"/>
       <c r="B28" s="36"/>
-      <c r="C28" s="213" t="s">
+      <c r="C28" s="156" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="165"/>
-      <c r="E28" s="188" t="s">
+      <c r="D28" s="157"/>
+      <c r="E28" s="161" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="190"/>
+      <c r="F28" s="144"/>
       <c r="G28" s="51"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -5501,10 +5504,10 @@
     <row r="29" spans="1:66" ht="12" customHeight="1">
       <c r="A29" s="118"/>
       <c r="B29" s="36"/>
-      <c r="C29" s="175"/>
-      <c r="D29" s="176"/>
-      <c r="E29" s="188"/>
-      <c r="F29" s="190"/>
+      <c r="C29" s="158"/>
+      <c r="D29" s="175"/>
+      <c r="E29" s="161"/>
+      <c r="F29" s="144"/>
       <c r="G29" s="51"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -5569,14 +5572,14 @@
     <row r="30" spans="1:66" ht="12" customHeight="1">
       <c r="A30" s="118"/>
       <c r="B30" s="36"/>
-      <c r="C30" s="213" t="s">
+      <c r="C30" s="156" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="165"/>
-      <c r="E30" s="188" t="s">
+      <c r="D30" s="157"/>
+      <c r="E30" s="161" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="190"/>
+      <c r="F30" s="144"/>
       <c r="G30" s="51"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -5641,10 +5644,10 @@
     <row r="31" spans="1:66" ht="12" customHeight="1">
       <c r="A31" s="118"/>
       <c r="B31" s="36"/>
-      <c r="C31" s="175"/>
-      <c r="D31" s="176"/>
-      <c r="E31" s="188"/>
-      <c r="F31" s="190"/>
+      <c r="C31" s="158"/>
+      <c r="D31" s="175"/>
+      <c r="E31" s="161"/>
+      <c r="F31" s="144"/>
       <c r="G31" s="51"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -5711,14 +5714,14 @@
         <v>11</v>
       </c>
       <c r="B32" s="36"/>
-      <c r="C32" s="213" t="s">
+      <c r="C32" s="156" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="165"/>
-      <c r="E32" s="188" t="s">
+      <c r="D32" s="157"/>
+      <c r="E32" s="161" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="190"/>
+      <c r="F32" s="144"/>
       <c r="G32" s="51"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -5783,10 +5786,10 @@
     <row r="33" spans="1:66" ht="12" customHeight="1">
       <c r="A33" s="119"/>
       <c r="B33" s="103"/>
-      <c r="C33" s="175"/>
-      <c r="D33" s="176"/>
-      <c r="E33" s="189"/>
-      <c r="F33" s="191"/>
+      <c r="C33" s="158"/>
+      <c r="D33" s="175"/>
+      <c r="E33" s="177"/>
+      <c r="F33" s="145"/>
       <c r="G33" s="51"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -5851,14 +5854,14 @@
     <row r="34" spans="1:66" ht="9.6" customHeight="1">
       <c r="A34" s="119"/>
       <c r="B34" s="103"/>
-      <c r="C34" s="213" t="s">
+      <c r="C34" s="156" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="165"/>
-      <c r="E34" s="210" t="s">
+      <c r="D34" s="157"/>
+      <c r="E34" s="160" t="s">
         <v>56</v>
       </c>
-      <c r="F34" s="202"/>
+      <c r="F34" s="162"/>
       <c r="G34" s="51"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -5923,10 +5926,10 @@
     <row r="35" spans="1:66">
       <c r="A35" s="119"/>
       <c r="B35" s="103"/>
-      <c r="C35" s="175"/>
-      <c r="D35" s="176"/>
-      <c r="E35" s="189"/>
-      <c r="F35" s="191"/>
+      <c r="C35" s="158"/>
+      <c r="D35" s="175"/>
+      <c r="E35" s="177"/>
+      <c r="F35" s="145"/>
       <c r="G35" s="51"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -5991,14 +5994,14 @@
     <row r="36" spans="1:66">
       <c r="A36" s="120"/>
       <c r="B36" s="103"/>
-      <c r="C36" s="213" t="s">
+      <c r="C36" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="165"/>
-      <c r="E36" s="210" t="s">
+      <c r="D36" s="157"/>
+      <c r="E36" s="160" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="202"/>
+      <c r="F36" s="162"/>
       <c r="G36" s="52"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
@@ -6063,10 +6066,10 @@
     <row r="37" spans="1:66">
       <c r="A37" s="117"/>
       <c r="B37" s="37"/>
-      <c r="C37" s="175"/>
-      <c r="D37" s="205"/>
-      <c r="E37" s="188"/>
-      <c r="F37" s="203"/>
+      <c r="C37" s="158"/>
+      <c r="D37" s="159"/>
+      <c r="E37" s="161"/>
+      <c r="F37" s="163"/>
       <c r="G37" s="54"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
@@ -6172,8 +6175,8 @@
       <c r="AG38" s="106"/>
       <c r="AH38" s="107"/>
       <c r="AI38" s="105"/>
-      <c r="AJ38" s="235"/>
-      <c r="AK38" s="236"/>
+      <c r="AJ38" s="141"/>
+      <c r="AK38" s="142"/>
       <c r="AL38" s="105"/>
       <c r="AM38" s="105"/>
       <c r="AN38" s="106"/>
@@ -6195,14 +6198,14 @@
       <c r="BD38" s="105"/>
       <c r="BE38" s="105"/>
       <c r="BF38" s="105"/>
-      <c r="BG38" s="237"/>
-      <c r="BH38" s="237"/>
+      <c r="BG38" s="143"/>
+      <c r="BH38" s="143"/>
       <c r="BI38" s="106"/>
       <c r="BJ38" s="107"/>
       <c r="BK38" s="105"/>
       <c r="BL38" s="105"/>
       <c r="BM38" s="105"/>
-      <c r="BN38" s="235"/>
+      <c r="BN38" s="141"/>
     </row>
     <row r="39" spans="1:66">
       <c r="A39" s="120"/>
@@ -6273,20 +6276,20 @@
       <c r="BN39" s="78"/>
     </row>
     <row r="40" spans="1:66">
-      <c r="A40" s="162">
+      <c r="A40" s="146">
         <v>13</v>
       </c>
       <c r="B40" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="221" t="s">
+      <c r="C40" s="165" t="s">
         <v>34</v>
       </c>
-      <c r="D40" s="222"/>
-      <c r="E40" s="225" t="s">
+      <c r="D40" s="166"/>
+      <c r="E40" s="169" t="s">
         <v>56</v>
       </c>
-      <c r="F40" s="227"/>
+      <c r="F40" s="171"/>
       <c r="G40" s="38"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
@@ -6349,12 +6352,12 @@
       <c r="BN40" s="79"/>
     </row>
     <row r="41" spans="1:66">
-      <c r="A41" s="163"/>
+      <c r="A41" s="164"/>
       <c r="B41" s="34"/>
-      <c r="C41" s="223"/>
-      <c r="D41" s="224"/>
-      <c r="E41" s="226"/>
-      <c r="F41" s="228"/>
+      <c r="C41" s="167"/>
+      <c r="D41" s="168"/>
+      <c r="E41" s="170"/>
+      <c r="F41" s="172"/>
       <c r="G41" s="51"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
@@ -6411,26 +6414,26 @@
       <c r="BH41" s="101"/>
       <c r="BI41" s="13"/>
       <c r="BJ41" s="19"/>
-      <c r="BK41" s="101"/>
-      <c r="BL41" s="30"/>
+      <c r="BK41" s="122"/>
+      <c r="BL41" s="101"/>
       <c r="BM41" s="101"/>
       <c r="BN41" s="140"/>
     </row>
     <row r="42" spans="1:66">
-      <c r="A42" s="162">
+      <c r="A42" s="146">
         <v>14</v>
       </c>
-      <c r="B42" s="215" t="s">
+      <c r="B42" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="C42" s="207" t="s">
+      <c r="C42" s="150" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="208"/>
-      <c r="E42" s="215" t="s">
+      <c r="D42" s="151"/>
+      <c r="E42" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="F42" s="219"/>
+      <c r="F42" s="154"/>
       <c r="G42" s="38"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
@@ -6488,17 +6491,17 @@
       <c r="BI42" s="15"/>
       <c r="BJ42" s="21"/>
       <c r="BK42" s="65"/>
-      <c r="BL42" s="65"/>
+      <c r="BL42" s="40"/>
       <c r="BM42" s="65"/>
       <c r="BN42" s="79"/>
     </row>
     <row r="43" spans="1:66" ht="10.199999999999999" thickBot="1">
-      <c r="A43" s="214"/>
-      <c r="B43" s="216"/>
-      <c r="C43" s="217"/>
-      <c r="D43" s="218"/>
-      <c r="E43" s="216"/>
-      <c r="F43" s="220"/>
+      <c r="A43" s="147"/>
+      <c r="B43" s="149"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="153"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="155"/>
       <c r="G43" s="39"/>
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
@@ -6556,7 +6559,7 @@
       <c r="BI43" s="14"/>
       <c r="BJ43" s="20"/>
       <c r="BK43" s="69"/>
-      <c r="BL43" s="69"/>
+      <c r="BL43" s="238"/>
       <c r="BM43" s="69"/>
       <c r="BN43" s="81"/>
     </row>
@@ -6578,21 +6581,51 @@
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="C24:D25"/>
     <mergeCell ref="E24:E25"/>
@@ -6609,51 +6642,21 @@
     <mergeCell ref="C30:D31"/>
     <mergeCell ref="C32:D33"/>
     <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
@@ -6689,54 +6692,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A1" s="144" t="s">
+      <c r="A1" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="217" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="220" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="151"/>
-      <c r="E1" s="156" t="s">
+      <c r="D1" s="221"/>
+      <c r="E1" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="159" t="s">
+      <c r="F1" s="229" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="141"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="142"/>
-      <c r="L1" s="142"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
-      <c r="R1" s="142"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="142"/>
-      <c r="V1" s="142"/>
-      <c r="W1" s="142"/>
-      <c r="X1" s="142"/>
-      <c r="Y1" s="142"/>
-      <c r="Z1" s="142"/>
-      <c r="AA1" s="142"/>
-      <c r="AB1" s="142"/>
-      <c r="AC1" s="142"/>
-      <c r="AD1" s="143"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="212"/>
+      <c r="S1" s="212"/>
+      <c r="T1" s="212"/>
+      <c r="U1" s="212"/>
+      <c r="V1" s="212"/>
+      <c r="W1" s="212"/>
+      <c r="X1" s="212"/>
+      <c r="Y1" s="212"/>
+      <c r="Z1" s="212"/>
+      <c r="AA1" s="212"/>
+      <c r="AB1" s="212"/>
+      <c r="AC1" s="212"/>
+      <c r="AD1" s="213"/>
     </row>
     <row r="2" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A2" s="145"/>
-      <c r="B2" s="148"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="160"/>
+      <c r="A2" s="215"/>
+      <c r="B2" s="218"/>
+      <c r="C2" s="222"/>
+      <c r="D2" s="223"/>
+      <c r="E2" s="227"/>
+      <c r="F2" s="230"/>
       <c r="G2" s="46">
         <v>22</v>
       </c>
@@ -6811,12 +6814,12 @@
       </c>
     </row>
     <row r="3" spans="1:30" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="146"/>
-      <c r="B3" s="149"/>
-      <c r="C3" s="154"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="161"/>
+      <c r="A3" s="216"/>
+      <c r="B3" s="219"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="225"/>
+      <c r="E3" s="228"/>
+      <c r="F3" s="231"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -6891,20 +6894,20 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A4" s="172">
+      <c r="A4" s="204">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="173" t="s">
+      <c r="C4" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="174"/>
-      <c r="E4" s="177" t="s">
+      <c r="D4" s="206"/>
+      <c r="E4" s="207" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="179"/>
+      <c r="F4" s="209"/>
       <c r="G4" s="49"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -6927,20 +6930,20 @@
       <c r="Z4" s="12"/>
       <c r="AA4" s="18"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="232" t="s">
+      <c r="AC4" s="235" t="s">
         <v>14</v>
       </c>
-      <c r="AD4" s="229" t="s">
+      <c r="AD4" s="232" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A5" s="163"/>
+      <c r="A5" s="164"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="175"/>
-      <c r="D5" s="176"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="180"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="210"/>
       <c r="G5" s="50"/>
       <c r="H5" s="31"/>
       <c r="I5" s="9"/>
@@ -6963,22 +6966,22 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="9"/>
-      <c r="AC5" s="233"/>
-      <c r="AD5" s="230"/>
+      <c r="AC5" s="236"/>
+      <c r="AD5" s="233"/>
     </row>
     <row r="6" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A6" s="162">
+      <c r="A6" s="146">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="164" t="s">
+      <c r="C6" s="182" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="165"/>
-      <c r="E6" s="168" t="s">
+      <c r="D6" s="157"/>
+      <c r="E6" s="200" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="170"/>
+      <c r="F6" s="202"/>
       <c r="G6" s="51"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -7001,16 +7004,16 @@
       <c r="Z6" s="13"/>
       <c r="AA6" s="19"/>
       <c r="AB6" s="7"/>
-      <c r="AC6" s="233"/>
-      <c r="AD6" s="230"/>
+      <c r="AC6" s="236"/>
+      <c r="AD6" s="233"/>
     </row>
     <row r="7" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A7" s="163"/>
+      <c r="A7" s="164"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="166"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="169"/>
-      <c r="F7" s="171"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="203"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="24"/>
@@ -7033,24 +7036,24 @@
       <c r="Z7" s="25"/>
       <c r="AA7" s="26"/>
       <c r="AB7" s="24"/>
-      <c r="AC7" s="233"/>
-      <c r="AD7" s="230"/>
+      <c r="AC7" s="236"/>
+      <c r="AD7" s="233"/>
     </row>
     <row r="8" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A8" s="181">
+      <c r="A8" s="173">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="192" t="s">
+      <c r="C8" s="193" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="193"/>
-      <c r="E8" s="198" t="s">
+      <c r="D8" s="194"/>
+      <c r="E8" s="199" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="201"/>
+      <c r="F8" s="188"/>
       <c r="G8" s="38"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -7073,16 +7076,16 @@
       <c r="Z8" s="15"/>
       <c r="AA8" s="21"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="233"/>
-      <c r="AD8" s="230"/>
+      <c r="AC8" s="236"/>
+      <c r="AD8" s="233"/>
     </row>
     <row r="9" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A9" s="183"/>
+      <c r="A9" s="174"/>
       <c r="B9" s="37"/>
-      <c r="C9" s="196"/>
-      <c r="D9" s="197"/>
-      <c r="E9" s="200"/>
-      <c r="F9" s="203"/>
+      <c r="C9" s="197"/>
+      <c r="D9" s="198"/>
+      <c r="E9" s="185"/>
+      <c r="F9" s="163"/>
       <c r="G9" s="53"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
@@ -7105,24 +7108,24 @@
       <c r="Z9" s="44"/>
       <c r="AA9" s="45"/>
       <c r="AB9" s="43"/>
-      <c r="AC9" s="233"/>
-      <c r="AD9" s="230"/>
+      <c r="AC9" s="236"/>
+      <c r="AD9" s="233"/>
     </row>
     <row r="10" spans="1:30" ht="12" customHeight="1">
-      <c r="A10" s="182">
+      <c r="A10" s="186">
         <v>4</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="184" t="s">
+      <c r="C10" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="185"/>
-      <c r="E10" s="188" t="s">
+      <c r="D10" s="190"/>
+      <c r="E10" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="190"/>
+      <c r="F10" s="144"/>
       <c r="G10" s="50"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -7145,16 +7148,16 @@
       <c r="Z10" s="16"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="233"/>
-      <c r="AD10" s="230"/>
+      <c r="AC10" s="236"/>
+      <c r="AD10" s="233"/>
     </row>
     <row r="11" spans="1:30" ht="12" customHeight="1">
-      <c r="A11" s="183"/>
+      <c r="A11" s="174"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="189"/>
-      <c r="F11" s="191"/>
+      <c r="C11" s="191"/>
+      <c r="D11" s="192"/>
+      <c r="E11" s="177"/>
+      <c r="F11" s="145"/>
       <c r="G11" s="50"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -7177,22 +7180,22 @@
       <c r="Z11" s="16"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="233"/>
-      <c r="AD11" s="230"/>
+      <c r="AC11" s="236"/>
+      <c r="AD11" s="233"/>
     </row>
     <row r="12" spans="1:30" ht="12" customHeight="1">
-      <c r="A12" s="181">
+      <c r="A12" s="173">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="164" t="s">
+      <c r="C12" s="182" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="165"/>
-      <c r="E12" s="199" t="s">
+      <c r="D12" s="157"/>
+      <c r="E12" s="180" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="202"/>
+      <c r="F12" s="162"/>
       <c r="G12" s="51"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -7215,16 +7218,16 @@
       <c r="Z12" s="13"/>
       <c r="AA12" s="19"/>
       <c r="AB12" s="7"/>
-      <c r="AC12" s="233"/>
-      <c r="AD12" s="230"/>
+      <c r="AC12" s="236"/>
+      <c r="AD12" s="233"/>
     </row>
     <row r="13" spans="1:30" ht="12" customHeight="1">
-      <c r="A13" s="182"/>
+      <c r="A13" s="186"/>
       <c r="B13" s="36"/>
-      <c r="C13" s="204"/>
-      <c r="D13" s="205"/>
-      <c r="E13" s="188"/>
-      <c r="F13" s="190"/>
+      <c r="C13" s="187"/>
+      <c r="D13" s="159"/>
+      <c r="E13" s="161"/>
+      <c r="F13" s="144"/>
       <c r="G13" s="52"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
@@ -7247,24 +7250,24 @@
       <c r="Z13" s="25"/>
       <c r="AA13" s="26"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="233"/>
-      <c r="AD13" s="230"/>
+      <c r="AC13" s="236"/>
+      <c r="AD13" s="233"/>
     </row>
     <row r="14" spans="1:30" ht="12" customHeight="1">
-      <c r="A14" s="206">
+      <c r="A14" s="181">
         <v>6</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="207" t="s">
+      <c r="C14" s="150" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="208"/>
-      <c r="E14" s="209" t="s">
+      <c r="D14" s="151"/>
+      <c r="E14" s="176" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="201"/>
+      <c r="F14" s="188"/>
       <c r="G14" s="38"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -7287,16 +7290,16 @@
       <c r="Z14" s="15"/>
       <c r="AA14" s="21"/>
       <c r="AB14" s="6"/>
-      <c r="AC14" s="233"/>
-      <c r="AD14" s="230"/>
+      <c r="AC14" s="236"/>
+      <c r="AD14" s="233"/>
     </row>
     <row r="15" spans="1:30" ht="12" customHeight="1">
-      <c r="A15" s="206"/>
+      <c r="A15" s="181"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="175"/>
-      <c r="D15" s="176"/>
-      <c r="E15" s="189"/>
-      <c r="F15" s="191"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="175"/>
+      <c r="E15" s="177"/>
+      <c r="F15" s="145"/>
       <c r="G15" s="52"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
@@ -7319,22 +7322,22 @@
       <c r="Z15" s="25"/>
       <c r="AA15" s="26"/>
       <c r="AB15" s="24"/>
-      <c r="AC15" s="233"/>
-      <c r="AD15" s="230"/>
+      <c r="AC15" s="236"/>
+      <c r="AD15" s="233"/>
     </row>
     <row r="16" spans="1:30" ht="12" customHeight="1">
-      <c r="A16" s="206">
+      <c r="A16" s="181">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="164" t="s">
+      <c r="C16" s="182" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="165"/>
-      <c r="E16" s="210" t="s">
+      <c r="D16" s="157"/>
+      <c r="E16" s="160" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="202"/>
+      <c r="F16" s="162"/>
       <c r="G16" s="51"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -7357,16 +7360,16 @@
       <c r="Z16" s="13"/>
       <c r="AA16" s="19"/>
       <c r="AB16" s="7"/>
-      <c r="AC16" s="233"/>
-      <c r="AD16" s="230"/>
+      <c r="AC16" s="236"/>
+      <c r="AD16" s="233"/>
     </row>
     <row r="17" spans="1:30" ht="12" customHeight="1">
-      <c r="A17" s="206"/>
+      <c r="A17" s="181"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="175"/>
-      <c r="D17" s="176"/>
-      <c r="E17" s="189"/>
-      <c r="F17" s="191"/>
+      <c r="C17" s="158"/>
+      <c r="D17" s="175"/>
+      <c r="E17" s="177"/>
+      <c r="F17" s="145"/>
       <c r="G17" s="52"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -7389,22 +7392,22 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="233"/>
-      <c r="AD17" s="230"/>
+      <c r="AC17" s="236"/>
+      <c r="AD17" s="233"/>
     </row>
     <row r="18" spans="1:30" ht="12" customHeight="1">
-      <c r="A18" s="206">
+      <c r="A18" s="181">
         <v>8</v>
       </c>
       <c r="B18" s="36"/>
-      <c r="C18" s="164" t="s">
+      <c r="C18" s="182" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="165"/>
-      <c r="E18" s="210" t="s">
+      <c r="D18" s="157"/>
+      <c r="E18" s="160" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="202"/>
+      <c r="F18" s="162"/>
       <c r="G18" s="52"/>
       <c r="H18" s="24"/>
       <c r="I18" s="24"/>
@@ -7427,16 +7430,16 @@
       <c r="Z18" s="25"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="233"/>
-      <c r="AD18" s="230"/>
+      <c r="AC18" s="236"/>
+      <c r="AD18" s="233"/>
     </row>
     <row r="19" spans="1:30" ht="12" customHeight="1">
-      <c r="A19" s="206"/>
+      <c r="A19" s="181"/>
       <c r="B19" s="37"/>
-      <c r="C19" s="166"/>
-      <c r="D19" s="167"/>
-      <c r="E19" s="200"/>
-      <c r="F19" s="203"/>
+      <c r="C19" s="183"/>
+      <c r="D19" s="184"/>
+      <c r="E19" s="185"/>
+      <c r="F19" s="163"/>
       <c r="G19" s="54"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -7459,24 +7462,24 @@
       <c r="Z19" s="17"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="233"/>
-      <c r="AD19" s="230"/>
+      <c r="AC19" s="236"/>
+      <c r="AD19" s="233"/>
     </row>
     <row r="20" spans="1:30" ht="12" customHeight="1">
-      <c r="A20" s="181">
+      <c r="A20" s="173">
         <v>9</v>
       </c>
       <c r="B20" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="207" t="s">
+      <c r="C20" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="208"/>
-      <c r="E20" s="209" t="s">
+      <c r="D20" s="151"/>
+      <c r="E20" s="176" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="201"/>
+      <c r="F20" s="188"/>
       <c r="G20" s="38"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -7499,18 +7502,18 @@
       <c r="Z20" s="15"/>
       <c r="AA20" s="21"/>
       <c r="AB20" s="6"/>
-      <c r="AC20" s="233"/>
-      <c r="AD20" s="230"/>
+      <c r="AC20" s="236"/>
+      <c r="AD20" s="233"/>
     </row>
     <row r="21" spans="1:30" ht="12" customHeight="1">
-      <c r="A21" s="183"/>
+      <c r="A21" s="174"/>
       <c r="B21" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="175"/>
-      <c r="D21" s="176"/>
-      <c r="E21" s="189"/>
-      <c r="F21" s="191"/>
+      <c r="C21" s="158"/>
+      <c r="D21" s="175"/>
+      <c r="E21" s="177"/>
+      <c r="F21" s="145"/>
       <c r="G21" s="51"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -7533,22 +7536,22 @@
       <c r="Z21" s="13"/>
       <c r="AA21" s="19"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="233"/>
-      <c r="AD21" s="230"/>
+      <c r="AC21" s="236"/>
+      <c r="AD21" s="233"/>
     </row>
     <row r="22" spans="1:30" ht="12" customHeight="1">
-      <c r="A22" s="181">
+      <c r="A22" s="173">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="213" t="s">
+      <c r="C22" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="165"/>
-      <c r="E22" s="210" t="s">
+      <c r="D22" s="157"/>
+      <c r="E22" s="160" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="202"/>
+      <c r="F22" s="162"/>
       <c r="G22" s="51"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -7571,16 +7574,16 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="19"/>
       <c r="AB22" s="7"/>
-      <c r="AC22" s="233"/>
-      <c r="AD22" s="230"/>
+      <c r="AC22" s="236"/>
+      <c r="AD22" s="233"/>
     </row>
     <row r="23" spans="1:30" ht="12" customHeight="1">
-      <c r="A23" s="183"/>
+      <c r="A23" s="174"/>
       <c r="B23" s="36"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="176"/>
-      <c r="E23" s="189"/>
-      <c r="F23" s="191"/>
+      <c r="C23" s="158"/>
+      <c r="D23" s="175"/>
+      <c r="E23" s="177"/>
+      <c r="F23" s="145"/>
       <c r="G23" s="51"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -7603,22 +7606,22 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="19"/>
       <c r="AB23" s="7"/>
-      <c r="AC23" s="233"/>
-      <c r="AD23" s="230"/>
+      <c r="AC23" s="236"/>
+      <c r="AD23" s="233"/>
     </row>
     <row r="24" spans="1:30" ht="12" customHeight="1">
-      <c r="A24" s="181">
+      <c r="A24" s="173">
         <v>11</v>
       </c>
       <c r="B24" s="36"/>
-      <c r="C24" s="213" t="s">
+      <c r="C24" s="156" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="165"/>
-      <c r="E24" s="210" t="s">
+      <c r="D24" s="157"/>
+      <c r="E24" s="160" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="202"/>
+      <c r="F24" s="162"/>
       <c r="G24" s="52"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -7641,16 +7644,16 @@
       <c r="Z24" s="25"/>
       <c r="AA24" s="26"/>
       <c r="AB24" s="24"/>
-      <c r="AC24" s="233"/>
-      <c r="AD24" s="230"/>
+      <c r="AC24" s="236"/>
+      <c r="AD24" s="233"/>
     </row>
     <row r="25" spans="1:30" ht="12" customHeight="1">
-      <c r="A25" s="183"/>
+      <c r="A25" s="174"/>
       <c r="B25" s="37"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="176"/>
-      <c r="E25" s="189"/>
-      <c r="F25" s="203"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="175"/>
+      <c r="E25" s="177"/>
+      <c r="F25" s="163"/>
       <c r="G25" s="54"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -7673,24 +7676,24 @@
       <c r="Z25" s="17"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="233"/>
-      <c r="AD25" s="230"/>
+      <c r="AC25" s="236"/>
+      <c r="AD25" s="233"/>
     </row>
     <row r="26" spans="1:30" ht="12" customHeight="1">
-      <c r="A26" s="162">
+      <c r="A26" s="146">
         <v>12</v>
       </c>
       <c r="B26" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="221" t="s">
+      <c r="C26" s="165" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="222"/>
-      <c r="E26" s="225" t="s">
+      <c r="D26" s="166"/>
+      <c r="E26" s="169" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="227"/>
+      <c r="F26" s="171"/>
       <c r="G26" s="38"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -7713,16 +7716,16 @@
       <c r="Z26" s="15"/>
       <c r="AA26" s="21"/>
       <c r="AB26" s="6"/>
-      <c r="AC26" s="233"/>
-      <c r="AD26" s="230"/>
+      <c r="AC26" s="236"/>
+      <c r="AD26" s="233"/>
     </row>
     <row r="27" spans="1:30" ht="12" customHeight="1">
-      <c r="A27" s="163"/>
+      <c r="A27" s="164"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="223"/>
-      <c r="D27" s="224"/>
-      <c r="E27" s="226"/>
-      <c r="F27" s="228"/>
+      <c r="C27" s="167"/>
+      <c r="D27" s="168"/>
+      <c r="E27" s="170"/>
+      <c r="F27" s="172"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -7745,24 +7748,24 @@
       <c r="Z27" s="13"/>
       <c r="AA27" s="19"/>
       <c r="AB27" s="7"/>
-      <c r="AC27" s="233"/>
-      <c r="AD27" s="230"/>
+      <c r="AC27" s="236"/>
+      <c r="AD27" s="233"/>
     </row>
     <row r="28" spans="1:30" ht="12" customHeight="1">
-      <c r="A28" s="162">
+      <c r="A28" s="146">
         <v>14</v>
       </c>
-      <c r="B28" s="215" t="s">
+      <c r="B28" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="207" t="s">
+      <c r="C28" s="150" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="208"/>
-      <c r="E28" s="215" t="s">
+      <c r="D28" s="151"/>
+      <c r="E28" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="219"/>
+      <c r="F28" s="154"/>
       <c r="G28" s="38"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -7785,16 +7788,16 @@
       <c r="Z28" s="15"/>
       <c r="AA28" s="21"/>
       <c r="AB28" s="40"/>
-      <c r="AC28" s="233"/>
-      <c r="AD28" s="230"/>
+      <c r="AC28" s="236"/>
+      <c r="AD28" s="233"/>
     </row>
     <row r="29" spans="1:30" ht="12" customHeight="1" thickBot="1">
-      <c r="A29" s="214"/>
-      <c r="B29" s="216"/>
-      <c r="C29" s="217"/>
-      <c r="D29" s="218"/>
-      <c r="E29" s="216"/>
-      <c r="F29" s="220"/>
+      <c r="A29" s="147"/>
+      <c r="B29" s="149"/>
+      <c r="C29" s="152"/>
+      <c r="D29" s="153"/>
+      <c r="E29" s="149"/>
+      <c r="F29" s="155"/>
       <c r="G29" s="39"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -7817,8 +7820,8 @@
       <c r="Z29" s="14"/>
       <c r="AA29" s="20"/>
       <c r="AB29" s="11"/>
-      <c r="AC29" s="234"/>
-      <c r="AD29" s="231"/>
+      <c r="AC29" s="237"/>
+      <c r="AD29" s="234"/>
     </row>
     <row r="30" spans="1:30">
       <c r="Z30" s="5"/>
@@ -7838,12 +7841,45 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="G1:AD1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="AD4:AD29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C6:D7"/>
@@ -7860,45 +7896,12 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G1:AD1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
